--- a/import/schedule/Расписание.xlsx
+++ b/import/schedule/Расписание.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asv\Desktop\CollegeLMS\import\schedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A9A65D-0D29-4AE5-BE9E-98FE27797884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F72D74C-D775-4138-BA33-7F95FD46542B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1570,9 +1570,6 @@
     <t>418 Биология (16) Боброва О.В.</t>
   </si>
   <si>
-    <t>232 История (9) Петренко В. Б.</t>
-  </si>
-  <si>
     <t>312 География (6,8) Москаленко А.Ш.</t>
   </si>
   <si>
@@ -3370,9 +3367,6 @@
     <t>Диспетчер образовательного учреждения________________/Е.С.Офицеркина</t>
   </si>
   <si>
-    <t>215л МДК.05.02 (7,9) Сурова Е.А. Романенко С.В.</t>
-  </si>
-  <si>
     <t>320 МДК.04.01 (11) Романенко С.В.</t>
   </si>
   <si>
@@ -3380,6 +3374,12 @@
   </si>
   <si>
     <t>414 Математика (2,4,6,8,10,12,14,16) Марченко В.Ф.</t>
+  </si>
+  <si>
+    <t>215л МДК.05.02 (7,9) Сурова Е.А.</t>
+  </si>
+  <si>
+    <t>232 История (9) Петренко В.Б.</t>
   </si>
 </sst>
 </file>
@@ -5010,26 +5010,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5046,6 +5039,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -5060,6 +5056,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5089,10 +5089,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5134,38 +5130,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5188,9 +5192,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5202,10 +5203,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5218,10 +5215,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5601,11 +5601,11 @@
       <c r="AF1" s="7"/>
       <c r="AG1" s="6"/>
       <c r="AL1" s="8"/>
-      <c r="AO1" s="254" t="s">
+      <c r="AO1" s="256" t="s">
         <v>0</v>
       </c>
       <c r="AP1" s="186"/>
-      <c r="AQ1" s="254"/>
+      <c r="AQ1" s="256"/>
       <c r="AR1" s="186"/>
       <c r="AU1" s="8"/>
     </row>
@@ -5826,10 +5826,10 @@
       </c>
     </row>
     <row r="6" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="205" t="s">
+      <c r="A6" s="203" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="239">
+      <c r="B6" s="237">
         <v>1</v>
       </c>
       <c r="C6" s="172" t="s">
@@ -5887,7 +5887,7 @@
         <v>73</v>
       </c>
       <c r="U6" s="120" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="V6" s="140" t="s">
         <v>74</v>
@@ -5975,12 +5975,12 @@
       </c>
     </row>
     <row r="7" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="196"/>
-      <c r="B7" s="196"/>
+      <c r="A7" s="194"/>
+      <c r="B7" s="194"/>
       <c r="C7" s="160"/>
       <c r="D7" s="120"/>
       <c r="E7" s="168" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="F7" s="124"/>
       <c r="G7" s="119"/>
@@ -6002,7 +6002,7 @@
       <c r="Q7" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="R7" s="272"/>
+      <c r="R7" s="271"/>
       <c r="S7" s="178"/>
       <c r="T7" s="120"/>
       <c r="U7" s="120"/>
@@ -6062,8 +6062,8 @@
       <c r="AY7" s="120"/>
     </row>
     <row r="8" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="196"/>
-      <c r="B8" s="196"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="194"/>
       <c r="C8" s="160"/>
       <c r="D8" s="120"/>
       <c r="E8" s="122" t="s">
@@ -6117,8 +6117,8 @@
       <c r="AY8" s="120"/>
     </row>
     <row r="9" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="196"/>
-      <c r="B9" s="196"/>
+      <c r="A9" s="194"/>
+      <c r="B9" s="194"/>
       <c r="C9" s="160"/>
       <c r="D9" s="120"/>
       <c r="E9" s="123"/>
@@ -6162,7 +6162,7 @@
       <c r="AQ9" s="179"/>
       <c r="AR9" s="120"/>
       <c r="AS9" s="179"/>
-      <c r="AT9" s="248"/>
+      <c r="AT9" s="249"/>
       <c r="AU9" s="221"/>
       <c r="AV9" s="179"/>
       <c r="AW9" s="120"/>
@@ -6170,8 +6170,8 @@
       <c r="AY9" s="120"/>
     </row>
     <row r="10" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="196"/>
-      <c r="B10" s="196"/>
+      <c r="A10" s="194"/>
+      <c r="B10" s="194"/>
       <c r="C10" s="160"/>
       <c r="D10" s="120"/>
       <c r="E10" s="123"/>
@@ -6215,16 +6215,16 @@
       <c r="AQ10" s="179"/>
       <c r="AR10" s="120"/>
       <c r="AS10" s="120"/>
-      <c r="AT10" s="225"/>
-      <c r="AU10" s="211"/>
+      <c r="AT10" s="240"/>
+      <c r="AU10" s="209"/>
       <c r="AV10" s="120"/>
       <c r="AW10" s="120"/>
       <c r="AX10" s="179"/>
       <c r="AY10" s="120"/>
     </row>
     <row r="11" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="196"/>
-      <c r="B11" s="196"/>
+      <c r="A11" s="194"/>
+      <c r="B11" s="194"/>
       <c r="C11" s="160"/>
       <c r="D11" s="120"/>
       <c r="E11" s="123"/>
@@ -6268,16 +6268,16 @@
       <c r="AQ11" s="120"/>
       <c r="AR11" s="131"/>
       <c r="AS11" s="120"/>
-      <c r="AT11" s="225"/>
-      <c r="AU11" s="211"/>
+      <c r="AT11" s="240"/>
+      <c r="AU11" s="209"/>
       <c r="AV11" s="121"/>
       <c r="AW11" s="120"/>
       <c r="AX11" s="179"/>
       <c r="AY11" s="120"/>
     </row>
     <row r="12" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="196"/>
-      <c r="B12" s="196"/>
+      <c r="A12" s="194"/>
+      <c r="B12" s="194"/>
       <c r="C12" s="160"/>
       <c r="D12" s="120"/>
       <c r="E12" s="123"/>
@@ -6321,16 +6321,16 @@
       <c r="AQ12" s="120"/>
       <c r="AR12" s="120"/>
       <c r="AS12" s="120"/>
-      <c r="AT12" s="225"/>
-      <c r="AU12" s="211"/>
+      <c r="AT12" s="240"/>
+      <c r="AU12" s="209"/>
       <c r="AV12" s="120"/>
       <c r="AW12" s="120"/>
       <c r="AX12" s="179"/>
       <c r="AY12" s="120"/>
     </row>
     <row r="13" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="196"/>
-      <c r="B13" s="197"/>
+      <c r="A13" s="194"/>
+      <c r="B13" s="195"/>
       <c r="C13" s="161"/>
       <c r="D13" s="139"/>
       <c r="E13" s="154"/>
@@ -6382,8 +6382,8 @@
       <c r="AY13" s="139"/>
     </row>
     <row r="14" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="196"/>
-      <c r="B14" s="195">
+      <c r="A14" s="194"/>
+      <c r="B14" s="193">
         <v>2</v>
       </c>
       <c r="C14" s="159" t="s">
@@ -6535,11 +6535,11 @@
       </c>
     </row>
     <row r="15" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="196"/>
-      <c r="B15" s="196"/>
+      <c r="A15" s="194"/>
+      <c r="B15" s="194"/>
       <c r="C15" s="160"/>
       <c r="D15" s="120"/>
-      <c r="E15" s="198"/>
+      <c r="E15" s="189"/>
       <c r="F15" s="122"/>
       <c r="G15" s="168" t="s">
         <v>152</v>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="AV15" s="187"/>
       <c r="AW15" s="143"/>
-      <c r="AX15" s="224"/>
+      <c r="AX15" s="239"/>
       <c r="AY15" s="143"/>
     </row>
     <row r="16" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="196"/>
-      <c r="B16" s="196"/>
+      <c r="A16" s="194"/>
+      <c r="B16" s="194"/>
       <c r="C16" s="160"/>
       <c r="D16" s="120"/>
       <c r="E16" s="179"/>
@@ -6642,7 +6642,7 @@
       <c r="Z16" s="120"/>
       <c r="AA16" s="179"/>
       <c r="AB16" s="179"/>
-      <c r="AC16" s="199"/>
+      <c r="AC16" s="196"/>
       <c r="AD16" s="178"/>
       <c r="AE16" s="179"/>
       <c r="AF16" s="179"/>
@@ -6663,12 +6663,12 @@
       <c r="AU16" s="120"/>
       <c r="AV16" s="188"/>
       <c r="AW16" s="143"/>
-      <c r="AX16" s="225"/>
+      <c r="AX16" s="240"/>
       <c r="AY16" s="143"/>
     </row>
     <row r="17" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="196"/>
-      <c r="B17" s="196"/>
+      <c r="A17" s="194"/>
+      <c r="B17" s="194"/>
       <c r="C17" s="160"/>
       <c r="D17" s="120"/>
       <c r="E17" s="179"/>
@@ -6679,11 +6679,11 @@
       <c r="J17" s="179"/>
       <c r="K17" s="46"/>
       <c r="L17" s="179"/>
-      <c r="M17" s="232"/>
+      <c r="M17" s="230"/>
       <c r="N17" s="179"/>
       <c r="O17" s="179"/>
       <c r="P17" s="179"/>
-      <c r="Q17" s="198"/>
+      <c r="Q17" s="189"/>
       <c r="R17" s="179"/>
       <c r="S17" s="179"/>
       <c r="T17" s="181"/>
@@ -6716,12 +6716,12 @@
       <c r="AU17" s="120"/>
       <c r="AV17" s="188"/>
       <c r="AW17" s="143"/>
-      <c r="AX17" s="225"/>
+      <c r="AX17" s="240"/>
       <c r="AY17" s="143"/>
     </row>
     <row r="18" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="196"/>
-      <c r="B18" s="196"/>
+      <c r="A18" s="194"/>
+      <c r="B18" s="194"/>
       <c r="C18" s="160"/>
       <c r="D18" s="120"/>
       <c r="E18" s="179"/>
@@ -6769,12 +6769,12 @@
       <c r="AU18" s="180"/>
       <c r="AV18" s="188"/>
       <c r="AW18" s="143"/>
-      <c r="AX18" s="225"/>
+      <c r="AX18" s="240"/>
       <c r="AY18" s="143"/>
     </row>
     <row r="19" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="196"/>
-      <c r="B19" s="196"/>
+      <c r="A19" s="194"/>
+      <c r="B19" s="194"/>
       <c r="C19" s="160"/>
       <c r="D19" s="120"/>
       <c r="E19" s="179"/>
@@ -6822,12 +6822,12 @@
       <c r="AU19" s="179"/>
       <c r="AV19" s="120"/>
       <c r="AW19" s="120"/>
-      <c r="AX19" s="225"/>
+      <c r="AX19" s="240"/>
       <c r="AY19" s="120"/>
     </row>
     <row r="20" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="196"/>
-      <c r="B20" s="196"/>
+      <c r="A20" s="194"/>
+      <c r="B20" s="194"/>
       <c r="C20" s="160"/>
       <c r="D20" s="120"/>
       <c r="E20" s="179"/>
@@ -6879,8 +6879,8 @@
       <c r="AY20" s="120"/>
     </row>
     <row r="21" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="196"/>
-      <c r="B21" s="196"/>
+      <c r="A21" s="194"/>
+      <c r="B21" s="194"/>
       <c r="C21" s="160"/>
       <c r="D21" s="120"/>
       <c r="E21" s="179"/>
@@ -6932,8 +6932,8 @@
       <c r="AY21" s="120"/>
     </row>
     <row r="22" spans="1:51" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="196"/>
-      <c r="B22" s="197"/>
+      <c r="A22" s="194"/>
+      <c r="B22" s="195"/>
       <c r="C22" s="161"/>
       <c r="D22" s="139"/>
       <c r="E22" s="184"/>
@@ -6985,7 +6985,7 @@
       <c r="AY22" s="132"/>
     </row>
     <row r="23" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="196"/>
+      <c r="A23" s="194"/>
       <c r="B23" s="213">
         <v>3</v>
       </c>
@@ -7138,13 +7138,13 @@
       </c>
     </row>
     <row r="24" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="196"/>
-      <c r="B24" s="196"/>
+      <c r="A24" s="194"/>
+      <c r="B24" s="194"/>
       <c r="C24" s="160"/>
       <c r="D24" s="122" t="s">
         <v>204</v>
       </c>
-      <c r="E24" s="201"/>
+      <c r="E24" s="198"/>
       <c r="F24" s="119" t="s">
         <v>205</v>
       </c>
@@ -7224,15 +7224,15 @@
       <c r="AV24" s="119" t="s">
         <v>218</v>
       </c>
-      <c r="AW24" s="267"/>
+      <c r="AW24" s="252"/>
       <c r="AX24" s="143"/>
       <c r="AY24" s="187"/>
     </row>
     <row r="25" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="196"/>
-      <c r="B25" s="196"/>
+      <c r="A25" s="194"/>
+      <c r="B25" s="194"/>
       <c r="C25" s="160"/>
-      <c r="D25" s="201"/>
+      <c r="D25" s="198"/>
       <c r="E25" s="179"/>
       <c r="F25" s="119"/>
       <c r="G25" s="120"/>
@@ -7273,7 +7273,7 @@
       <c r="AH25" s="119" t="s">
         <v>223</v>
       </c>
-      <c r="AI25" s="198"/>
+      <c r="AI25" s="189"/>
       <c r="AJ25" s="179"/>
       <c r="AK25" s="120"/>
       <c r="AL25" s="179"/>
@@ -7286,14 +7286,14 @@
       <c r="AS25" s="120"/>
       <c r="AT25" s="120"/>
       <c r="AU25" s="120"/>
-      <c r="AV25" s="224"/>
-      <c r="AW25" s="268"/>
+      <c r="AV25" s="239"/>
+      <c r="AW25" s="253"/>
       <c r="AX25" s="143"/>
       <c r="AY25" s="188"/>
     </row>
     <row r="26" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="196"/>
-      <c r="B26" s="196"/>
+      <c r="A26" s="194"/>
+      <c r="B26" s="194"/>
       <c r="C26" s="160"/>
       <c r="D26" s="179"/>
       <c r="E26" s="179"/>
@@ -7322,7 +7322,7 @@
       <c r="AB26" s="179"/>
       <c r="AC26" s="179"/>
       <c r="AD26" s="120"/>
-      <c r="AE26" s="258"/>
+      <c r="AE26" s="260"/>
       <c r="AF26" s="179"/>
       <c r="AG26" s="179"/>
       <c r="AH26" s="14"/>
@@ -7339,14 +7339,14 @@
       <c r="AS26" s="120"/>
       <c r="AT26" s="120"/>
       <c r="AU26" s="120"/>
-      <c r="AV26" s="225"/>
-      <c r="AW26" s="268"/>
+      <c r="AV26" s="240"/>
+      <c r="AW26" s="253"/>
       <c r="AX26" s="143"/>
       <c r="AY26" s="188"/>
     </row>
     <row r="27" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="196"/>
-      <c r="B27" s="196"/>
+      <c r="A27" s="194"/>
+      <c r="B27" s="194"/>
       <c r="C27" s="160"/>
       <c r="D27" s="179"/>
       <c r="E27" s="179"/>
@@ -7392,14 +7392,14 @@
       <c r="AS27" s="120"/>
       <c r="AT27" s="120"/>
       <c r="AU27" s="120"/>
-      <c r="AV27" s="225"/>
+      <c r="AV27" s="240"/>
       <c r="AW27" s="120"/>
       <c r="AX27" s="120"/>
       <c r="AY27" s="120"/>
     </row>
     <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="196"/>
-      <c r="B28" s="196"/>
+      <c r="A28" s="194"/>
+      <c r="B28" s="194"/>
       <c r="C28" s="160"/>
       <c r="D28" s="179"/>
       <c r="E28" s="179"/>
@@ -7407,7 +7407,7 @@
       <c r="G28" s="39"/>
       <c r="H28" s="123"/>
       <c r="I28" s="169"/>
-      <c r="J28" s="189"/>
+      <c r="J28" s="202"/>
       <c r="K28" s="179"/>
       <c r="L28" s="179"/>
       <c r="M28" s="39"/>
@@ -7431,7 +7431,7 @@
       <c r="AE28" s="179"/>
       <c r="AF28" s="148"/>
       <c r="AG28" s="120"/>
-      <c r="AH28" s="189"/>
+      <c r="AH28" s="202"/>
       <c r="AI28" s="179"/>
       <c r="AJ28" s="120"/>
       <c r="AK28" s="141"/>
@@ -7445,14 +7445,14 @@
       <c r="AS28" s="120"/>
       <c r="AT28" s="120"/>
       <c r="AU28" s="120"/>
-      <c r="AV28" s="225"/>
+      <c r="AV28" s="240"/>
       <c r="AW28" s="121"/>
       <c r="AX28" s="120"/>
       <c r="AY28" s="121"/>
     </row>
     <row r="29" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="196"/>
-      <c r="B29" s="196"/>
+      <c r="A29" s="194"/>
+      <c r="B29" s="194"/>
       <c r="C29" s="160"/>
       <c r="D29" s="179"/>
       <c r="E29" s="179"/>
@@ -7504,8 +7504,8 @@
       <c r="AY29" s="120"/>
     </row>
     <row r="30" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="196"/>
-      <c r="B30" s="197"/>
+      <c r="A30" s="194"/>
+      <c r="B30" s="195"/>
       <c r="C30" s="161"/>
       <c r="D30" s="184"/>
       <c r="E30" s="184"/>
@@ -7557,7 +7557,7 @@
       <c r="AY30" s="139"/>
     </row>
     <row r="31" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="196"/>
+      <c r="A31" s="194"/>
       <c r="B31" s="213">
         <v>4</v>
       </c>
@@ -7704,8 +7704,8 @@
       </c>
     </row>
     <row r="32" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="196"/>
-      <c r="B32" s="196"/>
+      <c r="A32" s="194"/>
+      <c r="B32" s="194"/>
       <c r="C32" s="159" t="s">
         <v>264</v>
       </c>
@@ -7813,10 +7813,10 @@
       <c r="AY32" s="120"/>
     </row>
     <row r="33" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="196"/>
-      <c r="B33" s="196"/>
-      <c r="C33" s="226"/>
-      <c r="D33" s="198"/>
+      <c r="A33" s="194"/>
+      <c r="B33" s="194"/>
+      <c r="C33" s="224"/>
+      <c r="D33" s="189"/>
       <c r="E33" s="51" t="s">
         <v>291</v>
       </c>
@@ -7824,7 +7824,7 @@
       <c r="G33" s="122" t="s">
         <v>292</v>
       </c>
-      <c r="H33" s="198"/>
+      <c r="H33" s="189"/>
       <c r="I33" s="119"/>
       <c r="J33" s="181"/>
       <c r="K33" s="122" t="s">
@@ -7871,7 +7871,7 @@
       <c r="AN33" s="179"/>
       <c r="AO33" s="120"/>
       <c r="AP33" s="179"/>
-      <c r="AQ33" s="233"/>
+      <c r="AQ33" s="231"/>
       <c r="AR33" s="178"/>
       <c r="AS33" s="120"/>
       <c r="AT33" s="178"/>
@@ -7882,13 +7882,13 @@
       <c r="AY33" s="120"/>
     </row>
     <row r="34" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="196"/>
-      <c r="B34" s="196"/>
+      <c r="A34" s="194"/>
+      <c r="B34" s="194"/>
       <c r="C34" s="215"/>
       <c r="D34" s="179"/>
-      <c r="E34" s="201"/>
+      <c r="E34" s="198"/>
       <c r="F34" s="46"/>
-      <c r="G34" s="201"/>
+      <c r="G34" s="198"/>
       <c r="H34" s="179"/>
       <c r="I34" s="120"/>
       <c r="J34" s="179"/>
@@ -7909,7 +7909,7 @@
       <c r="Y34" s="179"/>
       <c r="Z34" s="120"/>
       <c r="AA34" s="179"/>
-      <c r="AB34" s="198"/>
+      <c r="AB34" s="189"/>
       <c r="AC34" s="179"/>
       <c r="AD34" s="180"/>
       <c r="AE34" s="120"/>
@@ -7924,7 +7924,7 @@
       <c r="AN34" s="179"/>
       <c r="AO34" s="120"/>
       <c r="AP34" s="179"/>
-      <c r="AQ34" s="211"/>
+      <c r="AQ34" s="209"/>
       <c r="AR34" s="179"/>
       <c r="AS34" s="180"/>
       <c r="AT34" s="179"/>
@@ -7935,8 +7935,8 @@
       <c r="AY34" s="120"/>
     </row>
     <row r="35" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="196"/>
-      <c r="B35" s="196"/>
+      <c r="A35" s="194"/>
+      <c r="B35" s="194"/>
       <c r="C35" s="215"/>
       <c r="D35" s="179"/>
       <c r="E35" s="179"/>
@@ -7977,7 +7977,7 @@
       <c r="AN35" s="179"/>
       <c r="AO35" s="120"/>
       <c r="AP35" s="137"/>
-      <c r="AQ35" s="211"/>
+      <c r="AQ35" s="209"/>
       <c r="AR35" s="179"/>
       <c r="AS35" s="179"/>
       <c r="AT35" s="179"/>
@@ -7988,8 +7988,8 @@
       <c r="AY35" s="120"/>
     </row>
     <row r="36" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="196"/>
-      <c r="B36" s="196"/>
+      <c r="A36" s="194"/>
+      <c r="B36" s="194"/>
       <c r="C36" s="215"/>
       <c r="D36" s="179"/>
       <c r="E36" s="179"/>
@@ -8030,7 +8030,7 @@
       <c r="AN36" s="131"/>
       <c r="AO36" s="120"/>
       <c r="AP36" s="131"/>
-      <c r="AQ36" s="211"/>
+      <c r="AQ36" s="209"/>
       <c r="AR36" s="179"/>
       <c r="AS36" s="179"/>
       <c r="AT36" s="179"/>
@@ -8041,8 +8041,8 @@
       <c r="AY36" s="120"/>
     </row>
     <row r="37" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="196"/>
-      <c r="B37" s="196"/>
+      <c r="A37" s="194"/>
+      <c r="B37" s="194"/>
       <c r="C37" s="215"/>
       <c r="D37" s="179"/>
       <c r="E37" s="179"/>
@@ -8083,7 +8083,7 @@
       <c r="AN37" s="120"/>
       <c r="AO37" s="120"/>
       <c r="AP37" s="35"/>
-      <c r="AQ37" s="211"/>
+      <c r="AQ37" s="209"/>
       <c r="AR37" s="179"/>
       <c r="AS37" s="179"/>
       <c r="AT37" s="179"/>
@@ -8094,8 +8094,8 @@
       <c r="AY37" s="120"/>
     </row>
     <row r="38" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="196"/>
-      <c r="B38" s="197"/>
+      <c r="A38" s="194"/>
+      <c r="B38" s="195"/>
       <c r="C38" s="216"/>
       <c r="D38" s="184"/>
       <c r="E38" s="184"/>
@@ -8147,11 +8147,11 @@
       <c r="AY38" s="139"/>
     </row>
     <row r="39" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="196"/>
+      <c r="A39" s="194"/>
       <c r="B39" s="213">
         <v>5</v>
       </c>
-      <c r="C39" s="226"/>
+      <c r="C39" s="224"/>
       <c r="D39" s="119"/>
       <c r="E39" s="140"/>
       <c r="F39" s="119"/>
@@ -8216,8 +8216,8 @@
       <c r="AY39" s="134"/>
     </row>
     <row r="40" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="196"/>
-      <c r="B40" s="196"/>
+      <c r="A40" s="194"/>
+      <c r="B40" s="194"/>
       <c r="C40" s="215"/>
       <c r="D40" s="120"/>
       <c r="E40" s="141"/>
@@ -8273,8 +8273,8 @@
       <c r="AY40" s="39"/>
     </row>
     <row r="41" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="196"/>
-      <c r="B41" s="196"/>
+      <c r="A41" s="194"/>
+      <c r="B41" s="194"/>
       <c r="C41" s="215"/>
       <c r="D41" s="131"/>
       <c r="E41" s="141"/>
@@ -8326,8 +8326,8 @@
       <c r="AY41" s="134"/>
     </row>
     <row r="42" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="196"/>
-      <c r="B42" s="196"/>
+      <c r="A42" s="194"/>
+      <c r="B42" s="194"/>
       <c r="C42" s="215"/>
       <c r="D42" s="120"/>
       <c r="E42" s="53"/>
@@ -8379,8 +8379,8 @@
       <c r="AY42" s="55"/>
     </row>
     <row r="43" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="196"/>
-      <c r="B43" s="197"/>
+      <c r="A43" s="194"/>
+      <c r="B43" s="195"/>
       <c r="C43" s="216"/>
       <c r="D43" s="139"/>
       <c r="E43" s="167"/>
@@ -8432,12 +8432,12 @@
       <c r="AY43" s="173"/>
     </row>
     <row r="44" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="196"/>
+      <c r="A44" s="194"/>
       <c r="B44" s="213">
         <v>6</v>
       </c>
       <c r="C44" s="223"/>
-      <c r="D44" s="200"/>
+      <c r="D44" s="197"/>
       <c r="E44" s="140"/>
       <c r="F44" s="119"/>
       <c r="G44" s="119"/>
@@ -8489,8 +8489,8 @@
       <c r="AY44" s="55"/>
     </row>
     <row r="45" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="196"/>
-      <c r="B45" s="196"/>
+      <c r="A45" s="194"/>
+      <c r="B45" s="194"/>
       <c r="C45" s="215"/>
       <c r="D45" s="179"/>
       <c r="E45" s="141"/>
@@ -8542,8 +8542,8 @@
       <c r="AY45" s="146"/>
     </row>
     <row r="46" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="196"/>
-      <c r="B46" s="196"/>
+      <c r="A46" s="194"/>
+      <c r="B46" s="194"/>
       <c r="C46" s="215"/>
       <c r="D46" s="179"/>
       <c r="E46" s="141"/>
@@ -8595,8 +8595,8 @@
       <c r="AY46" s="146"/>
     </row>
     <row r="47" spans="1:51" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="196"/>
-      <c r="B47" s="196"/>
+      <c r="A47" s="194"/>
+      <c r="B47" s="194"/>
       <c r="C47" s="215"/>
       <c r="D47" s="179"/>
       <c r="E47" s="141"/>
@@ -8648,8 +8648,8 @@
       <c r="AY47" s="146"/>
     </row>
     <row r="48" spans="1:51" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="196"/>
-      <c r="B48" s="197"/>
+      <c r="A48" s="194"/>
+      <c r="B48" s="195"/>
       <c r="C48" s="216"/>
       <c r="D48" s="184"/>
       <c r="E48" s="167"/>
@@ -8701,11 +8701,11 @@
       <c r="AY48" s="62"/>
     </row>
     <row r="49" spans="1:51" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="196"/>
-      <c r="B49" s="273">
+      <c r="A49" s="194"/>
+      <c r="B49" s="243">
         <v>7</v>
       </c>
-      <c r="C49" s="236"/>
+      <c r="C49" s="234"/>
       <c r="D49" s="119"/>
       <c r="E49" s="140"/>
       <c r="F49" s="119"/>
@@ -8756,8 +8756,8 @@
       <c r="AY49" s="145"/>
     </row>
     <row r="50" spans="1:51" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="196"/>
-      <c r="B50" s="196"/>
+      <c r="A50" s="194"/>
+      <c r="B50" s="194"/>
       <c r="C50" s="215"/>
       <c r="D50" s="120"/>
       <c r="E50" s="141"/>
@@ -8809,8 +8809,8 @@
       <c r="AY50" s="146"/>
     </row>
     <row r="51" spans="1:51" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="196"/>
-      <c r="B51" s="196"/>
+      <c r="A51" s="194"/>
+      <c r="B51" s="194"/>
       <c r="C51" s="215"/>
       <c r="D51" s="120"/>
       <c r="E51" s="141"/>
@@ -8862,8 +8862,8 @@
       <c r="AY51" s="146"/>
     </row>
     <row r="52" spans="1:51" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="196"/>
-      <c r="B52" s="196"/>
+      <c r="A52" s="194"/>
+      <c r="B52" s="194"/>
       <c r="C52" s="215"/>
       <c r="D52" s="120"/>
       <c r="E52" s="141"/>
@@ -8915,9 +8915,9 @@
       <c r="AY52" s="146"/>
     </row>
     <row r="53" spans="1:51" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="206"/>
-      <c r="B53" s="206"/>
-      <c r="C53" s="237"/>
+      <c r="A53" s="204"/>
+      <c r="B53" s="204"/>
+      <c r="C53" s="235"/>
       <c r="D53" s="171"/>
       <c r="E53" s="141"/>
       <c r="F53" s="171"/>
@@ -8968,10 +8968,10 @@
       <c r="AY53" s="67"/>
     </row>
     <row r="54" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="205" t="s">
+      <c r="A54" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="B54" s="231">
+      <c r="B54" s="229">
         <v>1</v>
       </c>
       <c r="C54" s="166" t="s">
@@ -9119,7 +9119,7 @@
       </c>
     </row>
     <row r="55" spans="1:51" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="196"/>
+      <c r="A55" s="194"/>
       <c r="B55" s="191"/>
       <c r="C55" s="222"/>
       <c r="D55" s="174"/>
@@ -9176,7 +9176,7 @@
       <c r="AG55" s="119"/>
       <c r="AH55" s="178"/>
       <c r="AI55" s="178"/>
-      <c r="AJ55" s="271"/>
+      <c r="AJ55" s="270"/>
       <c r="AK55" s="178"/>
       <c r="AL55" s="120"/>
       <c r="AM55" s="178"/>
@@ -9198,17 +9198,17 @@
       <c r="AW55" s="136" t="s">
         <v>352</v>
       </c>
-      <c r="AX55" s="233"/>
+      <c r="AX55" s="231"/>
       <c r="AY55" s="136" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="56" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="196"/>
+      <c r="A56" s="194"/>
       <c r="B56" s="191"/>
       <c r="C56" s="215"/>
       <c r="D56" s="123"/>
-      <c r="E56" s="269"/>
+      <c r="E56" s="268"/>
       <c r="F56" s="123"/>
       <c r="G56" s="123"/>
       <c r="H56" s="124"/>
@@ -9235,7 +9235,7 @@
       <c r="Y56" s="119"/>
       <c r="Z56" s="119"/>
       <c r="AA56" s="179"/>
-      <c r="AB56" s="198"/>
+      <c r="AB56" s="189"/>
       <c r="AC56" s="179"/>
       <c r="AD56" s="179"/>
       <c r="AE56" s="178"/>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="AU56" s="120"/>
       <c r="AV56" s="179"/>
-      <c r="AW56" s="224"/>
-      <c r="AX56" s="211"/>
+      <c r="AW56" s="239"/>
+      <c r="AX56" s="209"/>
       <c r="AY56" s="185"/>
     </row>
     <row r="57" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="196"/>
+      <c r="A57" s="194"/>
       <c r="B57" s="191"/>
       <c r="C57" s="215"/>
       <c r="D57" s="123"/>
@@ -9312,15 +9312,15 @@
       <c r="AQ57" s="120"/>
       <c r="AR57" s="120"/>
       <c r="AS57" s="178"/>
-      <c r="AT57" s="189"/>
+      <c r="AT57" s="202"/>
       <c r="AU57" s="120"/>
       <c r="AV57" s="179"/>
-      <c r="AW57" s="225"/>
-      <c r="AX57" s="211"/>
+      <c r="AW57" s="240"/>
+      <c r="AX57" s="209"/>
       <c r="AY57" s="186"/>
     </row>
     <row r="58" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="196"/>
+      <c r="A58" s="194"/>
       <c r="B58" s="191"/>
       <c r="C58" s="215"/>
       <c r="D58" s="123"/>
@@ -9368,12 +9368,12 @@
       <c r="AT58" s="179"/>
       <c r="AU58" s="120"/>
       <c r="AV58" s="179"/>
-      <c r="AW58" s="225"/>
-      <c r="AX58" s="211"/>
+      <c r="AW58" s="240"/>
+      <c r="AX58" s="209"/>
       <c r="AY58" s="186"/>
     </row>
     <row r="59" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="196"/>
+      <c r="A59" s="194"/>
       <c r="B59" s="191"/>
       <c r="C59" s="215"/>
       <c r="D59" s="123"/>
@@ -9421,12 +9421,12 @@
       <c r="AT59" s="179"/>
       <c r="AU59" s="120"/>
       <c r="AV59" s="179"/>
-      <c r="AW59" s="225"/>
+      <c r="AW59" s="240"/>
       <c r="AX59" s="137"/>
       <c r="AY59" s="186"/>
     </row>
     <row r="60" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="196"/>
+      <c r="A60" s="194"/>
       <c r="B60" s="191"/>
       <c r="C60" s="215"/>
       <c r="D60" s="22"/>
@@ -9474,13 +9474,13 @@
       <c r="AT60" s="179"/>
       <c r="AU60" s="120"/>
       <c r="AV60" s="120"/>
-      <c r="AW60" s="225"/>
+      <c r="AW60" s="240"/>
       <c r="AX60" s="143"/>
       <c r="AY60" s="186"/>
     </row>
     <row r="61" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="196"/>
-      <c r="B61" s="192"/>
+      <c r="A61" s="194"/>
+      <c r="B61" s="212"/>
       <c r="C61" s="216"/>
       <c r="D61" s="24"/>
       <c r="E61" s="184"/>
@@ -9532,8 +9532,8 @@
       <c r="AY61" s="139"/>
     </row>
     <row r="62" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="196"/>
-      <c r="B62" s="190">
+      <c r="A62" s="194"/>
+      <c r="B62" s="211">
         <v>2</v>
       </c>
       <c r="C62" s="164" t="s">
@@ -9683,17 +9683,17 @@
       </c>
     </row>
     <row r="63" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="196"/>
+      <c r="A63" s="194"/>
       <c r="B63" s="191"/>
       <c r="C63" s="164" t="s">
         <v>387</v>
       </c>
       <c r="D63" s="169"/>
-      <c r="E63" s="201"/>
+      <c r="E63" s="198"/>
       <c r="F63" s="169" t="s">
         <v>388</v>
       </c>
-      <c r="G63" s="198"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="119"/>
       <c r="I63" s="122" t="s">
         <v>389</v>
@@ -9758,7 +9758,7 @@
       <c r="AY63" s="120"/>
     </row>
     <row r="64" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="196"/>
+      <c r="A64" s="194"/>
       <c r="B64" s="191"/>
       <c r="C64" s="164" t="s">
         <v>397</v>
@@ -9823,9 +9823,9 @@
       <c r="AY64" s="120"/>
     </row>
     <row r="65" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="196"/>
+      <c r="A65" s="194"/>
       <c r="B65" s="191"/>
-      <c r="C65" s="207"/>
+      <c r="C65" s="205"/>
       <c r="D65" s="169"/>
       <c r="E65" s="179"/>
       <c r="F65" s="123"/>
@@ -9876,9 +9876,9 @@
       <c r="AY65" s="120"/>
     </row>
     <row r="66" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="196"/>
+      <c r="A66" s="194"/>
       <c r="B66" s="191"/>
-      <c r="C66" s="208"/>
+      <c r="C66" s="206"/>
       <c r="D66" s="169"/>
       <c r="E66" s="179"/>
       <c r="F66" s="123"/>
@@ -9919,7 +9919,7 @@
       <c r="AO66" s="179"/>
       <c r="AP66" s="179"/>
       <c r="AQ66" s="179"/>
-      <c r="AR66" s="189"/>
+      <c r="AR66" s="202"/>
       <c r="AS66" s="179"/>
       <c r="AT66" s="179"/>
       <c r="AU66" s="120"/>
@@ -9929,9 +9929,9 @@
       <c r="AY66" s="120"/>
     </row>
     <row r="67" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="196"/>
+      <c r="A67" s="194"/>
       <c r="B67" s="191"/>
-      <c r="C67" s="208"/>
+      <c r="C67" s="206"/>
       <c r="D67" s="169"/>
       <c r="E67" s="179"/>
       <c r="F67" s="123"/>
@@ -9982,9 +9982,9 @@
       <c r="AY67" s="120"/>
     </row>
     <row r="68" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="196"/>
+      <c r="A68" s="194"/>
       <c r="B68" s="191"/>
-      <c r="C68" s="208"/>
+      <c r="C68" s="206"/>
       <c r="D68" s="169"/>
       <c r="E68" s="179"/>
       <c r="F68" s="123"/>
@@ -10035,9 +10035,9 @@
       <c r="AY68" s="120"/>
     </row>
     <row r="69" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="196"/>
+      <c r="A69" s="194"/>
       <c r="B69" s="191"/>
-      <c r="C69" s="208"/>
+      <c r="C69" s="206"/>
       <c r="D69" s="169"/>
       <c r="E69" s="179"/>
       <c r="F69" s="123"/>
@@ -10088,9 +10088,9 @@
       <c r="AY69" s="120"/>
     </row>
     <row r="70" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="196"/>
-      <c r="B70" s="192"/>
-      <c r="C70" s="209"/>
+      <c r="A70" s="194"/>
+      <c r="B70" s="212"/>
+      <c r="C70" s="207"/>
       <c r="D70" s="157"/>
       <c r="E70" s="184"/>
       <c r="F70" s="154"/>
@@ -10141,8 +10141,8 @@
       <c r="AY70" s="139"/>
     </row>
     <row r="71" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="196"/>
-      <c r="B71" s="190">
+      <c r="A71" s="194"/>
+      <c r="B71" s="211">
         <v>3</v>
       </c>
       <c r="C71" s="164" t="s">
@@ -10294,10 +10294,10 @@
       </c>
     </row>
     <row r="72" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="196"/>
+      <c r="A72" s="194"/>
       <c r="B72" s="191"/>
       <c r="C72" s="241"/>
-      <c r="D72" s="198"/>
+      <c r="D72" s="189"/>
       <c r="E72" s="122" t="s">
         <v>433</v>
       </c>
@@ -10395,7 +10395,7 @@
       <c r="AY72" s="143"/>
     </row>
     <row r="73" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="196"/>
+      <c r="A73" s="194"/>
       <c r="B73" s="191"/>
       <c r="C73" s="215"/>
       <c r="D73" s="179"/>
@@ -10454,24 +10454,24 @@
       <c r="AS73" s="179"/>
       <c r="AT73" s="120"/>
       <c r="AU73" s="179"/>
-      <c r="AV73" s="224"/>
+      <c r="AV73" s="239"/>
       <c r="AW73" s="143"/>
       <c r="AX73" s="188"/>
       <c r="AY73" s="143"/>
     </row>
     <row r="74" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="196"/>
+      <c r="A74" s="194"/>
       <c r="B74" s="191"/>
       <c r="C74" s="215"/>
       <c r="D74" s="179"/>
-      <c r="E74" s="201"/>
+      <c r="E74" s="198"/>
       <c r="F74" s="120"/>
       <c r="G74" s="123"/>
       <c r="H74" s="123"/>
       <c r="I74" s="169"/>
       <c r="J74" s="179"/>
       <c r="K74" s="123"/>
-      <c r="L74" s="232"/>
+      <c r="L74" s="230"/>
       <c r="M74" s="179"/>
       <c r="N74" s="179"/>
       <c r="O74" s="14"/>
@@ -10509,13 +10509,13 @@
       <c r="AS74" s="179"/>
       <c r="AT74" s="120"/>
       <c r="AU74" s="179"/>
-      <c r="AV74" s="225"/>
+      <c r="AV74" s="240"/>
       <c r="AW74" s="143"/>
       <c r="AX74" s="188"/>
       <c r="AY74" s="143"/>
     </row>
     <row r="75" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="196"/>
+      <c r="A75" s="194"/>
       <c r="B75" s="191"/>
       <c r="C75" s="215"/>
       <c r="D75" s="179"/>
@@ -10562,13 +10562,13 @@
       <c r="AS75" s="179"/>
       <c r="AT75" s="120"/>
       <c r="AU75" s="179"/>
-      <c r="AV75" s="225"/>
+      <c r="AV75" s="240"/>
       <c r="AW75" s="143"/>
       <c r="AX75" s="188"/>
       <c r="AY75" s="143"/>
     </row>
     <row r="76" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="196"/>
+      <c r="A76" s="194"/>
       <c r="B76" s="191"/>
       <c r="C76" s="215"/>
       <c r="D76" s="179"/>
@@ -10578,7 +10578,7 @@
       <c r="H76" s="123"/>
       <c r="I76" s="120"/>
       <c r="J76" s="179"/>
-      <c r="K76" s="256"/>
+      <c r="K76" s="258"/>
       <c r="L76" s="179"/>
       <c r="M76" s="123"/>
       <c r="N76" s="179"/>
@@ -10615,13 +10615,13 @@
       <c r="AS76" s="120"/>
       <c r="AT76" s="120"/>
       <c r="AU76" s="120"/>
-      <c r="AV76" s="225"/>
+      <c r="AV76" s="240"/>
       <c r="AW76" s="120"/>
       <c r="AX76" s="120"/>
       <c r="AY76" s="120"/>
     </row>
     <row r="77" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="196"/>
+      <c r="A77" s="194"/>
       <c r="B77" s="191"/>
       <c r="C77" s="215"/>
       <c r="D77" s="179"/>
@@ -10668,13 +10668,13 @@
       <c r="AS77" s="131"/>
       <c r="AT77" s="120"/>
       <c r="AU77" s="120"/>
-      <c r="AV77" s="225"/>
+      <c r="AV77" s="240"/>
       <c r="AW77" s="120"/>
       <c r="AX77" s="120"/>
       <c r="AY77" s="120"/>
     </row>
     <row r="78" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="196"/>
+      <c r="A78" s="194"/>
       <c r="B78" s="191"/>
       <c r="C78" s="215"/>
       <c r="D78" s="179"/>
@@ -10721,14 +10721,14 @@
       <c r="AS78" s="120"/>
       <c r="AT78" s="120"/>
       <c r="AU78" s="120"/>
-      <c r="AV78" s="225"/>
+      <c r="AV78" s="240"/>
       <c r="AW78" s="120"/>
       <c r="AX78" s="120"/>
       <c r="AY78" s="120"/>
     </row>
     <row r="79" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="196"/>
-      <c r="B79" s="192"/>
+      <c r="A79" s="194"/>
+      <c r="B79" s="212"/>
       <c r="C79" s="216"/>
       <c r="D79" s="184"/>
       <c r="E79" s="184"/>
@@ -10780,8 +10780,8 @@
       <c r="AY79" s="132"/>
     </row>
     <row r="80" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="196"/>
-      <c r="B80" s="190">
+      <c r="A80" s="194"/>
+      <c r="B80" s="211">
         <v>4</v>
       </c>
       <c r="C80" s="164" t="s">
@@ -10931,7 +10931,7 @@
       </c>
     </row>
     <row r="81" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="196"/>
+      <c r="A81" s="194"/>
       <c r="B81" s="191"/>
       <c r="C81" s="164" t="s">
         <v>493</v>
@@ -10939,7 +10939,7 @@
       <c r="D81" s="168" t="s">
         <v>494</v>
       </c>
-      <c r="E81" s="198"/>
+      <c r="E81" s="189"/>
       <c r="F81" s="168" t="s">
         <v>495</v>
       </c>
@@ -11029,14 +11029,14 @@
       <c r="AV81" s="119" t="s">
         <v>513</v>
       </c>
-      <c r="AW81" s="233"/>
+      <c r="AW81" s="231"/>
       <c r="AX81" s="120" t="s">
         <v>514</v>
       </c>
-      <c r="AY81" s="233"/>
+      <c r="AY81" s="231"/>
     </row>
     <row r="82" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="196"/>
+      <c r="A82" s="194"/>
       <c r="B82" s="191"/>
       <c r="C82" s="164" t="s">
         <v>515</v>
@@ -11046,11 +11046,11 @@
       </c>
       <c r="E82" s="179"/>
       <c r="F82" s="168" t="s">
-        <v>516</v>
+        <v>1119</v>
       </c>
       <c r="G82" s="120"/>
       <c r="H82" s="119" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I82" s="119"/>
       <c r="J82" s="20"/>
@@ -11060,14 +11060,14 @@
       <c r="N82" s="179"/>
       <c r="O82" s="178"/>
       <c r="P82" s="179"/>
-      <c r="Q82" s="198"/>
+      <c r="Q82" s="189"/>
       <c r="R82" s="134"/>
       <c r="S82" s="179"/>
       <c r="T82" s="120"/>
       <c r="U82" s="178"/>
       <c r="V82" s="179"/>
       <c r="W82" s="119" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="X82" s="120"/>
       <c r="Y82" s="180"/>
@@ -11089,22 +11089,22 @@
       <c r="AO82" s="141"/>
       <c r="AP82" s="120"/>
       <c r="AQ82" s="120" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AR82" s="179"/>
       <c r="AS82" s="120"/>
       <c r="AT82" s="120"/>
       <c r="AU82" s="120"/>
-      <c r="AV82" s="224"/>
-      <c r="AW82" s="211"/>
+      <c r="AV82" s="239"/>
+      <c r="AW82" s="209"/>
       <c r="AX82" s="120"/>
-      <c r="AY82" s="211"/>
+      <c r="AY82" s="209"/>
     </row>
     <row r="83" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="196"/>
+      <c r="A83" s="194"/>
       <c r="B83" s="191"/>
-      <c r="C83" s="207"/>
-      <c r="D83" s="274"/>
+      <c r="C83" s="205"/>
+      <c r="D83" s="273"/>
       <c r="E83" s="179"/>
       <c r="F83" s="122"/>
       <c r="G83" s="120"/>
@@ -11148,16 +11148,16 @@
       <c r="AS83" s="120"/>
       <c r="AT83" s="120"/>
       <c r="AU83" s="120"/>
-      <c r="AV83" s="225"/>
-      <c r="AW83" s="211"/>
-      <c r="AX83" s="251"/>
-      <c r="AY83" s="211"/>
+      <c r="AV83" s="240"/>
+      <c r="AW83" s="209"/>
+      <c r="AX83" s="250"/>
+      <c r="AY83" s="209"/>
     </row>
     <row r="84" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="196"/>
+      <c r="A84" s="194"/>
       <c r="B84" s="191"/>
-      <c r="C84" s="208"/>
-      <c r="D84" s="211"/>
+      <c r="C84" s="206"/>
+      <c r="D84" s="209"/>
       <c r="E84" s="179"/>
       <c r="F84" s="123"/>
       <c r="G84" s="120"/>
@@ -11201,16 +11201,16 @@
       <c r="AS84" s="120"/>
       <c r="AT84" s="120"/>
       <c r="AU84" s="120"/>
-      <c r="AV84" s="225"/>
-      <c r="AW84" s="211"/>
+      <c r="AV84" s="240"/>
+      <c r="AW84" s="209"/>
       <c r="AX84" s="186"/>
-      <c r="AY84" s="211"/>
+      <c r="AY84" s="209"/>
     </row>
     <row r="85" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="196"/>
+      <c r="A85" s="194"/>
       <c r="B85" s="191"/>
-      <c r="C85" s="208"/>
-      <c r="D85" s="211"/>
+      <c r="C85" s="206"/>
+      <c r="D85" s="209"/>
       <c r="E85" s="179"/>
       <c r="F85" s="123"/>
       <c r="G85" s="120"/>
@@ -11254,16 +11254,16 @@
       <c r="AS85" s="120"/>
       <c r="AT85" s="120"/>
       <c r="AU85" s="120"/>
-      <c r="AV85" s="225"/>
+      <c r="AV85" s="240"/>
       <c r="AW85" s="120"/>
       <c r="AX85" s="186"/>
       <c r="AY85" s="120"/>
     </row>
     <row r="86" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="196"/>
+      <c r="A86" s="194"/>
       <c r="B86" s="191"/>
-      <c r="C86" s="208"/>
-      <c r="D86" s="211"/>
+      <c r="C86" s="206"/>
+      <c r="D86" s="209"/>
       <c r="E86" s="179"/>
       <c r="F86" s="123"/>
       <c r="G86" s="120"/>
@@ -11302,21 +11302,21 @@
       <c r="AN86" s="120"/>
       <c r="AO86" s="131"/>
       <c r="AP86" s="179"/>
-      <c r="AQ86" s="189"/>
+      <c r="AQ86" s="202"/>
       <c r="AR86" s="131"/>
       <c r="AS86" s="120"/>
       <c r="AT86" s="120"/>
       <c r="AU86" s="120"/>
-      <c r="AV86" s="225"/>
+      <c r="AV86" s="240"/>
       <c r="AW86" s="137"/>
       <c r="AX86" s="186"/>
       <c r="AY86" s="137"/>
     </row>
     <row r="87" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="196"/>
+      <c r="A87" s="194"/>
       <c r="B87" s="191"/>
-      <c r="C87" s="208"/>
-      <c r="D87" s="211"/>
+      <c r="C87" s="206"/>
+      <c r="D87" s="209"/>
       <c r="E87" s="179"/>
       <c r="F87" s="123"/>
       <c r="G87" s="120"/>
@@ -11360,16 +11360,16 @@
       <c r="AS87" s="120"/>
       <c r="AT87" s="120"/>
       <c r="AU87" s="120"/>
-      <c r="AV87" s="225"/>
+      <c r="AV87" s="240"/>
       <c r="AW87" s="143"/>
       <c r="AX87" s="186"/>
       <c r="AY87" s="143"/>
     </row>
     <row r="88" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="196"/>
-      <c r="B88" s="192"/>
-      <c r="C88" s="209"/>
-      <c r="D88" s="212"/>
+      <c r="A88" s="194"/>
+      <c r="B88" s="212"/>
+      <c r="C88" s="207"/>
+      <c r="D88" s="210"/>
       <c r="E88" s="184"/>
       <c r="F88" s="154"/>
       <c r="G88" s="139"/>
@@ -11419,37 +11419,37 @@
       <c r="AY88" s="173"/>
     </row>
     <row r="89" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="196"/>
-      <c r="B89" s="190">
+      <c r="A89" s="194"/>
+      <c r="B89" s="211">
         <v>5</v>
       </c>
-      <c r="C89" s="266"/>
-      <c r="D89" s="198"/>
+      <c r="C89" s="267"/>
+      <c r="D89" s="189"/>
       <c r="E89" s="133" t="s">
+        <v>519</v>
+      </c>
+      <c r="F89" s="133" t="s">
         <v>520</v>
-      </c>
-      <c r="F89" s="133" t="s">
-        <v>521</v>
       </c>
       <c r="G89" s="122"/>
       <c r="H89" s="119"/>
       <c r="I89" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="J89" s="151" t="s">
         <v>522</v>
       </c>
-      <c r="J89" s="151" t="s">
+      <c r="K89" s="119" t="s">
         <v>523</v>
       </c>
-      <c r="K89" s="119" t="s">
+      <c r="L89" s="119" t="s">
         <v>524</v>
       </c>
-      <c r="L89" s="119" t="s">
+      <c r="M89" s="119" t="s">
         <v>525</v>
       </c>
-      <c r="M89" s="119" t="s">
+      <c r="N89" s="152" t="s">
         <v>526</v>
-      </c>
-      <c r="N89" s="152" t="s">
-        <v>527</v>
       </c>
       <c r="O89" s="134" t="s">
         <v>409</v>
@@ -11460,77 +11460,77 @@
       <c r="S89" s="178"/>
       <c r="T89" s="178"/>
       <c r="U89" s="120" t="s">
+        <v>527</v>
+      </c>
+      <c r="V89" s="119" t="s">
         <v>528</v>
       </c>
-      <c r="V89" s="119" t="s">
+      <c r="W89" s="119" t="s">
         <v>529</v>
-      </c>
-      <c r="W89" s="119" t="s">
-        <v>530</v>
       </c>
       <c r="X89" s="119"/>
       <c r="Y89" s="119" t="s">
+        <v>530</v>
+      </c>
+      <c r="Z89" s="120"/>
+      <c r="AA89" s="189"/>
+      <c r="AB89" s="119" t="s">
         <v>531</v>
-      </c>
-      <c r="Z89" s="120"/>
-      <c r="AA89" s="198"/>
-      <c r="AB89" s="119" t="s">
-        <v>532</v>
       </c>
       <c r="AC89" s="119" t="s">
         <v>480</v>
       </c>
       <c r="AD89" s="119" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AE89" s="178"/>
       <c r="AF89" s="119"/>
       <c r="AG89" s="119"/>
       <c r="AH89" s="119" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AI89" s="119" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AJ89" s="178"/>
       <c r="AK89" s="140" t="s">
+        <v>534</v>
+      </c>
+      <c r="AL89" s="119" t="s">
         <v>535</v>
       </c>
-      <c r="AL89" s="119" t="s">
+      <c r="AM89" s="141" t="s">
         <v>536</v>
       </c>
-      <c r="AM89" s="141" t="s">
+      <c r="AN89" s="119" t="s">
         <v>537</v>
       </c>
-      <c r="AN89" s="119" t="s">
+      <c r="AO89" s="141" t="s">
         <v>538</v>
       </c>
-      <c r="AO89" s="141" t="s">
+      <c r="AP89" s="120" t="s">
         <v>539</v>
-      </c>
-      <c r="AP89" s="120" t="s">
-        <v>540</v>
       </c>
       <c r="AQ89" s="119" t="s">
         <v>133</v>
       </c>
       <c r="AR89" s="141"/>
-      <c r="AS89" s="233"/>
+      <c r="AS89" s="231"/>
       <c r="AT89" s="120"/>
-      <c r="AU89" s="224"/>
+      <c r="AU89" s="239"/>
       <c r="AV89" s="185"/>
-      <c r="AW89" s="233"/>
+      <c r="AW89" s="231"/>
       <c r="AX89" s="120" t="s">
         <v>95</v>
       </c>
       <c r="AY89" s="134"/>
     </row>
     <row r="90" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="196"/>
+      <c r="A90" s="194"/>
       <c r="B90" s="191"/>
       <c r="C90" s="215"/>
       <c r="D90" s="179"/>
-      <c r="E90" s="198"/>
+      <c r="E90" s="189"/>
       <c r="F90" s="133" t="s">
         <v>294</v>
       </c>
@@ -11538,12 +11538,12 @@
       <c r="H90" s="120"/>
       <c r="I90" s="119"/>
       <c r="J90" s="151" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K90" s="178"/>
       <c r="L90" s="178"/>
       <c r="M90" s="178"/>
-      <c r="N90" s="261"/>
+      <c r="N90" s="272"/>
       <c r="O90" s="134"/>
       <c r="P90" s="179"/>
       <c r="Q90" s="179"/>
@@ -11552,7 +11552,7 @@
       <c r="T90" s="179"/>
       <c r="U90" s="120"/>
       <c r="V90" s="119" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="W90" s="119"/>
       <c r="X90" s="120"/>
@@ -11560,44 +11560,44 @@
       <c r="Z90" s="120"/>
       <c r="AA90" s="179"/>
       <c r="AB90" s="119" t="s">
-        <v>543</v>
-      </c>
-      <c r="AC90" s="198"/>
+        <v>542</v>
+      </c>
+      <c r="AC90" s="189"/>
       <c r="AD90" s="178"/>
       <c r="AE90" s="179"/>
       <c r="AF90" s="120"/>
       <c r="AG90" s="120"/>
       <c r="AH90" s="119" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AI90" s="119" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AJ90" s="179"/>
       <c r="AK90" s="140" t="s">
+        <v>544</v>
+      </c>
+      <c r="AL90" s="119" t="s">
         <v>545</v>
-      </c>
-      <c r="AL90" s="119" t="s">
-        <v>546</v>
       </c>
       <c r="AM90" s="141"/>
       <c r="AN90" s="178"/>
       <c r="AO90" s="141"/>
       <c r="AP90" s="120"/>
       <c r="AQ90" s="119" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AR90" s="141"/>
-      <c r="AS90" s="211"/>
+      <c r="AS90" s="209"/>
       <c r="AT90" s="120"/>
-      <c r="AU90" s="225"/>
+      <c r="AU90" s="240"/>
       <c r="AV90" s="186"/>
-      <c r="AW90" s="211"/>
+      <c r="AW90" s="209"/>
       <c r="AX90" s="120"/>
       <c r="AY90" s="134"/>
     </row>
     <row r="91" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="196"/>
+      <c r="A91" s="194"/>
       <c r="B91" s="191"/>
       <c r="C91" s="215"/>
       <c r="D91" s="179"/>
@@ -11625,7 +11625,7 @@
       <c r="Z91" s="120"/>
       <c r="AA91" s="179"/>
       <c r="AB91" s="119" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AC91" s="179"/>
       <c r="AD91" s="179"/>
@@ -11643,16 +11643,16 @@
       <c r="AP91" s="120"/>
       <c r="AQ91" s="178"/>
       <c r="AR91" s="141"/>
-      <c r="AS91" s="211"/>
+      <c r="AS91" s="209"/>
       <c r="AT91" s="120"/>
-      <c r="AU91" s="225"/>
+      <c r="AU91" s="240"/>
       <c r="AV91" s="186"/>
-      <c r="AW91" s="211"/>
+      <c r="AW91" s="209"/>
       <c r="AX91" s="120"/>
       <c r="AY91" s="134"/>
     </row>
     <row r="92" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="196"/>
+      <c r="A92" s="194"/>
       <c r="B92" s="191"/>
       <c r="C92" s="215"/>
       <c r="D92" s="179"/>
@@ -11696,16 +11696,16 @@
       <c r="AP92" s="120"/>
       <c r="AQ92" s="179"/>
       <c r="AR92" s="141"/>
-      <c r="AS92" s="211"/>
+      <c r="AS92" s="209"/>
       <c r="AT92" s="120"/>
-      <c r="AU92" s="225"/>
+      <c r="AU92" s="240"/>
       <c r="AV92" s="186"/>
-      <c r="AW92" s="211"/>
+      <c r="AW92" s="209"/>
       <c r="AX92" s="120"/>
       <c r="AY92" s="134"/>
     </row>
     <row r="93" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="196"/>
+      <c r="A93" s="194"/>
       <c r="B93" s="191"/>
       <c r="C93" s="215"/>
       <c r="D93" s="179"/>
@@ -11732,7 +11732,7 @@
       <c r="Y93" s="120"/>
       <c r="Z93" s="123"/>
       <c r="AA93" s="179"/>
-      <c r="AB93" s="189"/>
+      <c r="AB93" s="202"/>
       <c r="AC93" s="179"/>
       <c r="AD93" s="121"/>
       <c r="AE93" s="123"/>
@@ -11749,16 +11749,16 @@
       <c r="AP93" s="120"/>
       <c r="AQ93" s="179"/>
       <c r="AR93" s="131"/>
-      <c r="AS93" s="211"/>
+      <c r="AS93" s="209"/>
       <c r="AT93" s="131"/>
-      <c r="AU93" s="225"/>
+      <c r="AU93" s="240"/>
       <c r="AV93" s="186"/>
-      <c r="AW93" s="211"/>
+      <c r="AW93" s="209"/>
       <c r="AX93" s="120"/>
       <c r="AY93" s="39"/>
     </row>
     <row r="94" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="196"/>
+      <c r="A94" s="194"/>
       <c r="B94" s="191"/>
       <c r="C94" s="215"/>
       <c r="D94" s="179"/>
@@ -11811,7 +11811,7 @@
       <c r="AY94" s="146"/>
     </row>
     <row r="95" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="196"/>
+      <c r="A95" s="194"/>
       <c r="B95" s="191"/>
       <c r="C95" s="215"/>
       <c r="D95" s="179"/>
@@ -11864,8 +11864,8 @@
       <c r="AY95" s="146"/>
     </row>
     <row r="96" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="196"/>
-      <c r="B96" s="192"/>
+      <c r="A96" s="194"/>
+      <c r="B96" s="212"/>
       <c r="C96" s="216"/>
       <c r="D96" s="184"/>
       <c r="E96" s="184"/>
@@ -11917,14 +11917,14 @@
       <c r="AY96" s="39"/>
     </row>
     <row r="97" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="196"/>
-      <c r="B97" s="190">
+      <c r="A97" s="194"/>
+      <c r="B97" s="211">
         <v>6</v>
       </c>
-      <c r="C97" s="240"/>
-      <c r="D97" s="229"/>
-      <c r="E97" s="210"/>
-      <c r="F97" s="198"/>
+      <c r="C97" s="238"/>
+      <c r="D97" s="227"/>
+      <c r="E97" s="208"/>
+      <c r="F97" s="189"/>
       <c r="G97" s="119"/>
       <c r="H97" s="119"/>
       <c r="I97" s="119"/>
@@ -11938,9 +11938,9 @@
       <c r="Q97" s="178"/>
       <c r="R97" s="178"/>
       <c r="S97" s="178"/>
-      <c r="T97" s="264"/>
-      <c r="U97" s="264"/>
-      <c r="V97" s="265"/>
+      <c r="T97" s="265"/>
+      <c r="U97" s="265"/>
+      <c r="V97" s="266"/>
       <c r="W97" s="119"/>
       <c r="X97" s="119"/>
       <c r="Y97" s="120"/>
@@ -11957,30 +11957,30 @@
       <c r="AJ97" s="178"/>
       <c r="AK97" s="178"/>
       <c r="AL97" s="119" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AM97" s="178"/>
       <c r="AN97" s="141"/>
       <c r="AO97" s="178"/>
       <c r="AP97" s="178"/>
       <c r="AQ97" s="120" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AR97" s="141"/>
       <c r="AS97" s="178"/>
       <c r="AT97" s="178"/>
-      <c r="AU97" s="233"/>
+      <c r="AU97" s="231"/>
       <c r="AV97" s="178"/>
       <c r="AW97" s="178"/>
       <c r="AX97" s="187"/>
-      <c r="AY97" s="245"/>
+      <c r="AY97" s="246"/>
     </row>
     <row r="98" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="196"/>
+      <c r="A98" s="194"/>
       <c r="B98" s="191"/>
-      <c r="C98" s="208"/>
+      <c r="C98" s="206"/>
       <c r="D98" s="186"/>
-      <c r="E98" s="211"/>
+      <c r="E98" s="209"/>
       <c r="F98" s="179"/>
       <c r="G98" s="120"/>
       <c r="H98" s="120"/>
@@ -11994,10 +11994,10 @@
       <c r="P98" s="179"/>
       <c r="Q98" s="179"/>
       <c r="R98" s="179"/>
-      <c r="S98" s="225"/>
+      <c r="S98" s="240"/>
       <c r="T98" s="186"/>
       <c r="U98" s="186"/>
-      <c r="V98" s="211"/>
+      <c r="V98" s="209"/>
       <c r="W98" s="120"/>
       <c r="X98" s="120"/>
       <c r="Y98" s="120"/>
@@ -12014,7 +12014,7 @@
       <c r="AJ98" s="179"/>
       <c r="AK98" s="179"/>
       <c r="AL98" s="119" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AM98" s="179"/>
       <c r="AN98" s="141"/>
@@ -12024,18 +12024,18 @@
       <c r="AR98" s="141"/>
       <c r="AS98" s="179"/>
       <c r="AT98" s="179"/>
-      <c r="AU98" s="211"/>
+      <c r="AU98" s="209"/>
       <c r="AV98" s="179"/>
       <c r="AW98" s="179"/>
       <c r="AX98" s="188"/>
-      <c r="AY98" s="246"/>
+      <c r="AY98" s="247"/>
     </row>
     <row r="99" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="196"/>
+      <c r="A99" s="194"/>
       <c r="B99" s="191"/>
-      <c r="C99" s="208"/>
+      <c r="C99" s="206"/>
       <c r="D99" s="186"/>
-      <c r="E99" s="211"/>
+      <c r="E99" s="209"/>
       <c r="F99" s="179"/>
       <c r="G99" s="120"/>
       <c r="H99" s="141"/>
@@ -12049,10 +12049,10 @@
       <c r="P99" s="141"/>
       <c r="Q99" s="179"/>
       <c r="R99" s="179"/>
-      <c r="S99" s="225"/>
+      <c r="S99" s="240"/>
       <c r="T99" s="186"/>
       <c r="U99" s="186"/>
-      <c r="V99" s="211"/>
+      <c r="V99" s="209"/>
       <c r="W99" s="120"/>
       <c r="X99" s="120"/>
       <c r="Y99" s="148"/>
@@ -12077,18 +12077,18 @@
       <c r="AR99" s="120"/>
       <c r="AS99" s="179"/>
       <c r="AT99" s="179"/>
-      <c r="AU99" s="211"/>
+      <c r="AU99" s="209"/>
       <c r="AV99" s="137"/>
       <c r="AW99" s="120"/>
       <c r="AX99" s="188"/>
-      <c r="AY99" s="246"/>
+      <c r="AY99" s="247"/>
     </row>
     <row r="100" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="196"/>
+      <c r="A100" s="194"/>
       <c r="B100" s="191"/>
-      <c r="C100" s="208"/>
+      <c r="C100" s="206"/>
       <c r="D100" s="186"/>
-      <c r="E100" s="211"/>
+      <c r="E100" s="209"/>
       <c r="F100" s="179"/>
       <c r="G100" s="120"/>
       <c r="H100" s="141"/>
@@ -12102,10 +12102,10 @@
       <c r="P100" s="141"/>
       <c r="Q100" s="120"/>
       <c r="R100" s="141"/>
-      <c r="S100" s="225"/>
+      <c r="S100" s="240"/>
       <c r="T100" s="186"/>
       <c r="U100" s="186"/>
-      <c r="V100" s="211"/>
+      <c r="V100" s="209"/>
       <c r="W100" s="120"/>
       <c r="X100" s="141"/>
       <c r="Y100" s="120"/>
@@ -12130,18 +12130,18 @@
       <c r="AR100" s="120"/>
       <c r="AS100" s="137"/>
       <c r="AT100" s="137"/>
-      <c r="AU100" s="211"/>
+      <c r="AU100" s="209"/>
       <c r="AV100" s="137"/>
       <c r="AW100" s="120"/>
       <c r="AX100" s="146"/>
       <c r="AY100" s="146"/>
     </row>
     <row r="101" spans="1:51" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="196"/>
+      <c r="A101" s="194"/>
       <c r="B101" s="191"/>
-      <c r="C101" s="208"/>
+      <c r="C101" s="206"/>
       <c r="D101" s="186"/>
-      <c r="E101" s="211"/>
+      <c r="E101" s="209"/>
       <c r="F101" s="179"/>
       <c r="G101" s="120"/>
       <c r="H101" s="141"/>
@@ -12155,10 +12155,10 @@
       <c r="P101" s="141"/>
       <c r="Q101" s="120"/>
       <c r="R101" s="141"/>
-      <c r="S101" s="225"/>
+      <c r="S101" s="240"/>
       <c r="T101" s="186"/>
       <c r="U101" s="186"/>
-      <c r="V101" s="211"/>
+      <c r="V101" s="209"/>
       <c r="W101" s="120"/>
       <c r="X101" s="141"/>
       <c r="Y101" s="120"/>
@@ -12190,11 +12190,11 @@
       <c r="AY101" s="146"/>
     </row>
     <row r="102" spans="1:51" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="196"/>
-      <c r="B102" s="192"/>
-      <c r="C102" s="209"/>
-      <c r="D102" s="230"/>
-      <c r="E102" s="212"/>
+      <c r="A102" s="194"/>
+      <c r="B102" s="212"/>
+      <c r="C102" s="207"/>
+      <c r="D102" s="228"/>
+      <c r="E102" s="210"/>
       <c r="F102" s="184"/>
       <c r="G102" s="139"/>
       <c r="H102" s="167"/>
@@ -12243,11 +12243,11 @@
       <c r="AY102" s="62"/>
     </row>
     <row r="103" spans="1:51" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="196"/>
-      <c r="B103" s="193">
+      <c r="A103" s="194"/>
+      <c r="B103" s="190">
         <v>7</v>
       </c>
-      <c r="C103" s="236"/>
+      <c r="C103" s="234"/>
       <c r="D103" s="119"/>
       <c r="E103" s="140"/>
       <c r="F103" s="119"/>
@@ -12298,7 +12298,7 @@
       <c r="AY103" s="145"/>
     </row>
     <row r="104" spans="1:51" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="196"/>
+      <c r="A104" s="194"/>
       <c r="B104" s="191"/>
       <c r="C104" s="215"/>
       <c r="D104" s="120"/>
@@ -12351,7 +12351,7 @@
       <c r="AY104" s="146"/>
     </row>
     <row r="105" spans="1:51" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="196"/>
+      <c r="A105" s="194"/>
       <c r="B105" s="191"/>
       <c r="C105" s="215"/>
       <c r="D105" s="120"/>
@@ -12404,7 +12404,7 @@
       <c r="AY105" s="146"/>
     </row>
     <row r="106" spans="1:51" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="196"/>
+      <c r="A106" s="194"/>
       <c r="B106" s="191"/>
       <c r="C106" s="215"/>
       <c r="D106" s="120"/>
@@ -12457,9 +12457,9 @@
       <c r="AY106" s="146"/>
     </row>
     <row r="107" spans="1:51" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="206"/>
-      <c r="B107" s="194"/>
-      <c r="C107" s="237"/>
+      <c r="A107" s="204"/>
+      <c r="B107" s="192"/>
+      <c r="C107" s="235"/>
       <c r="D107" s="171"/>
       <c r="E107" s="63"/>
       <c r="F107" s="171"/>
@@ -12510,10 +12510,10 @@
       <c r="AY107" s="67"/>
     </row>
     <row r="108" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="205" t="s">
-        <v>552</v>
-      </c>
-      <c r="B108" s="231">
+      <c r="A108" s="203" t="s">
+        <v>551</v>
+      </c>
+      <c r="B108" s="229">
         <v>1</v>
       </c>
       <c r="C108" s="159" t="s">
@@ -12526,7 +12526,7 @@
         <v>59</v>
       </c>
       <c r="F108" s="123" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G108" s="122" t="s">
         <v>133</v>
@@ -12535,7 +12535,7 @@
         <v>61</v>
       </c>
       <c r="I108" s="122" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="J108" s="151" t="s">
         <v>310</v>
@@ -12547,108 +12547,108 @@
         <v>308</v>
       </c>
       <c r="M108" s="122" t="s">
+        <v>554</v>
+      </c>
+      <c r="N108" s="119" t="s">
         <v>555</v>
       </c>
-      <c r="N108" s="119" t="s">
+      <c r="O108" s="134" t="s">
         <v>556</v>
-      </c>
-      <c r="O108" s="134" t="s">
-        <v>557</v>
       </c>
       <c r="P108" s="119" t="s">
         <v>56</v>
       </c>
       <c r="Q108" s="119" t="s">
+        <v>557</v>
+      </c>
+      <c r="R108" s="120" t="s">
         <v>558</v>
       </c>
-      <c r="R108" s="120" t="s">
+      <c r="S108" s="119" t="s">
         <v>559</v>
       </c>
-      <c r="S108" s="119" t="s">
+      <c r="T108" s="120" t="s">
         <v>560</v>
       </c>
-      <c r="T108" s="120" t="s">
+      <c r="U108" s="120" t="s">
         <v>561</v>
-      </c>
-      <c r="U108" s="120" t="s">
-        <v>562</v>
       </c>
       <c r="V108" s="124" t="s">
         <v>126</v>
       </c>
       <c r="W108" s="30" t="s">
+        <v>562</v>
+      </c>
+      <c r="X108" s="119" t="s">
         <v>563</v>
       </c>
-      <c r="X108" s="119" t="s">
+      <c r="Y108" s="120" t="s">
         <v>564</v>
       </c>
-      <c r="Y108" s="120" t="s">
+      <c r="Z108" s="119" t="s">
         <v>565</v>
       </c>
-      <c r="Z108" s="119" t="s">
+      <c r="AA108" s="119" t="s">
         <v>566</v>
       </c>
-      <c r="AA108" s="119" t="s">
+      <c r="AB108" s="119" t="s">
         <v>567</v>
-      </c>
-      <c r="AB108" s="119" t="s">
-        <v>568</v>
       </c>
       <c r="AC108" s="119" t="s">
         <v>79</v>
       </c>
       <c r="AD108" s="120" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AE108" s="119" t="s">
         <v>373</v>
       </c>
       <c r="AF108" s="177" t="s">
+        <v>569</v>
+      </c>
+      <c r="AG108" s="119" t="s">
         <v>570</v>
       </c>
-      <c r="AG108" s="119" t="s">
+      <c r="AH108" s="119" t="s">
         <v>571</v>
       </c>
-      <c r="AH108" s="119" t="s">
+      <c r="AI108" s="119" t="s">
+        <v>571</v>
+      </c>
+      <c r="AJ108" s="124" t="s">
         <v>572</v>
       </c>
-      <c r="AI108" s="119" t="s">
-        <v>572</v>
-      </c>
-      <c r="AJ108" s="124" t="s">
+      <c r="AK108" s="140" t="s">
         <v>573</v>
-      </c>
-      <c r="AK108" s="140" t="s">
-        <v>574</v>
       </c>
       <c r="AL108" s="182"/>
       <c r="AM108" s="119" t="s">
+        <v>574</v>
+      </c>
+      <c r="AN108" s="124" t="s">
         <v>575</v>
       </c>
-      <c r="AN108" s="124" t="s">
+      <c r="AO108" s="124" t="s">
         <v>576</v>
       </c>
-      <c r="AO108" s="124" t="s">
+      <c r="AP108" s="141" t="s">
         <v>577</v>
-      </c>
-      <c r="AP108" s="141" t="s">
-        <v>578</v>
       </c>
       <c r="AQ108" s="182"/>
       <c r="AR108" s="119" t="s">
+        <v>578</v>
+      </c>
+      <c r="AS108" s="119" t="s">
         <v>579</v>
       </c>
-      <c r="AS108" s="119" t="s">
+      <c r="AT108" s="137" t="s">
         <v>580</v>
       </c>
-      <c r="AT108" s="137" t="s">
+      <c r="AU108" s="124" t="s">
         <v>581</v>
       </c>
-      <c r="AU108" s="124" t="s">
+      <c r="AV108" s="137" t="s">
         <v>582</v>
-      </c>
-      <c r="AV108" s="137" t="s">
-        <v>583</v>
       </c>
       <c r="AW108" s="120" t="s">
         <v>97</v>
@@ -12659,98 +12659,98 @@
       </c>
     </row>
     <row r="109" spans="1:51" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="196"/>
+      <c r="A109" s="194"/>
       <c r="B109" s="191"/>
-      <c r="C109" s="226"/>
+      <c r="C109" s="224"/>
       <c r="D109" s="119" t="s">
+        <v>583</v>
+      </c>
+      <c r="E109" s="189"/>
+      <c r="F109" s="123" t="s">
         <v>584</v>
       </c>
-      <c r="E109" s="198"/>
-      <c r="F109" s="123" t="s">
+      <c r="G109" s="122" t="s">
         <v>585</v>
-      </c>
-      <c r="G109" s="122" t="s">
-        <v>586</v>
       </c>
       <c r="H109" s="174"/>
       <c r="I109" s="122" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J109" s="151"/>
       <c r="K109" s="181"/>
       <c r="L109" s="169"/>
       <c r="M109" s="181"/>
       <c r="N109" s="119" t="s">
+        <v>587</v>
+      </c>
+      <c r="O109" s="134" t="s">
         <v>588</v>
-      </c>
-      <c r="O109" s="134" t="s">
-        <v>589</v>
       </c>
       <c r="P109" s="178"/>
       <c r="Q109" s="119" t="s">
+        <v>589</v>
+      </c>
+      <c r="R109" s="120" t="s">
         <v>590</v>
-      </c>
-      <c r="R109" s="120" t="s">
-        <v>591</v>
       </c>
       <c r="S109" s="178"/>
       <c r="T109" s="120"/>
       <c r="U109" s="120"/>
       <c r="V109" s="182"/>
       <c r="W109" s="30" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="X109" s="119"/>
       <c r="Y109" s="120" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Z109" s="119"/>
       <c r="AA109" s="178"/>
       <c r="AB109" s="178"/>
       <c r="AC109" s="178"/>
       <c r="AD109" s="120" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AE109" s="178"/>
       <c r="AF109" s="177"/>
       <c r="AG109" s="119" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AH109" s="178"/>
       <c r="AI109" s="178"/>
       <c r="AJ109" s="124" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AK109" s="178"/>
       <c r="AL109" s="179"/>
       <c r="AM109" s="178"/>
       <c r="AN109" s="124" t="s">
+        <v>596</v>
+      </c>
+      <c r="AO109" s="124" t="s">
         <v>597</v>
-      </c>
-      <c r="AO109" s="124" t="s">
-        <v>598</v>
       </c>
       <c r="AP109" s="141"/>
       <c r="AQ109" s="179"/>
       <c r="AR109" s="178"/>
       <c r="AS109" s="178"/>
       <c r="AT109" s="137" t="s">
+        <v>598</v>
+      </c>
+      <c r="AU109" s="251"/>
+      <c r="AV109" s="137" t="s">
         <v>599</v>
-      </c>
-      <c r="AU109" s="252"/>
-      <c r="AV109" s="137" t="s">
-        <v>600</v>
       </c>
       <c r="AW109" s="120"/>
       <c r="AX109" s="146"/>
       <c r="AY109" s="120"/>
     </row>
     <row r="110" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="196"/>
+      <c r="A110" s="194"/>
       <c r="B110" s="191"/>
       <c r="C110" s="215"/>
       <c r="D110" s="119" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E110" s="179"/>
       <c r="F110" s="123"/>
@@ -12794,17 +12794,17 @@
       <c r="AR110" s="179"/>
       <c r="AS110" s="179"/>
       <c r="AT110" s="137"/>
-      <c r="AU110" s="211"/>
+      <c r="AU110" s="209"/>
       <c r="AV110" s="137"/>
       <c r="AW110" s="120"/>
       <c r="AX110" s="146"/>
       <c r="AY110" s="120"/>
     </row>
     <row r="111" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="196"/>
+      <c r="A111" s="194"/>
       <c r="B111" s="191"/>
       <c r="C111" s="215"/>
-      <c r="D111" s="198"/>
+      <c r="D111" s="189"/>
       <c r="E111" s="179"/>
       <c r="F111" s="123"/>
       <c r="G111" s="123"/>
@@ -12847,14 +12847,14 @@
       <c r="AR111" s="179"/>
       <c r="AS111" s="179"/>
       <c r="AT111" s="137"/>
-      <c r="AU111" s="211"/>
+      <c r="AU111" s="209"/>
       <c r="AV111" s="137"/>
       <c r="AW111" s="120"/>
       <c r="AX111" s="146"/>
       <c r="AY111" s="120"/>
     </row>
     <row r="112" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="196"/>
+      <c r="A112" s="194"/>
       <c r="B112" s="191"/>
       <c r="C112" s="215"/>
       <c r="D112" s="179"/>
@@ -12900,14 +12900,14 @@
       <c r="AR112" s="120"/>
       <c r="AS112" s="120"/>
       <c r="AT112" s="180"/>
-      <c r="AU112" s="211"/>
+      <c r="AU112" s="209"/>
       <c r="AV112" s="180"/>
       <c r="AW112" s="120"/>
       <c r="AX112" s="134"/>
       <c r="AY112" s="120"/>
     </row>
     <row r="113" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="196"/>
+      <c r="A113" s="194"/>
       <c r="B113" s="191"/>
       <c r="C113" s="215"/>
       <c r="D113" s="179"/>
@@ -12953,14 +12953,14 @@
       <c r="AR113" s="120"/>
       <c r="AS113" s="131"/>
       <c r="AT113" s="179"/>
-      <c r="AU113" s="211"/>
+      <c r="AU113" s="209"/>
       <c r="AV113" s="179"/>
       <c r="AW113" s="120"/>
       <c r="AX113" s="134"/>
       <c r="AY113" s="120"/>
     </row>
     <row r="114" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="196"/>
+      <c r="A114" s="194"/>
       <c r="B114" s="191"/>
       <c r="C114" s="215"/>
       <c r="D114" s="179"/>
@@ -13013,8 +13013,8 @@
       <c r="AY114" s="120"/>
     </row>
     <row r="115" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="196"/>
-      <c r="B115" s="192"/>
+      <c r="A115" s="194"/>
+      <c r="B115" s="212"/>
       <c r="C115" s="216"/>
       <c r="D115" s="184"/>
       <c r="E115" s="184"/>
@@ -13066,12 +13066,12 @@
       <c r="AY115" s="139"/>
     </row>
     <row r="116" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="196"/>
-      <c r="B116" s="190">
+      <c r="A116" s="194"/>
+      <c r="B116" s="211">
         <v>2</v>
       </c>
       <c r="C116" s="76" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D116" s="133" t="s">
         <v>57</v>
@@ -13086,7 +13086,7 @@
         <v>61</v>
       </c>
       <c r="H116" s="123" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I116" s="119" t="s">
         <v>118</v>
@@ -13095,13 +13095,13 @@
         <v>313</v>
       </c>
       <c r="K116" s="119" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L116" s="120" t="s">
         <v>59</v>
       </c>
       <c r="M116" s="119" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="N116" s="151" t="s">
         <v>310</v>
@@ -13113,10 +13113,10 @@
         <v>120</v>
       </c>
       <c r="Q116" s="26" t="s">
+        <v>605</v>
+      </c>
+      <c r="R116" s="119" t="s">
         <v>606</v>
-      </c>
-      <c r="R116" s="119" t="s">
-        <v>607</v>
       </c>
       <c r="S116" s="140" t="s">
         <v>168</v>
@@ -13128,34 +13128,34 @@
         <v>126</v>
       </c>
       <c r="V116" s="119" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="W116" s="119" t="s">
         <v>75</v>
       </c>
       <c r="X116" s="119" t="s">
+        <v>608</v>
+      </c>
+      <c r="Y116" s="119" t="s">
         <v>609</v>
       </c>
-      <c r="Y116" s="119" t="s">
+      <c r="Z116" s="119" t="s">
         <v>610</v>
-      </c>
-      <c r="Z116" s="119" t="s">
-        <v>611</v>
       </c>
       <c r="AA116" s="119" t="s">
         <v>182</v>
       </c>
       <c r="AB116" s="119" t="s">
+        <v>611</v>
+      </c>
+      <c r="AC116" s="119" t="s">
         <v>612</v>
-      </c>
-      <c r="AC116" s="119" t="s">
-        <v>613</v>
       </c>
       <c r="AD116" s="119" t="s">
         <v>327</v>
       </c>
       <c r="AE116" s="119" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AF116" s="120" t="s">
         <v>188</v>
@@ -13164,34 +13164,34 @@
         <v>187</v>
       </c>
       <c r="AH116" s="119" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AI116" s="119" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AJ116" s="119" t="s">
         <v>191</v>
       </c>
       <c r="AK116" s="119" t="s">
+        <v>615</v>
+      </c>
+      <c r="AL116" s="120" t="s">
         <v>616</v>
       </c>
-      <c r="AL116" s="120" t="s">
+      <c r="AM116" s="120" t="s">
         <v>617</v>
       </c>
-      <c r="AM116" s="120" t="s">
+      <c r="AN116" s="119" t="s">
         <v>618</v>
       </c>
-      <c r="AN116" s="119" t="s">
+      <c r="AO116" s="141" t="s">
         <v>619</v>
       </c>
-      <c r="AO116" s="141" t="s">
+      <c r="AP116" s="119" t="s">
         <v>620</v>
       </c>
-      <c r="AP116" s="119" t="s">
+      <c r="AQ116" s="119" t="s">
         <v>621</v>
-      </c>
-      <c r="AQ116" s="119" t="s">
-        <v>622</v>
       </c>
       <c r="AR116" s="120" t="s">
         <v>334</v>
@@ -13200,7 +13200,7 @@
         <v>93</v>
       </c>
       <c r="AT116" s="119" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AU116" s="120" t="s">
         <v>201</v>
@@ -13209,67 +13209,67 @@
         <v>337</v>
       </c>
       <c r="AW116" s="142" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AX116" s="138" t="s">
         <v>203</v>
       </c>
       <c r="AY116" s="142" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="117" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="196"/>
+      <c r="A117" s="194"/>
       <c r="B117" s="191"/>
       <c r="C117" s="76" t="s">
-        <v>625</v>
-      </c>
-      <c r="D117" s="198"/>
+        <v>624</v>
+      </c>
+      <c r="D117" s="189"/>
       <c r="E117" s="169"/>
       <c r="F117" s="119"/>
       <c r="G117" s="122"/>
       <c r="H117" s="123" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I117" s="119"/>
       <c r="J117" s="181"/>
       <c r="K117" s="119" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="L117" s="120"/>
       <c r="M117" s="119" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="N117" s="217"/>
       <c r="O117" s="181"/>
       <c r="P117" s="178"/>
       <c r="Q117" s="26" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R117" s="178"/>
       <c r="S117" s="178"/>
       <c r="T117" s="119" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="U117" s="140" t="s">
         <v>162</v>
       </c>
       <c r="V117" s="119" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="W117" s="119"/>
       <c r="X117" s="119" t="s">
+        <v>630</v>
+      </c>
+      <c r="Y117" s="119" t="s">
         <v>631</v>
       </c>
-      <c r="Y117" s="119" t="s">
+      <c r="Z117" s="119" t="s">
         <v>632</v>
-      </c>
-      <c r="Z117" s="119" t="s">
-        <v>633</v>
       </c>
       <c r="AA117" s="178"/>
       <c r="AB117" s="119" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AC117" s="178"/>
       <c r="AD117" s="178"/>
@@ -13286,7 +13286,7 @@
       <c r="AO117" s="141"/>
       <c r="AP117" s="178"/>
       <c r="AQ117" s="119" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AR117" s="120"/>
       <c r="AS117" s="178"/>
@@ -13296,13 +13296,13 @@
       <c r="AW117" s="142" t="s">
         <v>392</v>
       </c>
-      <c r="AX117" s="267"/>
+      <c r="AX117" s="252"/>
       <c r="AY117" s="142" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="118" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="196"/>
+      <c r="A118" s="194"/>
       <c r="B118" s="191"/>
       <c r="C118" s="76" t="s">
         <v>269</v>
@@ -13315,7 +13315,7 @@
       <c r="I118" s="120"/>
       <c r="J118" s="179"/>
       <c r="K118" s="119" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="L118" s="120"/>
       <c r="M118" s="178"/>
@@ -13333,7 +13333,7 @@
       <c r="W118" s="120"/>
       <c r="X118" s="119"/>
       <c r="Y118" s="119" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="Z118" s="119"/>
       <c r="AA118" s="179"/>
@@ -13359,13 +13359,13 @@
       <c r="AU118" s="120"/>
       <c r="AV118" s="188"/>
       <c r="AW118" s="185"/>
-      <c r="AX118" s="268"/>
+      <c r="AX118" s="253"/>
       <c r="AY118" s="185"/>
     </row>
     <row r="119" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="196"/>
+      <c r="A119" s="194"/>
       <c r="B119" s="191"/>
-      <c r="C119" s="244"/>
+      <c r="C119" s="274"/>
       <c r="D119" s="179"/>
       <c r="E119" s="169"/>
       <c r="F119" s="120"/>
@@ -13379,7 +13379,7 @@
       <c r="N119" s="179"/>
       <c r="O119" s="179"/>
       <c r="P119" s="179"/>
-      <c r="Q119" s="199"/>
+      <c r="Q119" s="196"/>
       <c r="R119" s="179"/>
       <c r="S119" s="179"/>
       <c r="T119" s="179"/>
@@ -13412,11 +13412,11 @@
       <c r="AU119" s="120"/>
       <c r="AV119" s="188"/>
       <c r="AW119" s="186"/>
-      <c r="AX119" s="268"/>
+      <c r="AX119" s="253"/>
       <c r="AY119" s="186"/>
     </row>
     <row r="120" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="196"/>
+      <c r="A120" s="194"/>
       <c r="B120" s="191"/>
       <c r="C120" s="215"/>
       <c r="D120" s="179"/>
@@ -13465,11 +13465,11 @@
       <c r="AU120" s="120"/>
       <c r="AV120" s="188"/>
       <c r="AW120" s="186"/>
-      <c r="AX120" s="268"/>
+      <c r="AX120" s="253"/>
       <c r="AY120" s="186"/>
     </row>
     <row r="121" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="196"/>
+      <c r="A121" s="194"/>
       <c r="B121" s="191"/>
       <c r="C121" s="215"/>
       <c r="D121" s="179"/>
@@ -13522,7 +13522,7 @@
       <c r="AY121" s="186"/>
     </row>
     <row r="122" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="196"/>
+      <c r="A122" s="194"/>
       <c r="B122" s="191"/>
       <c r="C122" s="215"/>
       <c r="D122" s="179"/>
@@ -13575,7 +13575,7 @@
       <c r="AY122" s="186"/>
     </row>
     <row r="123" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="196"/>
+      <c r="A123" s="194"/>
       <c r="B123" s="191"/>
       <c r="C123" s="215"/>
       <c r="D123" s="179"/>
@@ -13628,8 +13628,8 @@
       <c r="AY123" s="186"/>
     </row>
     <row r="124" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="196"/>
-      <c r="B124" s="192"/>
+      <c r="A124" s="194"/>
+      <c r="B124" s="212"/>
       <c r="C124" s="216"/>
       <c r="D124" s="184"/>
       <c r="E124" s="157"/>
@@ -13681,7 +13681,7 @@
       <c r="AY124" s="61"/>
     </row>
     <row r="125" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="196"/>
+      <c r="A125" s="194"/>
       <c r="B125" s="213">
         <v>3</v>
       </c>
@@ -13689,7 +13689,7 @@
         <v>166</v>
       </c>
       <c r="D125" s="123" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E125" s="133" t="s">
         <v>56</v>
@@ -13704,10 +13704,10 @@
         <v>64</v>
       </c>
       <c r="I125" s="122" t="s">
+        <v>638</v>
+      </c>
+      <c r="J125" s="119" t="s">
         <v>639</v>
-      </c>
-      <c r="J125" s="119" t="s">
-        <v>640</v>
       </c>
       <c r="K125" s="133" t="s">
         <v>59</v>
@@ -13719,7 +13719,7 @@
         <v>168</v>
       </c>
       <c r="N125" s="122" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="O125" s="119" t="s">
         <v>124</v>
@@ -13728,25 +13728,25 @@
         <v>123</v>
       </c>
       <c r="Q125" s="119" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="R125" s="120" t="s">
         <v>68</v>
       </c>
       <c r="S125" s="133" t="s">
+        <v>642</v>
+      </c>
+      <c r="T125" s="140" t="s">
         <v>643</v>
-      </c>
-      <c r="T125" s="140" t="s">
-        <v>644</v>
       </c>
       <c r="U125" s="120" t="s">
         <v>127</v>
       </c>
       <c r="V125" s="120" t="s">
+        <v>644</v>
+      </c>
+      <c r="W125" s="119" t="s">
         <v>645</v>
-      </c>
-      <c r="W125" s="119" t="s">
-        <v>646</v>
       </c>
       <c r="X125" s="119" t="s">
         <v>77</v>
@@ -13755,64 +13755,64 @@
         <v>129</v>
       </c>
       <c r="Z125" s="120" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AA125" s="119" t="s">
         <v>414</v>
       </c>
       <c r="AB125" s="176" t="s">
+        <v>647</v>
+      </c>
+      <c r="AC125" s="119" t="s">
         <v>648</v>
       </c>
-      <c r="AC125" s="119" t="s">
+      <c r="AD125" s="119" t="s">
         <v>649</v>
       </c>
-      <c r="AD125" s="119" t="s">
+      <c r="AE125" s="119" t="s">
         <v>650</v>
       </c>
-      <c r="AE125" s="119" t="s">
+      <c r="AF125" s="119" t="s">
         <v>651</v>
       </c>
-      <c r="AF125" s="119" t="s">
+      <c r="AG125" s="120" t="s">
         <v>652</v>
       </c>
-      <c r="AG125" s="120" t="s">
+      <c r="AH125" s="120" t="s">
         <v>653</v>
       </c>
-      <c r="AH125" s="120" t="s">
-        <v>654</v>
-      </c>
       <c r="AI125" s="120" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AJ125" s="140" t="s">
         <v>137</v>
       </c>
       <c r="AK125" s="119" t="s">
+        <v>654</v>
+      </c>
+      <c r="AL125" s="119" t="s">
+        <v>535</v>
+      </c>
+      <c r="AM125" s="119" t="s">
         <v>655</v>
       </c>
-      <c r="AL125" s="119" t="s">
-        <v>536</v>
-      </c>
-      <c r="AM125" s="119" t="s">
+      <c r="AN125" s="141" t="s">
         <v>656</v>
       </c>
-      <c r="AN125" s="141" t="s">
+      <c r="AO125" s="119" t="s">
         <v>657</v>
       </c>
-      <c r="AO125" s="119" t="s">
+      <c r="AP125" s="120" t="s">
         <v>658</v>
-      </c>
-      <c r="AP125" s="120" t="s">
-        <v>659</v>
       </c>
       <c r="AQ125" s="119" t="s">
         <v>133</v>
       </c>
       <c r="AR125" s="119" t="s">
+        <v>659</v>
+      </c>
+      <c r="AS125" s="119" t="s">
         <v>660</v>
-      </c>
-      <c r="AS125" s="119" t="s">
-        <v>661</v>
       </c>
       <c r="AT125" s="120" t="s">
         <v>430</v>
@@ -13821,38 +13821,38 @@
         <v>384</v>
       </c>
       <c r="AV125" s="120" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AW125" s="138" t="s">
         <v>203</v>
       </c>
       <c r="AX125" s="142" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AY125" s="138" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="126" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="196"/>
-      <c r="B126" s="196"/>
+      <c r="A126" s="194"/>
+      <c r="B126" s="194"/>
       <c r="C126" s="241"/>
       <c r="D126" s="123" t="s">
-        <v>664</v>
-      </c>
-      <c r="E126" s="198"/>
+        <v>663</v>
+      </c>
+      <c r="E126" s="189"/>
       <c r="F126" s="119"/>
       <c r="G126" s="119"/>
       <c r="H126" s="119"/>
       <c r="I126" s="122" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="J126" s="178"/>
       <c r="K126" s="178"/>
       <c r="L126" s="123"/>
       <c r="M126" s="181"/>
       <c r="N126" s="122" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O126" s="178"/>
       <c r="P126" s="181"/>
@@ -13868,47 +13868,47 @@
       <c r="Z126" s="120"/>
       <c r="AA126" s="178"/>
       <c r="AB126" s="176" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AC126" s="178"/>
       <c r="AD126" s="178"/>
       <c r="AE126" s="178"/>
       <c r="AF126" s="119" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AG126" s="120"/>
       <c r="AH126" s="120"/>
       <c r="AI126" s="120"/>
       <c r="AJ126" s="178"/>
-      <c r="AK126" s="271"/>
+      <c r="AK126" s="270"/>
       <c r="AL126" s="119" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AM126" s="178"/>
       <c r="AN126" s="141"/>
       <c r="AO126" s="178"/>
       <c r="AP126" s="120" t="s">
+        <v>669</v>
+      </c>
+      <c r="AQ126" s="119" t="s">
+        <v>546</v>
+      </c>
+      <c r="AR126" s="119" t="s">
         <v>670</v>
-      </c>
-      <c r="AQ126" s="119" t="s">
-        <v>547</v>
-      </c>
-      <c r="AR126" s="119" t="s">
-        <v>671</v>
       </c>
       <c r="AS126" s="178"/>
       <c r="AT126" s="120"/>
       <c r="AU126" s="120"/>
       <c r="AV126" s="120"/>
-      <c r="AW126" s="224"/>
+      <c r="AW126" s="239"/>
       <c r="AX126" s="142" t="s">
         <v>514</v>
       </c>
       <c r="AY126" s="185"/>
     </row>
     <row r="127" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="196"/>
-      <c r="B127" s="196"/>
+      <c r="A127" s="194"/>
+      <c r="B127" s="194"/>
       <c r="C127" s="215"/>
       <c r="D127" s="219"/>
       <c r="E127" s="179"/>
@@ -13921,7 +13921,7 @@
       <c r="L127" s="123"/>
       <c r="M127" s="179"/>
       <c r="N127" s="122" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="O127" s="179"/>
       <c r="P127" s="179"/>
@@ -13957,13 +13957,13 @@
       <c r="AT127" s="120"/>
       <c r="AU127" s="120"/>
       <c r="AV127" s="120"/>
-      <c r="AW127" s="225"/>
+      <c r="AW127" s="240"/>
       <c r="AX127" s="185"/>
       <c r="AY127" s="186"/>
     </row>
     <row r="128" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="196"/>
-      <c r="B128" s="196"/>
+      <c r="A128" s="194"/>
+      <c r="B128" s="194"/>
       <c r="C128" s="215"/>
       <c r="D128" s="179"/>
       <c r="E128" s="179"/>
@@ -14010,13 +14010,13 @@
       <c r="AT128" s="120"/>
       <c r="AU128" s="120"/>
       <c r="AV128" s="120"/>
-      <c r="AW128" s="225"/>
+      <c r="AW128" s="240"/>
       <c r="AX128" s="186"/>
       <c r="AY128" s="186"/>
     </row>
     <row r="129" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="196"/>
-      <c r="B129" s="196"/>
+      <c r="A129" s="194"/>
+      <c r="B129" s="194"/>
       <c r="C129" s="215"/>
       <c r="D129" s="179"/>
       <c r="E129" s="179"/>
@@ -14042,7 +14042,7 @@
       <c r="Y129" s="120"/>
       <c r="Z129" s="123"/>
       <c r="AA129" s="121"/>
-      <c r="AB129" s="189"/>
+      <c r="AB129" s="202"/>
       <c r="AC129" s="179"/>
       <c r="AD129" s="123"/>
       <c r="AE129" s="121"/>
@@ -14063,13 +14063,13 @@
       <c r="AT129" s="120"/>
       <c r="AU129" s="120"/>
       <c r="AV129" s="120"/>
-      <c r="AW129" s="225"/>
+      <c r="AW129" s="240"/>
       <c r="AX129" s="186"/>
       <c r="AY129" s="186"/>
     </row>
     <row r="130" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="196"/>
-      <c r="B130" s="196"/>
+      <c r="A130" s="194"/>
+      <c r="B130" s="194"/>
       <c r="C130" s="215"/>
       <c r="D130" s="179"/>
       <c r="E130" s="179"/>
@@ -14121,8 +14121,8 @@
       <c r="AY130" s="121"/>
     </row>
     <row r="131" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="196"/>
-      <c r="B131" s="196"/>
+      <c r="A131" s="194"/>
+      <c r="B131" s="194"/>
       <c r="C131" s="215"/>
       <c r="D131" s="179"/>
       <c r="E131" s="179"/>
@@ -14174,8 +14174,8 @@
       <c r="AY131" s="120"/>
     </row>
     <row r="132" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="196"/>
-      <c r="B132" s="197"/>
+      <c r="A132" s="194"/>
+      <c r="B132" s="195"/>
       <c r="C132" s="216"/>
       <c r="D132" s="184"/>
       <c r="E132" s="184"/>
@@ -14227,100 +14227,100 @@
       <c r="AY132" s="139"/>
     </row>
     <row r="133" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="196"/>
-      <c r="B133" s="190">
+      <c r="A133" s="194"/>
+      <c r="B133" s="211">
         <v>4</v>
       </c>
       <c r="C133" s="163" t="s">
+        <v>672</v>
+      </c>
+      <c r="D133" s="128" t="s">
         <v>673</v>
       </c>
-      <c r="D133" s="128" t="s">
+      <c r="E133" s="168" t="s">
         <v>674</v>
-      </c>
-      <c r="E133" s="168" t="s">
-        <v>675</v>
       </c>
       <c r="F133" s="169" t="s">
         <v>271</v>
       </c>
       <c r="G133" s="119" t="s">
+        <v>675</v>
+      </c>
+      <c r="H133" s="119" t="s">
         <v>676</v>
       </c>
-      <c r="H133" s="119" t="s">
+      <c r="I133" s="122" t="s">
         <v>677</v>
       </c>
-      <c r="I133" s="122" t="s">
+      <c r="J133" s="122" t="s">
         <v>678</v>
       </c>
-      <c r="J133" s="122" t="s">
+      <c r="K133" s="119" t="s">
         <v>679</v>
       </c>
-      <c r="K133" s="119" t="s">
+      <c r="L133" s="151" t="s">
         <v>680</v>
-      </c>
-      <c r="L133" s="151" t="s">
-        <v>681</v>
       </c>
       <c r="M133" s="120" t="s">
         <v>59</v>
       </c>
       <c r="N133" s="168" t="s">
+        <v>681</v>
+      </c>
+      <c r="O133" s="133" t="s">
         <v>682</v>
-      </c>
-      <c r="O133" s="133" t="s">
-        <v>683</v>
       </c>
       <c r="P133" s="133" t="s">
         <v>274</v>
       </c>
       <c r="Q133" s="119" t="s">
+        <v>683</v>
+      </c>
+      <c r="R133" s="119" t="s">
         <v>684</v>
       </c>
-      <c r="R133" s="119" t="s">
+      <c r="S133" s="122" t="s">
         <v>685</v>
       </c>
-      <c r="S133" s="122" t="s">
+      <c r="T133" s="133" t="s">
         <v>686</v>
       </c>
-      <c r="T133" s="133" t="s">
+      <c r="U133" s="120" t="s">
         <v>687</v>
       </c>
-      <c r="U133" s="120" t="s">
+      <c r="V133" s="119" t="s">
         <v>688</v>
       </c>
-      <c r="V133" s="119" t="s">
-        <v>689</v>
-      </c>
       <c r="W133" s="120" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X133" s="119" t="s">
         <v>129</v>
       </c>
       <c r="Y133" s="119" t="s">
+        <v>689</v>
+      </c>
+      <c r="Z133" s="119" t="s">
         <v>690</v>
       </c>
-      <c r="Z133" s="119" t="s">
+      <c r="AA133" s="119" t="s">
         <v>691</v>
       </c>
-      <c r="AA133" s="119" t="s">
+      <c r="AB133" s="189"/>
+      <c r="AC133" s="133" t="s">
         <v>692</v>
       </c>
-      <c r="AB133" s="198"/>
-      <c r="AC133" s="133" t="s">
+      <c r="AD133" s="119" t="s">
         <v>693</v>
-      </c>
-      <c r="AD133" s="119" t="s">
-        <v>694</v>
       </c>
       <c r="AE133" s="119" t="s">
         <v>418</v>
       </c>
       <c r="AF133" s="119" t="s">
+        <v>694</v>
+      </c>
+      <c r="AG133" s="120" t="s">
         <v>695</v>
-      </c>
-      <c r="AG133" s="120" t="s">
-        <v>696</v>
       </c>
       <c r="AH133" s="119" t="s">
         <v>251</v>
@@ -14329,136 +14329,136 @@
         <v>251</v>
       </c>
       <c r="AJ133" s="140" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AK133" s="119" t="s">
         <v>423</v>
       </c>
       <c r="AL133" s="119" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AM133" s="119" t="s">
+        <v>697</v>
+      </c>
+      <c r="AN133" s="119" t="s">
         <v>698</v>
       </c>
-      <c r="AN133" s="119" t="s">
+      <c r="AO133" s="119" t="s">
         <v>699</v>
       </c>
-      <c r="AO133" s="119" t="s">
+      <c r="AP133" s="120" t="s">
         <v>700</v>
       </c>
-      <c r="AP133" s="120" t="s">
+      <c r="AQ133" s="119" t="s">
         <v>701</v>
       </c>
-      <c r="AQ133" s="119" t="s">
+      <c r="AR133" s="119" t="s">
         <v>702</v>
       </c>
-      <c r="AR133" s="119" t="s">
+      <c r="AS133" s="119" t="s">
         <v>703</v>
-      </c>
-      <c r="AS133" s="119" t="s">
-        <v>704</v>
       </c>
       <c r="AT133" s="120" t="s">
         <v>200</v>
       </c>
       <c r="AU133" s="119" t="s">
+        <v>704</v>
+      </c>
+      <c r="AV133" s="119" t="s">
+        <v>661</v>
+      </c>
+      <c r="AW133" s="120" t="s">
         <v>705</v>
-      </c>
-      <c r="AV133" s="119" t="s">
-        <v>662</v>
-      </c>
-      <c r="AW133" s="120" t="s">
-        <v>706</v>
       </c>
       <c r="AX133" s="142" t="s">
         <v>339</v>
       </c>
       <c r="AY133" s="120" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="134" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="196"/>
+      <c r="A134" s="194"/>
       <c r="B134" s="191"/>
       <c r="C134" s="163" t="s">
+        <v>706</v>
+      </c>
+      <c r="D134" s="128" t="s">
         <v>707</v>
       </c>
-      <c r="D134" s="128" t="s">
+      <c r="E134" s="198"/>
+      <c r="F134" s="169" t="s">
         <v>708</v>
       </c>
-      <c r="E134" s="201"/>
-      <c r="F134" s="169" t="s">
+      <c r="G134" s="119" t="s">
         <v>709</v>
       </c>
-      <c r="G134" s="119" t="s">
+      <c r="H134" s="119" t="s">
         <v>710</v>
       </c>
-      <c r="H134" s="119" t="s">
+      <c r="I134" s="122" t="s">
         <v>711</v>
       </c>
-      <c r="I134" s="122" t="s">
+      <c r="J134" s="122" t="s">
         <v>712</v>
       </c>
-      <c r="J134" s="122" t="s">
+      <c r="K134" s="119" t="s">
         <v>713</v>
       </c>
-      <c r="K134" s="119" t="s">
+      <c r="L134" s="151" t="s">
         <v>714</v>
-      </c>
-      <c r="L134" s="151" t="s">
-        <v>715</v>
       </c>
       <c r="M134" s="120"/>
       <c r="N134" s="168" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="O134" s="178"/>
       <c r="P134" s="178"/>
       <c r="Q134" s="119" t="s">
+        <v>716</v>
+      </c>
+      <c r="R134" s="119" t="s">
         <v>717</v>
-      </c>
-      <c r="R134" s="119" t="s">
-        <v>718</v>
       </c>
       <c r="S134" s="181"/>
       <c r="T134" s="133" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="U134" s="126"/>
       <c r="V134" s="242"/>
       <c r="W134" s="120"/>
       <c r="X134" s="119"/>
       <c r="Y134" s="119" t="s">
+        <v>719</v>
+      </c>
+      <c r="Z134" s="119" t="s">
+        <v>632</v>
+      </c>
+      <c r="AA134" s="119" t="s">
         <v>720</v>
-      </c>
-      <c r="Z134" s="119" t="s">
-        <v>633</v>
-      </c>
-      <c r="AA134" s="119" t="s">
-        <v>721</v>
       </c>
       <c r="AB134" s="179"/>
       <c r="AC134" s="178"/>
       <c r="AD134" s="119" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AE134" s="178"/>
       <c r="AF134" s="119" t="s">
+        <v>722</v>
+      </c>
+      <c r="AG134" s="120" t="s">
         <v>723</v>
       </c>
-      <c r="AG134" s="120" t="s">
+      <c r="AH134" s="119" t="s">
         <v>724</v>
       </c>
-      <c r="AH134" s="119" t="s">
-        <v>725</v>
-      </c>
       <c r="AI134" s="119" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AJ134" s="119"/>
       <c r="AK134" s="178"/>
       <c r="AL134" s="119" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AM134" s="178"/>
       <c r="AN134" s="178"/>
@@ -14466,38 +14466,38 @@
         <v>450</v>
       </c>
       <c r="AP134" s="120" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AQ134" s="119" t="s">
         <v>342</v>
       </c>
       <c r="AR134" s="119" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AS134" s="178"/>
       <c r="AT134" s="120"/>
       <c r="AU134" s="119" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AV134" s="178"/>
       <c r="AW134" s="120" t="s">
-        <v>729</v>
-      </c>
-      <c r="AX134" s="233"/>
+        <v>728</v>
+      </c>
+      <c r="AX134" s="231"/>
       <c r="AY134" s="120" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="135" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="196"/>
+      <c r="A135" s="194"/>
       <c r="B135" s="191"/>
       <c r="C135" s="223"/>
-      <c r="D135" s="253"/>
+      <c r="D135" s="255"/>
       <c r="E135" s="179"/>
       <c r="F135" s="123"/>
       <c r="G135" s="119"/>
       <c r="H135" s="119" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I135" s="122"/>
       <c r="J135" s="181"/>
@@ -14517,7 +14517,7 @@
       <c r="X135" s="120"/>
       <c r="Y135" s="119"/>
       <c r="Z135" s="119" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AA135" s="178"/>
       <c r="AB135" s="184"/>
@@ -14527,10 +14527,10 @@
       <c r="AF135" s="119"/>
       <c r="AG135" s="120"/>
       <c r="AH135" s="119" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AI135" s="119" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AJ135" s="120"/>
       <c r="AK135" s="179"/>
@@ -14539,22 +14539,22 @@
       <c r="AN135" s="179"/>
       <c r="AO135" s="178"/>
       <c r="AP135" s="120" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AQ135" s="178"/>
       <c r="AR135" s="178"/>
       <c r="AS135" s="179"/>
       <c r="AT135" s="120"/>
       <c r="AU135" s="119" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AV135" s="179"/>
       <c r="AW135" s="120"/>
-      <c r="AX135" s="211"/>
+      <c r="AX135" s="209"/>
       <c r="AY135" s="120"/>
     </row>
     <row r="136" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="196"/>
+      <c r="A136" s="194"/>
       <c r="B136" s="191"/>
       <c r="C136" s="215"/>
       <c r="D136" s="179"/>
@@ -14588,10 +14588,10 @@
       <c r="AF136" s="120"/>
       <c r="AG136" s="120"/>
       <c r="AH136" s="119" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AI136" s="119" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AJ136" s="120"/>
       <c r="AK136" s="179"/>
@@ -14604,21 +14604,21 @@
       <c r="AR136" s="179"/>
       <c r="AS136" s="179"/>
       <c r="AT136" s="120"/>
-      <c r="AU136" s="224"/>
+      <c r="AU136" s="239"/>
       <c r="AV136" s="179"/>
-      <c r="AW136" s="248"/>
-      <c r="AX136" s="211"/>
-      <c r="AY136" s="251"/>
+      <c r="AW136" s="249"/>
+      <c r="AX136" s="209"/>
+      <c r="AY136" s="250"/>
     </row>
     <row r="137" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="196"/>
+      <c r="A137" s="194"/>
       <c r="B137" s="191"/>
       <c r="C137" s="215"/>
       <c r="D137" s="179"/>
       <c r="E137" s="179"/>
       <c r="F137" s="123"/>
       <c r="G137" s="120"/>
-      <c r="H137" s="243"/>
+      <c r="H137" s="245"/>
       <c r="I137" s="123"/>
       <c r="J137" s="179"/>
       <c r="K137" s="179"/>
@@ -14645,26 +14645,26 @@
       <c r="AF137" s="139"/>
       <c r="AG137" s="139"/>
       <c r="AH137" s="125"/>
-      <c r="AI137" s="249"/>
+      <c r="AI137" s="248"/>
       <c r="AJ137" s="120"/>
       <c r="AK137" s="131"/>
       <c r="AL137" s="179"/>
       <c r="AM137" s="131"/>
       <c r="AN137" s="120"/>
       <c r="AO137" s="179"/>
-      <c r="AP137" s="189"/>
+      <c r="AP137" s="202"/>
       <c r="AQ137" s="179"/>
       <c r="AR137" s="179"/>
       <c r="AS137" s="179"/>
       <c r="AT137" s="120"/>
-      <c r="AU137" s="225"/>
+      <c r="AU137" s="240"/>
       <c r="AV137" s="179"/>
-      <c r="AW137" s="225"/>
-      <c r="AX137" s="211"/>
+      <c r="AW137" s="240"/>
+      <c r="AX137" s="209"/>
       <c r="AY137" s="186"/>
     </row>
     <row r="138" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="196"/>
+      <c r="A138" s="194"/>
       <c r="B138" s="191"/>
       <c r="C138" s="215"/>
       <c r="D138" s="179"/>
@@ -14710,14 +14710,14 @@
       <c r="AR138" s="179"/>
       <c r="AS138" s="120"/>
       <c r="AT138" s="120"/>
-      <c r="AU138" s="225"/>
+      <c r="AU138" s="240"/>
       <c r="AV138" s="120"/>
-      <c r="AW138" s="225"/>
+      <c r="AW138" s="240"/>
       <c r="AX138" s="137"/>
       <c r="AY138" s="186"/>
     </row>
     <row r="139" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="196"/>
+      <c r="A139" s="194"/>
       <c r="B139" s="191"/>
       <c r="C139" s="215"/>
       <c r="D139" s="179"/>
@@ -14763,16 +14763,16 @@
       <c r="AR139" s="120"/>
       <c r="AS139" s="120"/>
       <c r="AT139" s="120"/>
-      <c r="AU139" s="225"/>
+      <c r="AU139" s="240"/>
       <c r="AV139" s="143"/>
-      <c r="AW139" s="225"/>
+      <c r="AW139" s="240"/>
       <c r="AX139" s="143"/>
       <c r="AY139" s="186"/>
       <c r="AZ139" s="6"/>
     </row>
     <row r="140" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="196"/>
-      <c r="B140" s="192"/>
+      <c r="A140" s="194"/>
+      <c r="B140" s="212"/>
       <c r="C140" s="216"/>
       <c r="D140" s="184"/>
       <c r="E140" s="184"/>
@@ -14824,66 +14824,66 @@
       <c r="AY140" s="139"/>
     </row>
     <row r="141" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="196"/>
+      <c r="A141" s="194"/>
       <c r="B141" s="213">
         <v>5</v>
       </c>
       <c r="C141" s="223"/>
-      <c r="D141" s="198"/>
-      <c r="E141" s="198"/>
+      <c r="D141" s="189"/>
+      <c r="E141" s="189"/>
       <c r="F141" s="119"/>
       <c r="G141" s="122" t="s">
+        <v>735</v>
+      </c>
+      <c r="H141" s="140" t="s">
         <v>736</v>
-      </c>
-      <c r="H141" s="140" t="s">
-        <v>737</v>
       </c>
       <c r="I141" s="119"/>
       <c r="J141" s="122" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K141" s="122" t="s">
+        <v>737</v>
+      </c>
+      <c r="L141" s="78" t="s">
         <v>738</v>
       </c>
-      <c r="L141" s="78" t="s">
+      <c r="M141" s="139" t="s">
         <v>739</v>
-      </c>
-      <c r="M141" s="139" t="s">
-        <v>740</v>
       </c>
       <c r="N141" s="178"/>
       <c r="O141" s="178"/>
       <c r="P141" s="122" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q141" s="178"/>
       <c r="R141" s="178"/>
       <c r="S141" s="122" t="s">
+        <v>741</v>
+      </c>
+      <c r="T141" s="120" t="s">
         <v>742</v>
-      </c>
-      <c r="T141" s="120" t="s">
-        <v>743</v>
       </c>
       <c r="U141" s="122" t="s">
         <v>118</v>
       </c>
       <c r="V141" s="120"/>
       <c r="W141" s="119" t="s">
+        <v>743</v>
+      </c>
+      <c r="X141" s="119" t="s">
         <v>744</v>
       </c>
-      <c r="X141" s="119" t="s">
+      <c r="Y141" s="119" t="s">
         <v>745</v>
       </c>
-      <c r="Y141" s="119" t="s">
+      <c r="Z141" s="119" t="s">
         <v>746</v>
       </c>
-      <c r="Z141" s="119" t="s">
+      <c r="AA141" s="178"/>
+      <c r="AB141" s="189"/>
+      <c r="AC141" s="119" t="s">
         <v>747</v>
-      </c>
-      <c r="AA141" s="178"/>
-      <c r="AB141" s="198"/>
-      <c r="AC141" s="119" t="s">
-        <v>748</v>
       </c>
       <c r="AD141" s="178"/>
       <c r="AE141" s="120" t="s">
@@ -14892,61 +14892,61 @@
       <c r="AF141" s="147"/>
       <c r="AG141" s="119"/>
       <c r="AH141" s="133" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AI141" s="133" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AJ141" s="119"/>
       <c r="AK141" s="140" t="s">
         <v>192</v>
       </c>
       <c r="AL141" s="119" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AM141" s="141" t="s">
+        <v>749</v>
+      </c>
+      <c r="AN141" s="119" t="s">
         <v>750</v>
-      </c>
-      <c r="AN141" s="119" t="s">
-        <v>751</v>
       </c>
       <c r="AO141" s="119" t="s">
         <v>450</v>
       </c>
       <c r="AP141" s="119" t="s">
+        <v>751</v>
+      </c>
+      <c r="AQ141" s="141" t="s">
         <v>752</v>
-      </c>
-      <c r="AQ141" s="141" t="s">
-        <v>753</v>
       </c>
       <c r="AR141" s="187"/>
       <c r="AS141" s="134"/>
       <c r="AT141" s="185"/>
-      <c r="AU141" s="203"/>
+      <c r="AU141" s="200"/>
       <c r="AV141" s="119" t="s">
-        <v>754</v>
-      </c>
-      <c r="AW141" s="233"/>
+        <v>753</v>
+      </c>
+      <c r="AW141" s="231"/>
       <c r="AX141" s="187"/>
-      <c r="AY141" s="245"/>
+      <c r="AY141" s="246"/>
     </row>
     <row r="142" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="196"/>
-      <c r="B142" s="196"/>
+      <c r="A142" s="194"/>
+      <c r="B142" s="194"/>
       <c r="C142" s="215"/>
       <c r="D142" s="179"/>
       <c r="E142" s="179"/>
       <c r="F142" s="120"/>
       <c r="G142" s="122"/>
-      <c r="H142" s="198"/>
+      <c r="H142" s="189"/>
       <c r="I142" s="120"/>
       <c r="J142" s="181"/>
       <c r="K142" s="181"/>
       <c r="L142" s="78" t="s">
+        <v>754</v>
+      </c>
+      <c r="M142" s="139" t="s">
         <v>755</v>
-      </c>
-      <c r="M142" s="139" t="s">
-        <v>756</v>
       </c>
       <c r="N142" s="179"/>
       <c r="O142" s="179"/>
@@ -14958,17 +14958,17 @@
       <c r="U142" s="181"/>
       <c r="V142" s="120"/>
       <c r="W142" s="119" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="X142" s="119"/>
       <c r="Y142" s="119"/>
       <c r="Z142" s="119" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AA142" s="179"/>
       <c r="AB142" s="184"/>
       <c r="AC142" s="119" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AD142" s="179"/>
       <c r="AE142" s="120"/>
@@ -14989,15 +14989,15 @@
       <c r="AR142" s="188"/>
       <c r="AS142" s="134"/>
       <c r="AT142" s="186"/>
-      <c r="AU142" s="204"/>
+      <c r="AU142" s="201"/>
       <c r="AV142" s="185"/>
-      <c r="AW142" s="211"/>
+      <c r="AW142" s="209"/>
       <c r="AX142" s="188"/>
-      <c r="AY142" s="246"/>
+      <c r="AY142" s="247"/>
     </row>
     <row r="143" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="196"/>
-      <c r="B143" s="196"/>
+      <c r="A143" s="194"/>
+      <c r="B143" s="194"/>
       <c r="C143" s="215"/>
       <c r="D143" s="179"/>
       <c r="E143" s="179"/>
@@ -15008,10 +15008,10 @@
       <c r="J143" s="179"/>
       <c r="K143" s="179"/>
       <c r="L143" s="78" t="s">
+        <v>759</v>
+      </c>
+      <c r="M143" s="139" t="s">
         <v>760</v>
-      </c>
-      <c r="M143" s="139" t="s">
-        <v>761</v>
       </c>
       <c r="N143" s="179"/>
       <c r="O143" s="179"/>
@@ -15046,15 +15046,15 @@
       <c r="AR143" s="188"/>
       <c r="AS143" s="134"/>
       <c r="AT143" s="186"/>
-      <c r="AU143" s="204"/>
+      <c r="AU143" s="201"/>
       <c r="AV143" s="186"/>
-      <c r="AW143" s="211"/>
+      <c r="AW143" s="209"/>
       <c r="AX143" s="188"/>
-      <c r="AY143" s="246"/>
+      <c r="AY143" s="247"/>
     </row>
     <row r="144" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="196"/>
-      <c r="B144" s="196"/>
+      <c r="A144" s="194"/>
+      <c r="B144" s="194"/>
       <c r="C144" s="215"/>
       <c r="D144" s="179"/>
       <c r="E144" s="179"/>
@@ -15064,7 +15064,7 @@
       <c r="I144" s="120"/>
       <c r="J144" s="179"/>
       <c r="K144" s="179"/>
-      <c r="L144" s="199"/>
+      <c r="L144" s="196"/>
       <c r="M144" s="178"/>
       <c r="N144" s="179"/>
       <c r="O144" s="179"/>
@@ -15081,7 +15081,7 @@
       <c r="Z144" s="120"/>
       <c r="AA144" s="131"/>
       <c r="AB144" s="120"/>
-      <c r="AC144" s="263"/>
+      <c r="AC144" s="264"/>
       <c r="AD144" s="179"/>
       <c r="AE144" s="120"/>
       <c r="AF144" s="131"/>
@@ -15106,8 +15106,8 @@
       <c r="AY144" s="146"/>
     </row>
     <row r="145" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="196"/>
-      <c r="B145" s="196"/>
+      <c r="A145" s="194"/>
+      <c r="B145" s="194"/>
       <c r="C145" s="215"/>
       <c r="D145" s="179"/>
       <c r="E145" s="179"/>
@@ -15130,7 +15130,7 @@
       <c r="V145" s="120"/>
       <c r="W145" s="121"/>
       <c r="X145" s="120"/>
-      <c r="Y145" s="263"/>
+      <c r="Y145" s="264"/>
       <c r="Z145" s="120"/>
       <c r="AA145" s="120"/>
       <c r="AB145" s="120"/>
@@ -15143,7 +15143,7 @@
       <c r="AI145" s="120"/>
       <c r="AJ145" s="131"/>
       <c r="AK145" s="179"/>
-      <c r="AL145" s="270"/>
+      <c r="AL145" s="269"/>
       <c r="AM145" s="131"/>
       <c r="AN145" s="179"/>
       <c r="AO145" s="120"/>
@@ -15159,8 +15159,8 @@
       <c r="AY145" s="146"/>
     </row>
     <row r="146" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="196"/>
-      <c r="B146" s="196"/>
+      <c r="A146" s="194"/>
+      <c r="B146" s="194"/>
       <c r="C146" s="215"/>
       <c r="D146" s="179"/>
       <c r="E146" s="179"/>
@@ -15212,8 +15212,8 @@
       <c r="AY146" s="55"/>
     </row>
     <row r="147" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="196"/>
-      <c r="B147" s="197"/>
+      <c r="A147" s="194"/>
+      <c r="B147" s="195"/>
       <c r="C147" s="216"/>
       <c r="D147" s="184"/>
       <c r="E147" s="184"/>
@@ -15265,8 +15265,8 @@
       <c r="AY147" s="62"/>
     </row>
     <row r="148" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="196"/>
-      <c r="B148" s="190">
+      <c r="A148" s="194"/>
+      <c r="B148" s="211">
         <v>6</v>
       </c>
       <c r="C148" s="223"/>
@@ -15307,14 +15307,14 @@
       <c r="AJ148" s="140"/>
       <c r="AK148" s="119"/>
       <c r="AL148" s="119" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AM148" s="119"/>
       <c r="AN148" s="140"/>
       <c r="AO148" s="119"/>
       <c r="AP148" s="136"/>
       <c r="AQ148" s="141" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AR148" s="136"/>
       <c r="AS148" s="136"/>
@@ -15326,7 +15326,7 @@
       <c r="AY148" s="145"/>
     </row>
     <row r="149" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="196"/>
+      <c r="A149" s="194"/>
       <c r="B149" s="191"/>
       <c r="C149" s="215"/>
       <c r="D149" s="120"/>
@@ -15379,7 +15379,7 @@
       <c r="AY149" s="146"/>
     </row>
     <row r="150" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="196"/>
+      <c r="A150" s="194"/>
       <c r="B150" s="191"/>
       <c r="C150" s="215"/>
       <c r="D150" s="120"/>
@@ -15432,7 +15432,7 @@
       <c r="AY150" s="146"/>
     </row>
     <row r="151" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="196"/>
+      <c r="A151" s="194"/>
       <c r="B151" s="191"/>
       <c r="C151" s="215"/>
       <c r="D151" s="120"/>
@@ -15485,8 +15485,8 @@
       <c r="AY151" s="146"/>
     </row>
     <row r="152" spans="1:51" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="196"/>
-      <c r="B152" s="192"/>
+      <c r="A152" s="194"/>
+      <c r="B152" s="212"/>
       <c r="C152" s="216"/>
       <c r="D152" s="139"/>
       <c r="E152" s="167"/>
@@ -15538,11 +15538,11 @@
       <c r="AY152" s="62"/>
     </row>
     <row r="153" spans="1:51" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="196"/>
-      <c r="B153" s="193">
+      <c r="A153" s="194"/>
+      <c r="B153" s="190">
         <v>7</v>
       </c>
-      <c r="C153" s="236"/>
+      <c r="C153" s="234"/>
       <c r="D153" s="119"/>
       <c r="E153" s="140"/>
       <c r="F153" s="119"/>
@@ -15593,7 +15593,7 @@
       <c r="AY153" s="145"/>
     </row>
     <row r="154" spans="1:51" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="196"/>
+      <c r="A154" s="194"/>
       <c r="B154" s="191"/>
       <c r="C154" s="215"/>
       <c r="D154" s="120"/>
@@ -15646,7 +15646,7 @@
       <c r="AY154" s="146"/>
     </row>
     <row r="155" spans="1:51" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="196"/>
+      <c r="A155" s="194"/>
       <c r="B155" s="191"/>
       <c r="C155" s="215"/>
       <c r="D155" s="120"/>
@@ -15699,7 +15699,7 @@
       <c r="AY155" s="146"/>
     </row>
     <row r="156" spans="1:51" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="196"/>
+      <c r="A156" s="194"/>
       <c r="B156" s="191"/>
       <c r="C156" s="215"/>
       <c r="D156" s="120"/>
@@ -15752,9 +15752,9 @@
       <c r="AY156" s="146"/>
     </row>
     <row r="157" spans="1:51" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="206"/>
-      <c r="B157" s="194"/>
-      <c r="C157" s="237"/>
+      <c r="A157" s="204"/>
+      <c r="B157" s="192"/>
+      <c r="C157" s="235"/>
       <c r="D157" s="171"/>
       <c r="E157" s="63"/>
       <c r="F157" s="82"/>
@@ -15805,10 +15805,10 @@
       <c r="AY157" s="67"/>
     </row>
     <row r="158" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="205" t="s">
-        <v>762</v>
-      </c>
-      <c r="B158" s="231">
+      <c r="A158" s="203" t="s">
+        <v>761</v>
+      </c>
+      <c r="B158" s="229">
         <v>1</v>
       </c>
       <c r="C158" s="166" t="s">
@@ -15818,7 +15818,7 @@
         <v>308</v>
       </c>
       <c r="E158" s="168" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F158" s="133" t="s">
         <v>59</v>
@@ -15827,13 +15827,13 @@
         <v>56</v>
       </c>
       <c r="H158" s="124" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="I158" s="124" t="s">
         <v>57</v>
       </c>
       <c r="J158" s="168" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="K158" s="122" t="s">
         <v>117</v>
@@ -15842,42 +15842,42 @@
         <v>168</v>
       </c>
       <c r="M158" s="151" t="s">
+        <v>765</v>
+      </c>
+      <c r="N158" s="134" t="s">
         <v>766</v>
-      </c>
-      <c r="N158" s="134" t="s">
-        <v>767</v>
       </c>
       <c r="O158" s="182"/>
       <c r="P158" s="122" t="s">
+        <v>767</v>
+      </c>
+      <c r="Q158" s="122" t="s">
         <v>768</v>
       </c>
-      <c r="Q158" s="122" t="s">
+      <c r="R158" s="120" t="s">
         <v>769</v>
       </c>
-      <c r="R158" s="120" t="s">
+      <c r="S158" s="119" t="s">
         <v>770</v>
       </c>
-      <c r="S158" s="119" t="s">
+      <c r="T158" s="124" t="s">
         <v>771</v>
-      </c>
-      <c r="T158" s="124" t="s">
-        <v>772</v>
       </c>
       <c r="U158" s="140" t="s">
         <v>126</v>
       </c>
       <c r="V158" s="182"/>
       <c r="W158" s="120" t="s">
+        <v>772</v>
+      </c>
+      <c r="X158" s="119" t="s">
         <v>773</v>
       </c>
-      <c r="X158" s="119" t="s">
+      <c r="Y158" s="119" t="s">
         <v>774</v>
       </c>
-      <c r="Y158" s="119" t="s">
+      <c r="Z158" s="133" t="s">
         <v>775</v>
-      </c>
-      <c r="Z158" s="133" t="s">
-        <v>776</v>
       </c>
       <c r="AA158" s="119" t="s">
         <v>182</v>
@@ -15889,37 +15889,37 @@
         <v>371</v>
       </c>
       <c r="AD158" s="120" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AE158" s="119" t="s">
         <v>373</v>
       </c>
       <c r="AF158" s="119" t="s">
+        <v>777</v>
+      </c>
+      <c r="AG158" s="119" t="s">
         <v>778</v>
       </c>
-      <c r="AG158" s="119" t="s">
+      <c r="AH158" s="120" t="s">
         <v>779</v>
       </c>
-      <c r="AH158" s="120" t="s">
-        <v>780</v>
-      </c>
       <c r="AI158" s="120" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AJ158" s="119" t="s">
         <v>254</v>
       </c>
       <c r="AK158" s="140" t="s">
+        <v>780</v>
+      </c>
+      <c r="AL158" s="119" t="s">
         <v>781</v>
       </c>
-      <c r="AL158" s="119" t="s">
+      <c r="AM158" s="119" t="s">
         <v>782</v>
       </c>
-      <c r="AM158" s="119" t="s">
+      <c r="AN158" s="120" t="s">
         <v>783</v>
-      </c>
-      <c r="AN158" s="120" t="s">
-        <v>784</v>
       </c>
       <c r="AO158" s="141" t="s">
         <v>486</v>
@@ -15933,31 +15933,31 @@
         <v>146</v>
       </c>
       <c r="AT158" s="119" t="s">
+        <v>784</v>
+      </c>
+      <c r="AU158" s="119" t="s">
+        <v>784</v>
+      </c>
+      <c r="AV158" s="119" t="s">
         <v>785</v>
-      </c>
-      <c r="AU158" s="119" t="s">
-        <v>785</v>
-      </c>
-      <c r="AV158" s="119" t="s">
-        <v>786</v>
       </c>
       <c r="AW158" s="120" t="s">
         <v>260</v>
       </c>
       <c r="AX158" s="134" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AY158" s="120" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="159" spans="1:51" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="196"/>
+      <c r="A159" s="194"/>
       <c r="B159" s="191"/>
       <c r="C159" s="222"/>
       <c r="D159" s="169"/>
       <c r="E159" s="168" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F159" s="119"/>
       <c r="G159" s="119"/>
@@ -15966,7 +15966,7 @@
       </c>
       <c r="I159" s="124"/>
       <c r="J159" s="168" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K159" s="181"/>
       <c r="L159" s="181"/>
@@ -15976,27 +15976,27 @@
       </c>
       <c r="O159" s="179"/>
       <c r="P159" s="122" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="Q159" s="181"/>
       <c r="R159" s="120" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="S159" s="178"/>
       <c r="T159" s="124" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="U159" s="178"/>
       <c r="V159" s="179"/>
       <c r="W159" s="120"/>
       <c r="X159" s="119" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y159" s="119" t="s">
         <v>793</v>
       </c>
-      <c r="Y159" s="119" t="s">
+      <c r="Z159" s="133" t="s">
         <v>794</v>
-      </c>
-      <c r="Z159" s="133" t="s">
-        <v>795</v>
       </c>
       <c r="AA159" s="178"/>
       <c r="AB159" s="178"/>
@@ -16006,19 +16006,19 @@
       <c r="AD159" s="120"/>
       <c r="AE159" s="178"/>
       <c r="AF159" s="119" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG159" s="119"/>
       <c r="AH159" s="120"/>
       <c r="AI159" s="120"/>
       <c r="AJ159" s="119" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AK159" s="178"/>
       <c r="AL159" s="178"/>
       <c r="AM159" s="178"/>
       <c r="AN159" s="120" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AO159" s="141"/>
       <c r="AP159" s="120"/>
@@ -16026,30 +16026,30 @@
       <c r="AR159" s="178"/>
       <c r="AS159" s="120"/>
       <c r="AT159" s="119" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AU159" s="119" t="s">
         <v>113</v>
       </c>
       <c r="AV159" s="119" t="s">
+        <v>798</v>
+      </c>
+      <c r="AW159" s="120" t="s">
         <v>799</v>
       </c>
-      <c r="AW159" s="120" t="s">
-        <v>800</v>
-      </c>
       <c r="AX159" s="134" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="AY159" s="120" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="160" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="196"/>
+      <c r="A160" s="194"/>
       <c r="B160" s="191"/>
       <c r="C160" s="215"/>
       <c r="D160" s="169"/>
-      <c r="E160" s="201"/>
+      <c r="E160" s="198"/>
       <c r="F160" s="120"/>
       <c r="G160" s="120"/>
       <c r="H160" s="124"/>
@@ -16063,7 +16063,7 @@
       <c r="P160" s="19"/>
       <c r="Q160" s="179"/>
       <c r="R160" s="120" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="S160" s="179"/>
       <c r="T160" s="182"/>
@@ -16071,10 +16071,10 @@
       <c r="V160" s="179"/>
       <c r="W160" s="120"/>
       <c r="X160" s="119" t="s">
+        <v>801</v>
+      </c>
+      <c r="Y160" s="119" t="s">
         <v>802</v>
-      </c>
-      <c r="Y160" s="119" t="s">
-        <v>803</v>
       </c>
       <c r="Z160" s="119"/>
       <c r="AA160" s="179"/>
@@ -16096,17 +16096,17 @@
       <c r="AQ160" s="179"/>
       <c r="AR160" s="179"/>
       <c r="AS160" s="120"/>
-      <c r="AT160" s="224"/>
-      <c r="AU160" s="233"/>
+      <c r="AT160" s="239"/>
+      <c r="AU160" s="231"/>
       <c r="AV160" s="178"/>
       <c r="AW160" s="120"/>
       <c r="AX160" s="134" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="AY160" s="180"/>
     </row>
     <row r="161" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="196"/>
+      <c r="A161" s="194"/>
       <c r="B161" s="191"/>
       <c r="C161" s="215"/>
       <c r="D161" s="169"/>
@@ -16151,15 +16151,15 @@
       <c r="AQ161" s="179"/>
       <c r="AR161" s="179"/>
       <c r="AS161" s="120"/>
-      <c r="AT161" s="225"/>
-      <c r="AU161" s="211"/>
+      <c r="AT161" s="240"/>
+      <c r="AU161" s="209"/>
       <c r="AV161" s="179"/>
-      <c r="AW161" s="248"/>
+      <c r="AW161" s="249"/>
       <c r="AX161" s="221"/>
       <c r="AY161" s="179"/>
     </row>
     <row r="162" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="196"/>
+      <c r="A162" s="194"/>
       <c r="B162" s="191"/>
       <c r="C162" s="215"/>
       <c r="D162" s="169"/>
@@ -16204,15 +16204,15 @@
       <c r="AQ162" s="179"/>
       <c r="AR162" s="179"/>
       <c r="AS162" s="120"/>
-      <c r="AT162" s="225"/>
-      <c r="AU162" s="211"/>
+      <c r="AT162" s="240"/>
+      <c r="AU162" s="209"/>
       <c r="AV162" s="179"/>
-      <c r="AW162" s="225"/>
-      <c r="AX162" s="211"/>
+      <c r="AW162" s="240"/>
+      <c r="AX162" s="209"/>
       <c r="AY162" s="179"/>
     </row>
     <row r="163" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="196"/>
+      <c r="A163" s="194"/>
       <c r="B163" s="191"/>
       <c r="C163" s="215"/>
       <c r="D163" s="169"/>
@@ -16257,15 +16257,15 @@
       <c r="AQ163" s="120"/>
       <c r="AR163" s="179"/>
       <c r="AS163" s="120"/>
-      <c r="AT163" s="225"/>
-      <c r="AU163" s="211"/>
+      <c r="AT163" s="240"/>
+      <c r="AU163" s="209"/>
       <c r="AV163" s="179"/>
-      <c r="AW163" s="225"/>
-      <c r="AX163" s="211"/>
+      <c r="AW163" s="240"/>
+      <c r="AX163" s="209"/>
       <c r="AY163" s="179"/>
     </row>
     <row r="164" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="196"/>
+      <c r="A164" s="194"/>
       <c r="B164" s="191"/>
       <c r="C164" s="215"/>
       <c r="D164" s="169"/>
@@ -16310,16 +16310,16 @@
       <c r="AQ164" s="148"/>
       <c r="AR164" s="120"/>
       <c r="AS164" s="120"/>
-      <c r="AT164" s="225"/>
-      <c r="AU164" s="211"/>
+      <c r="AT164" s="240"/>
+      <c r="AU164" s="209"/>
       <c r="AV164" s="179"/>
-      <c r="AW164" s="225"/>
-      <c r="AX164" s="211"/>
+      <c r="AW164" s="240"/>
+      <c r="AX164" s="209"/>
       <c r="AY164" s="179"/>
     </row>
     <row r="165" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="196"/>
-      <c r="B165" s="192"/>
+      <c r="A165" s="194"/>
+      <c r="B165" s="212"/>
       <c r="C165" s="216"/>
       <c r="D165" s="156"/>
       <c r="E165" s="184"/>
@@ -16371,8 +16371,8 @@
       <c r="AY165" s="139"/>
     </row>
     <row r="166" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="196"/>
-      <c r="B166" s="190">
+      <c r="A166" s="194"/>
+      <c r="B166" s="211">
         <v>2</v>
       </c>
       <c r="C166" s="164" t="s">
@@ -16385,7 +16385,7 @@
         <v>57</v>
       </c>
       <c r="F166" s="168" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G166" s="169" t="s">
         <v>308</v>
@@ -16403,22 +16403,22 @@
         <v>118</v>
       </c>
       <c r="L166" s="168" t="s">
+        <v>803</v>
+      </c>
+      <c r="M166" s="119" t="s">
         <v>804</v>
       </c>
-      <c r="M166" s="119" t="s">
+      <c r="N166" s="119" t="s">
         <v>805</v>
       </c>
-      <c r="N166" s="119" t="s">
+      <c r="O166" s="119" t="s">
         <v>806</v>
       </c>
-      <c r="O166" s="119" t="s">
+      <c r="P166" s="133" t="s">
         <v>807</v>
       </c>
-      <c r="P166" s="133" t="s">
+      <c r="Q166" s="119" t="s">
         <v>808</v>
-      </c>
-      <c r="Q166" s="119" t="s">
-        <v>809</v>
       </c>
       <c r="R166" s="120" t="s">
         <v>124</v>
@@ -16430,79 +16430,79 @@
         <v>126</v>
       </c>
       <c r="U166" s="119" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="V166" s="119" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="W166" s="120" t="s">
         <v>127</v>
       </c>
       <c r="X166" s="119" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="Y166" s="119" t="s">
         <v>368</v>
       </c>
       <c r="Z166" s="120" t="s">
+        <v>646</v>
+      </c>
+      <c r="AA166" s="119" t="s">
+        <v>566</v>
+      </c>
+      <c r="AB166" s="176" t="s">
         <v>647</v>
-      </c>
-      <c r="AA166" s="119" t="s">
-        <v>567</v>
-      </c>
-      <c r="AB166" s="176" t="s">
-        <v>648</v>
       </c>
       <c r="AC166" s="119" t="s">
         <v>120</v>
       </c>
       <c r="AD166" s="119" t="s">
+        <v>811</v>
+      </c>
+      <c r="AE166" s="119" t="s">
         <v>812</v>
-      </c>
-      <c r="AE166" s="119" t="s">
-        <v>813</v>
       </c>
       <c r="AF166" s="119" t="s">
         <v>83</v>
       </c>
       <c r="AG166" s="119" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AH166" s="119" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AI166" s="119" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AJ166" s="119" t="s">
         <v>191</v>
       </c>
       <c r="AK166" s="119" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AL166" s="119" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AM166" s="141" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN166" s="119" t="s">
         <v>815</v>
       </c>
-      <c r="AN166" s="119" t="s">
+      <c r="AO166" s="141" t="s">
         <v>816</v>
       </c>
-      <c r="AO166" s="141" t="s">
+      <c r="AP166" s="139" t="s">
         <v>817</v>
       </c>
-      <c r="AP166" s="139" t="s">
+      <c r="AQ166" s="119" t="s">
         <v>818</v>
       </c>
-      <c r="AQ166" s="119" t="s">
+      <c r="AR166" s="120" t="s">
         <v>819</v>
       </c>
-      <c r="AR166" s="120" t="s">
-        <v>820</v>
-      </c>
       <c r="AS166" s="119" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AT166" s="120" t="s">
         <v>147</v>
@@ -16511,7 +16511,7 @@
         <v>262</v>
       </c>
       <c r="AV166" s="120" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AW166" s="138" t="s">
         <v>203</v>
@@ -16524,13 +16524,13 @@
       </c>
     </row>
     <row r="167" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="196"/>
+      <c r="A167" s="194"/>
       <c r="B167" s="191"/>
       <c r="C167" s="241"/>
-      <c r="D167" s="201"/>
-      <c r="E167" s="198"/>
+      <c r="D167" s="198"/>
+      <c r="E167" s="189"/>
       <c r="F167" s="168" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G167" s="169"/>
       <c r="H167" s="122"/>
@@ -16541,7 +16541,7 @@
         <v>392</v>
       </c>
       <c r="M167" s="119" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="N167" s="178"/>
       <c r="O167" s="119" t="s">
@@ -16553,7 +16553,7 @@
       <c r="S167" s="181"/>
       <c r="T167" s="178"/>
       <c r="U167" s="119" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V167" s="178"/>
       <c r="W167" s="120"/>
@@ -16561,7 +16561,7 @@
       <c r="Y167" s="119"/>
       <c r="Z167" s="120"/>
       <c r="AA167" s="119" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AB167" s="176" t="s">
         <v>342</v>
@@ -16582,24 +16582,24 @@
       <c r="AN167" s="178"/>
       <c r="AO167" s="141"/>
       <c r="AP167" s="139" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AQ167" s="178"/>
       <c r="AR167" s="120"/>
       <c r="AS167" s="119" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AT167" s="120"/>
       <c r="AU167" s="120"/>
       <c r="AV167" s="120" t="s">
-        <v>827</v>
-      </c>
-      <c r="AW167" s="224"/>
+        <v>826</v>
+      </c>
+      <c r="AW167" s="239"/>
       <c r="AX167" s="185"/>
       <c r="AY167" s="185"/>
     </row>
     <row r="168" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="196"/>
+      <c r="A168" s="194"/>
       <c r="B168" s="191"/>
       <c r="C168" s="215"/>
       <c r="D168" s="179"/>
@@ -16610,9 +16610,9 @@
       <c r="I168" s="120"/>
       <c r="J168" s="179"/>
       <c r="K168" s="179"/>
-      <c r="L168" s="201"/>
+      <c r="L168" s="198"/>
       <c r="M168" s="119" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="N168" s="179"/>
       <c r="O168" s="178"/>
@@ -16629,7 +16629,7 @@
       <c r="Z168" s="120"/>
       <c r="AA168" s="178"/>
       <c r="AB168" s="176" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AC168" s="179"/>
       <c r="AD168" s="179"/>
@@ -16645,7 +16645,7 @@
       <c r="AN168" s="179"/>
       <c r="AO168" s="141"/>
       <c r="AP168" s="139" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AQ168" s="179"/>
       <c r="AR168" s="120"/>
@@ -16653,12 +16653,12 @@
       <c r="AT168" s="120"/>
       <c r="AU168" s="120"/>
       <c r="AV168" s="120"/>
-      <c r="AW168" s="225"/>
+      <c r="AW168" s="240"/>
       <c r="AX168" s="186"/>
       <c r="AY168" s="186"/>
     </row>
     <row r="169" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="196"/>
+      <c r="A169" s="194"/>
       <c r="B169" s="191"/>
       <c r="C169" s="215"/>
       <c r="D169" s="179"/>
@@ -16685,7 +16685,7 @@
       <c r="Y169" s="120"/>
       <c r="Z169" s="120"/>
       <c r="AA169" s="179"/>
-      <c r="AB169" s="234"/>
+      <c r="AB169" s="232"/>
       <c r="AC169" s="179"/>
       <c r="AD169" s="179"/>
       <c r="AE169" s="179"/>
@@ -16706,12 +16706,12 @@
       <c r="AT169" s="120"/>
       <c r="AU169" s="120"/>
       <c r="AV169" s="180"/>
-      <c r="AW169" s="225"/>
+      <c r="AW169" s="240"/>
       <c r="AX169" s="186"/>
       <c r="AY169" s="186"/>
     </row>
     <row r="170" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="196"/>
+      <c r="A170" s="194"/>
       <c r="B170" s="191"/>
       <c r="C170" s="215"/>
       <c r="D170" s="179"/>
@@ -16759,12 +16759,12 @@
       <c r="AT170" s="120"/>
       <c r="AU170" s="120"/>
       <c r="AV170" s="179"/>
-      <c r="AW170" s="225"/>
+      <c r="AW170" s="240"/>
       <c r="AX170" s="186"/>
       <c r="AY170" s="186"/>
     </row>
     <row r="171" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="196"/>
+      <c r="A171" s="194"/>
       <c r="B171" s="191"/>
       <c r="C171" s="215"/>
       <c r="D171" s="179"/>
@@ -16817,7 +16817,7 @@
       <c r="AY171" s="121"/>
     </row>
     <row r="172" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="196"/>
+      <c r="A172" s="194"/>
       <c r="B172" s="191"/>
       <c r="C172" s="215"/>
       <c r="D172" s="179"/>
@@ -16870,8 +16870,8 @@
       <c r="AY172" s="120"/>
     </row>
     <row r="173" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="196"/>
-      <c r="B173" s="192"/>
+      <c r="A173" s="194"/>
+      <c r="B173" s="212"/>
       <c r="C173" s="216"/>
       <c r="D173" s="184"/>
       <c r="E173" s="184"/>
@@ -16923,30 +16923,30 @@
       <c r="AY173" s="139"/>
     </row>
     <row r="174" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="196"/>
-      <c r="B174" s="190">
+      <c r="A174" s="194"/>
+      <c r="B174" s="211">
         <v>3</v>
       </c>
       <c r="C174" s="159" t="s">
         <v>59</v>
       </c>
       <c r="D174" s="122" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E174" s="122" t="s">
         <v>61</v>
       </c>
       <c r="F174" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G174" s="168" t="s">
         <v>166</v>
       </c>
       <c r="H174" s="122" t="s">
+        <v>832</v>
+      </c>
+      <c r="I174" s="168" t="s">
         <v>833</v>
-      </c>
-      <c r="I174" s="168" t="s">
-        <v>834</v>
       </c>
       <c r="J174" s="119" t="s">
         <v>118</v>
@@ -16955,40 +16955,40 @@
         <v>64</v>
       </c>
       <c r="L174" s="123" t="s">
+        <v>834</v>
+      </c>
+      <c r="M174" s="119" t="s">
         <v>835</v>
-      </c>
-      <c r="M174" s="119" t="s">
-        <v>836</v>
       </c>
       <c r="N174" s="119" t="s">
         <v>63</v>
       </c>
       <c r="O174" s="119" t="s">
+        <v>836</v>
+      </c>
+      <c r="P174" s="119" t="s">
         <v>837</v>
-      </c>
-      <c r="P174" s="119" t="s">
-        <v>838</v>
       </c>
       <c r="Q174" s="119" t="s">
         <v>133</v>
       </c>
       <c r="R174" s="133" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="S174" s="28" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="T174" s="119" t="s">
         <v>73</v>
       </c>
       <c r="U174" s="120" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="V174" s="119" t="s">
         <v>75</v>
       </c>
       <c r="W174" s="119" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X174" s="119" t="s">
         <v>475</v>
@@ -16997,111 +16997,111 @@
         <v>77</v>
       </c>
       <c r="Z174" s="119" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AA174" s="119" t="s">
         <v>414</v>
       </c>
       <c r="AB174" s="119" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AC174" s="119" t="s">
+        <v>841</v>
+      </c>
+      <c r="AD174" s="119" t="s">
         <v>842</v>
       </c>
-      <c r="AD174" s="119" t="s">
+      <c r="AE174" s="119" t="s">
         <v>843</v>
-      </c>
-      <c r="AE174" s="119" t="s">
-        <v>844</v>
       </c>
       <c r="AF174" s="119" t="s">
         <v>84</v>
       </c>
       <c r="AG174" s="119" t="s">
+        <v>844</v>
+      </c>
+      <c r="AH174" s="119" t="s">
         <v>845</v>
       </c>
-      <c r="AH174" s="119" t="s">
-        <v>846</v>
-      </c>
       <c r="AI174" s="119" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AJ174" s="119" t="s">
         <v>137</v>
       </c>
       <c r="AK174" s="140" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AL174" s="120" t="s">
         <v>139</v>
       </c>
       <c r="AM174" s="119" t="s">
+        <v>847</v>
+      </c>
+      <c r="AN174" s="119" t="s">
         <v>848</v>
       </c>
-      <c r="AN174" s="119" t="s">
+      <c r="AO174" s="120" t="s">
         <v>849</v>
       </c>
-      <c r="AO174" s="120" t="s">
+      <c r="AP174" s="120" t="s">
         <v>850</v>
       </c>
-      <c r="AP174" s="120" t="s">
+      <c r="AQ174" s="119" t="s">
         <v>851</v>
-      </c>
-      <c r="AQ174" s="119" t="s">
-        <v>852</v>
       </c>
       <c r="AR174" s="120" t="s">
         <v>92</v>
       </c>
       <c r="AS174" s="119" t="s">
+        <v>852</v>
+      </c>
+      <c r="AT174" s="120" t="s">
         <v>853</v>
       </c>
-      <c r="AT174" s="120" t="s">
+      <c r="AU174" s="120" t="s">
         <v>854</v>
       </c>
-      <c r="AU174" s="120" t="s">
+      <c r="AV174" s="120" t="s">
         <v>855</v>
       </c>
-      <c r="AV174" s="120" t="s">
+      <c r="AW174" s="119" t="s">
         <v>856</v>
       </c>
-      <c r="AW174" s="119" t="s">
+      <c r="AX174" s="138" t="s">
         <v>857</v>
       </c>
-      <c r="AX174" s="138" t="s">
+      <c r="AY174" s="119" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="175" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="194"/>
+      <c r="B175" s="191"/>
+      <c r="C175" s="224"/>
+      <c r="D175" s="198"/>
+      <c r="E175" s="198"/>
+      <c r="F175" s="119" t="s">
         <v>858</v>
-      </c>
-      <c r="AY174" s="119" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="175" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="196"/>
-      <c r="B175" s="191"/>
-      <c r="C175" s="226"/>
-      <c r="D175" s="201"/>
-      <c r="E175" s="201"/>
-      <c r="F175" s="119" t="s">
-        <v>859</v>
       </c>
       <c r="G175" s="122"/>
       <c r="H175" s="122" t="s">
+        <v>859</v>
+      </c>
+      <c r="I175" s="168" t="s">
         <v>860</v>
-      </c>
-      <c r="I175" s="168" t="s">
-        <v>861</v>
       </c>
       <c r="J175" s="178"/>
       <c r="K175" s="178"/>
       <c r="L175" s="123" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M175" s="119" t="s">
         <v>162</v>
       </c>
       <c r="N175" s="178"/>
       <c r="O175" s="119" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="P175" s="178"/>
       <c r="Q175" s="119" t="s">
@@ -17117,23 +17117,23 @@
       </c>
       <c r="V175" s="178"/>
       <c r="W175" s="119" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="X175" s="119"/>
       <c r="Y175" s="119" t="s">
         <v>162</v>
       </c>
       <c r="Z175" s="119" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="AA175" s="178"/>
       <c r="AB175" s="178"/>
       <c r="AC175" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="AD175" s="178"/>
       <c r="AE175" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="AF175" s="119"/>
       <c r="AG175" s="119"/>
@@ -17143,10 +17143,10 @@
       <c r="AK175" s="178"/>
       <c r="AL175" s="120"/>
       <c r="AM175" s="119" t="s">
+        <v>867</v>
+      </c>
+      <c r="AN175" s="119" t="s">
         <v>868</v>
-      </c>
-      <c r="AN175" s="119" t="s">
-        <v>869</v>
       </c>
       <c r="AO175" s="120" t="s">
         <v>450</v>
@@ -17155,55 +17155,55 @@
       <c r="AQ175" s="178"/>
       <c r="AR175" s="120"/>
       <c r="AS175" s="119" t="s">
+        <v>869</v>
+      </c>
+      <c r="AT175" s="120" t="s">
         <v>870</v>
-      </c>
-      <c r="AT175" s="120" t="s">
-        <v>871</v>
       </c>
       <c r="AU175" s="120"/>
       <c r="AV175" s="120" t="s">
+        <v>871</v>
+      </c>
+      <c r="AW175" s="119" t="s">
         <v>872</v>
       </c>
-      <c r="AW175" s="119" t="s">
+      <c r="AX175" s="138" t="s">
         <v>873</v>
       </c>
-      <c r="AX175" s="138" t="s">
-        <v>874</v>
-      </c>
       <c r="AY175" s="119"/>
     </row>
     <row r="176" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="196"/>
+      <c r="A176" s="194"/>
       <c r="B176" s="191"/>
       <c r="C176" s="215"/>
       <c r="D176" s="179"/>
       <c r="E176" s="179"/>
-      <c r="F176" s="198"/>
+      <c r="F176" s="189"/>
       <c r="G176" s="123"/>
       <c r="H176" s="122"/>
       <c r="I176" s="122"/>
       <c r="J176" s="179"/>
       <c r="K176" s="179"/>
       <c r="L176" s="123" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="M176" s="178"/>
       <c r="N176" s="179"/>
-      <c r="O176" s="198"/>
+      <c r="O176" s="189"/>
       <c r="P176" s="179"/>
       <c r="Q176" s="178"/>
       <c r="R176" s="179"/>
       <c r="S176" s="218"/>
       <c r="T176" s="179"/>
-      <c r="U176" s="258"/>
+      <c r="U176" s="260"/>
       <c r="V176" s="179"/>
       <c r="W176" s="119" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="X176" s="120"/>
       <c r="Y176" s="119"/>
       <c r="Z176" s="119" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AA176" s="179"/>
       <c r="AB176" s="179"/>
@@ -17227,18 +17227,18 @@
       <c r="AT176" s="180"/>
       <c r="AU176" s="120"/>
       <c r="AV176" s="120" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AW176" s="119"/>
       <c r="AX176" s="138" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AY176" s="119" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="177" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="196"/>
+      <c r="A177" s="194"/>
       <c r="B177" s="191"/>
       <c r="C177" s="215"/>
       <c r="D177" s="179"/>
@@ -17291,7 +17291,7 @@
       <c r="AY177" s="185"/>
     </row>
     <row r="178" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="196"/>
+      <c r="A178" s="194"/>
       <c r="B178" s="191"/>
       <c r="C178" s="215"/>
       <c r="D178" s="179"/>
@@ -17340,11 +17340,11 @@
       <c r="AU178" s="120"/>
       <c r="AV178" s="179"/>
       <c r="AW178" s="180"/>
-      <c r="AX178" s="189"/>
+      <c r="AX178" s="202"/>
       <c r="AY178" s="186"/>
     </row>
     <row r="179" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="196"/>
+      <c r="A179" s="194"/>
       <c r="B179" s="191"/>
       <c r="C179" s="215"/>
       <c r="D179" s="179"/>
@@ -17397,7 +17397,7 @@
       <c r="AY179" s="186"/>
     </row>
     <row r="180" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="196"/>
+      <c r="A180" s="194"/>
       <c r="B180" s="191"/>
       <c r="C180" s="215"/>
       <c r="D180" s="179"/>
@@ -17450,8 +17450,8 @@
       <c r="AY180" s="186"/>
     </row>
     <row r="181" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="196"/>
-      <c r="B181" s="192"/>
+      <c r="A181" s="194"/>
+      <c r="B181" s="212"/>
       <c r="C181" s="216"/>
       <c r="D181" s="184"/>
       <c r="E181" s="184"/>
@@ -17503,85 +17503,85 @@
       <c r="AY181" s="139"/>
     </row>
     <row r="182" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="196"/>
-      <c r="B182" s="190">
+      <c r="A182" s="194"/>
+      <c r="B182" s="211">
         <v>4</v>
       </c>
       <c r="C182" s="164" t="s">
+        <v>878</v>
+      </c>
+      <c r="D182" s="51" t="s">
         <v>879</v>
       </c>
-      <c r="D182" s="51" t="s">
+      <c r="E182" s="122" t="s">
         <v>880</v>
-      </c>
-      <c r="E182" s="122" t="s">
-        <v>881</v>
       </c>
       <c r="F182" s="45" t="s">
         <v>117</v>
       </c>
       <c r="G182" s="128" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H182" s="122" t="s">
         <v>67</v>
       </c>
       <c r="I182" s="119" t="s">
+        <v>882</v>
+      </c>
+      <c r="J182" s="119" t="s">
         <v>883</v>
       </c>
-      <c r="J182" s="119" t="s">
+      <c r="K182" s="119" t="s">
         <v>884</v>
       </c>
-      <c r="K182" s="119" t="s">
+      <c r="L182" s="119" t="s">
         <v>885</v>
       </c>
-      <c r="L182" s="119" t="s">
+      <c r="M182" s="119" t="s">
         <v>886</v>
       </c>
-      <c r="M182" s="119" t="s">
+      <c r="N182" s="119" t="s">
         <v>887</v>
       </c>
-      <c r="N182" s="119" t="s">
+      <c r="O182" s="133" t="s">
         <v>888</v>
       </c>
-      <c r="O182" s="133" t="s">
+      <c r="P182" s="119" t="s">
         <v>889</v>
       </c>
-      <c r="P182" s="119" t="s">
+      <c r="Q182" s="119" t="s">
         <v>890</v>
       </c>
-      <c r="Q182" s="119" t="s">
+      <c r="R182" s="133" t="s">
         <v>891</v>
-      </c>
-      <c r="R182" s="133" t="s">
-        <v>892</v>
       </c>
       <c r="S182" s="120"/>
       <c r="T182" s="120" t="s">
+        <v>892</v>
+      </c>
+      <c r="U182" s="120" t="s">
         <v>893</v>
       </c>
-      <c r="U182" s="120" t="s">
+      <c r="V182" s="120" t="s">
         <v>894</v>
       </c>
-      <c r="V182" s="120" t="s">
+      <c r="W182" s="119" t="s">
         <v>895</v>
       </c>
-      <c r="W182" s="119" t="s">
+      <c r="X182" s="119" t="s">
         <v>896</v>
       </c>
-      <c r="X182" s="119" t="s">
+      <c r="Y182" s="119" t="s">
         <v>897</v>
       </c>
-      <c r="Y182" s="119" t="s">
+      <c r="Z182" s="119" t="s">
         <v>898</v>
       </c>
-      <c r="Z182" s="119" t="s">
+      <c r="AA182" s="119" t="s">
         <v>899</v>
       </c>
-      <c r="AA182" s="119" t="s">
+      <c r="AB182" s="119" t="s">
         <v>900</v>
-      </c>
-      <c r="AB182" s="119" t="s">
-        <v>901</v>
       </c>
       <c r="AC182" s="119" t="s">
         <v>300</v>
@@ -17590,66 +17590,66 @@
         <v>481</v>
       </c>
       <c r="AE182" s="119" t="s">
+        <v>901</v>
+      </c>
+      <c r="AF182" s="119" t="s">
         <v>902</v>
       </c>
-      <c r="AF182" s="119" t="s">
+      <c r="AG182" s="119" t="s">
         <v>903</v>
-      </c>
-      <c r="AG182" s="119" t="s">
-        <v>904</v>
       </c>
       <c r="AH182" s="119"/>
       <c r="AI182" s="119"/>
       <c r="AJ182" s="140" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="AK182" s="178"/>
       <c r="AL182" s="119" t="s">
+        <v>905</v>
+      </c>
+      <c r="AM182" s="141" t="s">
         <v>906</v>
-      </c>
-      <c r="AM182" s="141" t="s">
-        <v>907</v>
       </c>
       <c r="AN182" s="119" t="s">
         <v>256</v>
       </c>
       <c r="AO182" s="141" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AP182" s="119" t="s">
         <v>91</v>
       </c>
       <c r="AQ182" s="120" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AR182" s="120" t="s">
         <v>92</v>
       </c>
       <c r="AS182" s="142" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="AT182" s="178"/>
       <c r="AU182" s="119" t="s">
         <v>431</v>
       </c>
       <c r="AV182" s="119" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AW182" s="178"/>
       <c r="AX182" s="178"/>
       <c r="AY182" s="178"/>
     </row>
     <row r="183" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="196"/>
+      <c r="A183" s="194"/>
       <c r="B183" s="191"/>
       <c r="C183" s="164" t="s">
+        <v>911</v>
+      </c>
+      <c r="D183" s="51" t="s">
         <v>912</v>
       </c>
-      <c r="D183" s="51" t="s">
+      <c r="E183" s="122" t="s">
         <v>913</v>
-      </c>
-      <c r="E183" s="122" t="s">
-        <v>914</v>
       </c>
       <c r="F183" s="128"/>
       <c r="G183" s="128" t="s">
@@ -17660,29 +17660,29 @@
         <v>295</v>
       </c>
       <c r="J183" s="119" t="s">
+        <v>914</v>
+      </c>
+      <c r="K183" s="119" t="s">
         <v>915</v>
-      </c>
-      <c r="K183" s="119" t="s">
-        <v>916</v>
       </c>
       <c r="L183" s="178"/>
       <c r="M183" s="119" t="s">
+        <v>916</v>
+      </c>
+      <c r="N183" s="119" t="s">
         <v>917</v>
       </c>
-      <c r="N183" s="119" t="s">
+      <c r="O183" s="119" t="s">
         <v>918</v>
       </c>
-      <c r="O183" s="119" t="s">
+      <c r="P183" s="119" t="s">
         <v>919</v>
-      </c>
-      <c r="P183" s="119" t="s">
-        <v>920</v>
       </c>
       <c r="Q183" s="178"/>
       <c r="R183" s="178"/>
       <c r="S183" s="120"/>
       <c r="T183" s="120" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="U183" s="126"/>
       <c r="V183" s="120"/>
@@ -17691,13 +17691,13 @@
       <c r="Y183" s="119"/>
       <c r="Z183" s="119"/>
       <c r="AA183" s="119" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB183" s="119" t="s">
         <v>922</v>
       </c>
-      <c r="AB183" s="119" t="s">
+      <c r="AC183" s="119" t="s">
         <v>923</v>
-      </c>
-      <c r="AC183" s="119" t="s">
-        <v>924</v>
       </c>
       <c r="AD183" s="178"/>
       <c r="AE183" s="178"/>
@@ -17711,17 +17711,17 @@
       <c r="AK183" s="179"/>
       <c r="AL183" s="178"/>
       <c r="AM183" s="141" t="s">
+        <v>924</v>
+      </c>
+      <c r="AN183" s="119" t="s">
         <v>925</v>
-      </c>
-      <c r="AN183" s="119" t="s">
-        <v>926</v>
       </c>
       <c r="AO183" s="141"/>
       <c r="AP183" s="119" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AQ183" s="120" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AR183" s="120"/>
       <c r="AS183" s="178"/>
@@ -17733,14 +17733,14 @@
       <c r="AY183" s="179"/>
     </row>
     <row r="184" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="196"/>
+      <c r="A184" s="194"/>
       <c r="B184" s="191"/>
       <c r="C184" s="241"/>
-      <c r="D184" s="201"/>
-      <c r="E184" s="201"/>
+      <c r="D184" s="198"/>
+      <c r="E184" s="198"/>
       <c r="F184" s="129"/>
       <c r="G184" s="128" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H184" s="123"/>
       <c r="I184" s="119"/>
@@ -17749,7 +17749,7 @@
       <c r="L184" s="179"/>
       <c r="M184" s="178"/>
       <c r="N184" s="119" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="O184" s="14"/>
       <c r="P184" s="14"/>
@@ -17757,7 +17757,7 @@
       <c r="R184" s="179"/>
       <c r="S184" s="120"/>
       <c r="T184" s="120" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="U184" s="126"/>
       <c r="V184" s="120"/>
@@ -17786,7 +17786,7 @@
       <c r="AO184" s="141"/>
       <c r="AP184" s="178"/>
       <c r="AQ184" s="120" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="AR184" s="120"/>
       <c r="AS184" s="179"/>
@@ -17798,7 +17798,7 @@
       <c r="AY184" s="179"/>
     </row>
     <row r="185" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="196"/>
+      <c r="A185" s="194"/>
       <c r="B185" s="191"/>
       <c r="C185" s="215"/>
       <c r="D185" s="179"/>
@@ -17811,7 +17811,7 @@
       <c r="K185" s="179"/>
       <c r="L185" s="179"/>
       <c r="M185" s="179"/>
-      <c r="N185" s="198"/>
+      <c r="N185" s="189"/>
       <c r="O185" s="14"/>
       <c r="P185" s="14"/>
       <c r="Q185" s="179"/>
@@ -17851,7 +17851,7 @@
       <c r="AY185" s="179"/>
     </row>
     <row r="186" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="196"/>
+      <c r="A186" s="194"/>
       <c r="B186" s="191"/>
       <c r="C186" s="215"/>
       <c r="D186" s="179"/>
@@ -17893,7 +17893,7 @@
       <c r="AN186" s="179"/>
       <c r="AO186" s="141"/>
       <c r="AP186" s="179"/>
-      <c r="AQ186" s="189"/>
+      <c r="AQ186" s="202"/>
       <c r="AR186" s="120"/>
       <c r="AS186" s="179"/>
       <c r="AT186" s="179"/>
@@ -17904,7 +17904,7 @@
       <c r="AY186" s="179"/>
     </row>
     <row r="187" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="196"/>
+      <c r="A187" s="194"/>
       <c r="B187" s="191"/>
       <c r="C187" s="215"/>
       <c r="D187" s="179"/>
@@ -17914,7 +17914,7 @@
       <c r="H187" s="123"/>
       <c r="I187" s="120"/>
       <c r="J187" s="179"/>
-      <c r="K187" s="250"/>
+      <c r="K187" s="254"/>
       <c r="L187" s="121"/>
       <c r="M187" s="179"/>
       <c r="N187" s="179"/>
@@ -17957,7 +17957,7 @@
       <c r="AY187" s="134"/>
     </row>
     <row r="188" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="196"/>
+      <c r="A188" s="194"/>
       <c r="B188" s="191"/>
       <c r="C188" s="215"/>
       <c r="D188" s="179"/>
@@ -18010,7 +18010,7 @@
       <c r="AY188" s="134"/>
     </row>
     <row r="189" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="196"/>
+      <c r="A189" s="194"/>
       <c r="B189" s="191"/>
       <c r="C189" s="215"/>
       <c r="D189" s="179"/>
@@ -18063,8 +18063,8 @@
       <c r="AY189" s="134"/>
     </row>
     <row r="190" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="196"/>
-      <c r="B190" s="192"/>
+      <c r="A190" s="194"/>
+      <c r="B190" s="212"/>
       <c r="C190" s="216"/>
       <c r="D190" s="184"/>
       <c r="E190" s="184"/>
@@ -18116,29 +18116,29 @@
       <c r="AY190" s="173"/>
     </row>
     <row r="191" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="196"/>
-      <c r="B191" s="190">
+      <c r="A191" s="194"/>
+      <c r="B191" s="211">
         <v>5</v>
       </c>
-      <c r="C191" s="226"/>
-      <c r="D191" s="198"/>
-      <c r="E191" s="198"/>
+      <c r="C191" s="224"/>
+      <c r="D191" s="189"/>
+      <c r="E191" s="189"/>
       <c r="F191" s="119"/>
       <c r="G191" s="147"/>
       <c r="H191" s="140" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I191" s="120"/>
       <c r="J191" s="140" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="K191" s="178"/>
       <c r="L191" s="178"/>
       <c r="M191" s="178"/>
       <c r="N191" s="178"/>
       <c r="O191" s="178"/>
-      <c r="P191" s="227"/>
-      <c r="Q191" s="227"/>
+      <c r="P191" s="225"/>
+      <c r="Q191" s="225"/>
       <c r="R191" s="178"/>
       <c r="S191" s="178"/>
       <c r="T191" s="181"/>
@@ -18149,47 +18149,47 @@
       <c r="W191" s="147"/>
       <c r="X191" s="120"/>
       <c r="Y191" s="119" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="Z191" s="119"/>
       <c r="AA191" s="178"/>
       <c r="AB191" s="120"/>
       <c r="AC191" s="178"/>
       <c r="AD191" s="120" t="s">
+        <v>934</v>
+      </c>
+      <c r="AE191" s="119" t="s">
         <v>935</v>
       </c>
-      <c r="AE191" s="119" t="s">
-        <v>936</v>
-      </c>
-      <c r="AF191" s="227"/>
+      <c r="AF191" s="225"/>
       <c r="AG191" s="178"/>
       <c r="AH191" s="178"/>
       <c r="AI191" s="119"/>
       <c r="AJ191" s="178"/>
       <c r="AK191" s="119"/>
       <c r="AL191" s="119" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AM191" s="119"/>
       <c r="AN191" s="119"/>
       <c r="AO191" s="142"/>
       <c r="AP191" s="119" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AQ191" s="141" t="s">
-        <v>578</v>
-      </c>
-      <c r="AR191" s="224"/>
+        <v>577</v>
+      </c>
+      <c r="AR191" s="239"/>
       <c r="AS191" s="185"/>
       <c r="AT191" s="185"/>
       <c r="AU191" s="185"/>
-      <c r="AV191" s="233"/>
+      <c r="AV191" s="231"/>
       <c r="AW191" s="120"/>
-      <c r="AX191" s="224"/>
+      <c r="AX191" s="239"/>
       <c r="AY191" s="185"/>
     </row>
     <row r="192" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="196"/>
+      <c r="A192" s="194"/>
       <c r="B192" s="191"/>
       <c r="C192" s="215"/>
       <c r="D192" s="179"/>
@@ -18220,7 +18220,7 @@
       <c r="AC192" s="179"/>
       <c r="AD192" s="120"/>
       <c r="AE192" s="119" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AF192" s="179"/>
       <c r="AG192" s="179"/>
@@ -18233,20 +18233,20 @@
       <c r="AN192" s="119"/>
       <c r="AO192" s="142"/>
       <c r="AP192" s="119" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AQ192" s="141"/>
-      <c r="AR192" s="225"/>
+      <c r="AR192" s="240"/>
       <c r="AS192" s="186"/>
       <c r="AT192" s="186"/>
       <c r="AU192" s="186"/>
-      <c r="AV192" s="211"/>
+      <c r="AV192" s="209"/>
       <c r="AW192" s="120"/>
-      <c r="AX192" s="225"/>
+      <c r="AX192" s="240"/>
       <c r="AY192" s="186"/>
     </row>
     <row r="193" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="196"/>
+      <c r="A193" s="194"/>
       <c r="B193" s="191"/>
       <c r="C193" s="215"/>
       <c r="D193" s="179"/>
@@ -18289,17 +18289,17 @@
       <c r="AO193" s="120"/>
       <c r="AP193" s="120"/>
       <c r="AQ193" s="134"/>
-      <c r="AR193" s="225"/>
+      <c r="AR193" s="240"/>
       <c r="AS193" s="186"/>
       <c r="AT193" s="186"/>
       <c r="AU193" s="186"/>
-      <c r="AV193" s="211"/>
+      <c r="AV193" s="209"/>
       <c r="AW193" s="131"/>
-      <c r="AX193" s="225"/>
+      <c r="AX193" s="240"/>
       <c r="AY193" s="186"/>
     </row>
     <row r="194" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="196"/>
+      <c r="A194" s="194"/>
       <c r="B194" s="191"/>
       <c r="C194" s="215"/>
       <c r="D194" s="179"/>
@@ -18346,13 +18346,13 @@
       <c r="AS194" s="137"/>
       <c r="AT194" s="137"/>
       <c r="AU194" s="186"/>
-      <c r="AV194" s="211"/>
+      <c r="AV194" s="209"/>
       <c r="AW194" s="120"/>
-      <c r="AX194" s="225"/>
+      <c r="AX194" s="240"/>
       <c r="AY194" s="186"/>
     </row>
     <row r="195" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="196"/>
+      <c r="A195" s="194"/>
       <c r="B195" s="191"/>
       <c r="C195" s="215"/>
       <c r="D195" s="179"/>
@@ -18405,8 +18405,8 @@
       <c r="AY195" s="146"/>
     </row>
     <row r="196" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="196"/>
-      <c r="B196" s="192"/>
+      <c r="A196" s="194"/>
+      <c r="B196" s="212"/>
       <c r="C196" s="216"/>
       <c r="D196" s="184"/>
       <c r="E196" s="184"/>
@@ -18458,8 +18458,8 @@
       <c r="AY196" s="84"/>
     </row>
     <row r="197" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="196"/>
-      <c r="B197" s="190">
+      <c r="A197" s="194"/>
+      <c r="B197" s="211">
         <v>6</v>
       </c>
       <c r="C197" s="223"/>
@@ -18513,7 +18513,7 @@
       <c r="AY197" s="145"/>
     </row>
     <row r="198" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="196"/>
+      <c r="A198" s="194"/>
       <c r="B198" s="191"/>
       <c r="C198" s="215"/>
       <c r="D198" s="120"/>
@@ -18566,7 +18566,7 @@
       <c r="AY198" s="146"/>
     </row>
     <row r="199" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="196"/>
+      <c r="A199" s="194"/>
       <c r="B199" s="191"/>
       <c r="C199" s="215"/>
       <c r="D199" s="120"/>
@@ -18619,7 +18619,7 @@
       <c r="AY199" s="146"/>
     </row>
     <row r="200" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="196"/>
+      <c r="A200" s="194"/>
       <c r="B200" s="191"/>
       <c r="C200" s="215"/>
       <c r="D200" s="120"/>
@@ -18672,8 +18672,8 @@
       <c r="AY200" s="146"/>
     </row>
     <row r="201" spans="1:51" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="196"/>
-      <c r="B201" s="192"/>
+      <c r="A201" s="194"/>
+      <c r="B201" s="212"/>
       <c r="C201" s="216"/>
       <c r="D201" s="120"/>
       <c r="E201" s="167"/>
@@ -18725,12 +18725,12 @@
       <c r="AY201" s="62"/>
     </row>
     <row r="202" spans="1:51" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="196"/>
-      <c r="B202" s="193">
+      <c r="A202" s="194"/>
+      <c r="B202" s="190">
         <v>7</v>
       </c>
-      <c r="C202" s="236"/>
-      <c r="D202" s="262"/>
+      <c r="C202" s="234"/>
+      <c r="D202" s="263"/>
       <c r="E202" s="140"/>
       <c r="F202" s="119"/>
       <c r="G202" s="119"/>
@@ -18780,7 +18780,7 @@
       <c r="AY202" s="145"/>
     </row>
     <row r="203" spans="1:51" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="196"/>
+      <c r="A203" s="194"/>
       <c r="B203" s="191"/>
       <c r="C203" s="215"/>
       <c r="D203" s="179"/>
@@ -18833,7 +18833,7 @@
       <c r="AY203" s="146"/>
     </row>
     <row r="204" spans="1:51" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="196"/>
+      <c r="A204" s="194"/>
       <c r="B204" s="191"/>
       <c r="C204" s="215"/>
       <c r="D204" s="179"/>
@@ -18886,7 +18886,7 @@
       <c r="AY204" s="146"/>
     </row>
     <row r="205" spans="1:51" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="196"/>
+      <c r="A205" s="194"/>
       <c r="B205" s="191"/>
       <c r="C205" s="215"/>
       <c r="D205" s="179"/>
@@ -18939,10 +18939,10 @@
       <c r="AY205" s="146"/>
     </row>
     <row r="206" spans="1:51" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="206"/>
-      <c r="B206" s="194"/>
-      <c r="C206" s="237"/>
-      <c r="D206" s="260"/>
+      <c r="A206" s="204"/>
+      <c r="B206" s="192"/>
+      <c r="C206" s="235"/>
+      <c r="D206" s="262"/>
       <c r="E206" s="63"/>
       <c r="F206" s="171"/>
       <c r="G206" s="85"/>
@@ -18992,20 +18992,20 @@
       <c r="AY206" s="67"/>
     </row>
     <row r="207" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="205" t="s">
+      <c r="A207" s="203" t="s">
+        <v>938</v>
+      </c>
+      <c r="B207" s="229">
+        <v>1</v>
+      </c>
+      <c r="C207" s="172" t="s">
         <v>939</v>
-      </c>
-      <c r="B207" s="231">
-        <v>1</v>
-      </c>
-      <c r="C207" s="172" t="s">
-        <v>940</v>
       </c>
       <c r="D207" s="124" t="s">
         <v>59</v>
       </c>
       <c r="E207" s="168" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F207" s="122" t="s">
         <v>61</v>
@@ -19020,16 +19020,16 @@
         <v>310</v>
       </c>
       <c r="J207" s="124" t="s">
+        <v>941</v>
+      </c>
+      <c r="K207" s="122" t="s">
         <v>942</v>
       </c>
-      <c r="K207" s="122" t="s">
+      <c r="L207" s="119" t="s">
         <v>943</v>
       </c>
-      <c r="L207" s="119" t="s">
+      <c r="M207" s="122" t="s">
         <v>944</v>
-      </c>
-      <c r="M207" s="122" t="s">
-        <v>945</v>
       </c>
       <c r="N207" s="123" t="s">
         <v>389</v>
@@ -19044,87 +19044,87 @@
         <v>362</v>
       </c>
       <c r="R207" s="133" t="s">
+        <v>945</v>
+      </c>
+      <c r="S207" s="133" t="s">
+        <v>642</v>
+      </c>
+      <c r="T207" s="119" t="s">
         <v>946</v>
       </c>
-      <c r="S207" s="133" t="s">
-        <v>643</v>
-      </c>
-      <c r="T207" s="119" t="s">
+      <c r="U207" s="119" t="s">
         <v>947</v>
       </c>
-      <c r="U207" s="119" t="s">
+      <c r="V207" s="30" t="s">
         <v>948</v>
-      </c>
-      <c r="V207" s="30" t="s">
-        <v>949</v>
       </c>
       <c r="W207" s="124" t="s">
         <v>126</v>
       </c>
       <c r="X207" s="120" t="s">
+        <v>949</v>
+      </c>
+      <c r="Y207" s="119" t="s">
         <v>950</v>
       </c>
-      <c r="Y207" s="119" t="s">
+      <c r="Z207" s="119" t="s">
+        <v>565</v>
+      </c>
+      <c r="AA207" s="119" t="s">
         <v>951</v>
-      </c>
-      <c r="Z207" s="119" t="s">
-        <v>566</v>
-      </c>
-      <c r="AA207" s="119" t="s">
-        <v>952</v>
       </c>
       <c r="AB207" s="119" t="s">
         <v>370</v>
       </c>
       <c r="AC207" s="120" t="s">
+        <v>952</v>
+      </c>
+      <c r="AD207" s="119" t="s">
         <v>953</v>
       </c>
-      <c r="AD207" s="119" t="s">
+      <c r="AE207" s="199"/>
+      <c r="AF207" s="119" t="s">
+        <v>844</v>
+      </c>
+      <c r="AG207" s="119" t="s">
         <v>954</v>
       </c>
-      <c r="AE207" s="202"/>
-      <c r="AF207" s="119" t="s">
-        <v>845</v>
-      </c>
-      <c r="AG207" s="119" t="s">
+      <c r="AH207" s="119" t="s">
         <v>955</v>
       </c>
-      <c r="AH207" s="119" t="s">
+      <c r="AI207" s="119" t="s">
+        <v>955</v>
+      </c>
+      <c r="AJ207" s="140" t="s">
         <v>956</v>
-      </c>
-      <c r="AI207" s="119" t="s">
-        <v>956</v>
-      </c>
-      <c r="AJ207" s="140" t="s">
-        <v>957</v>
       </c>
       <c r="AK207" s="182"/>
       <c r="AL207" s="182"/>
       <c r="AM207" s="182"/>
       <c r="AN207" s="119" t="s">
+        <v>957</v>
+      </c>
+      <c r="AO207" s="124" t="s">
         <v>958</v>
       </c>
-      <c r="AO207" s="124" t="s">
+      <c r="AP207" s="144" t="s">
         <v>959</v>
-      </c>
-      <c r="AP207" s="144" t="s">
-        <v>960</v>
       </c>
       <c r="AQ207" s="182"/>
       <c r="AR207" s="120" t="s">
         <v>334</v>
       </c>
       <c r="AS207" s="119" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AT207" s="120" t="s">
         <v>147</v>
       </c>
       <c r="AU207" s="120" t="s">
+        <v>960</v>
+      </c>
+      <c r="AV207" s="119" t="s">
         <v>961</v>
-      </c>
-      <c r="AV207" s="119" t="s">
-        <v>962</v>
       </c>
       <c r="AW207" s="142" t="s">
         <v>339</v>
@@ -19137,13 +19137,13 @@
       </c>
     </row>
     <row r="208" spans="1:51" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="196"/>
+      <c r="A208" s="194"/>
       <c r="B208" s="191"/>
       <c r="C208" s="172" t="s">
-        <v>718</v>
-      </c>
-      <c r="D208" s="202"/>
-      <c r="E208" s="201"/>
+        <v>717</v>
+      </c>
+      <c r="D208" s="199"/>
+      <c r="E208" s="198"/>
       <c r="F208" s="122"/>
       <c r="G208" s="169"/>
       <c r="H208" s="119"/>
@@ -19153,13 +19153,13 @@
         <v>270</v>
       </c>
       <c r="L208" s="119" t="s">
+        <v>962</v>
+      </c>
+      <c r="M208" s="122" t="s">
         <v>963</v>
       </c>
-      <c r="M208" s="122" t="s">
+      <c r="N208" s="123" t="s">
         <v>964</v>
-      </c>
-      <c r="N208" s="123" t="s">
-        <v>965</v>
       </c>
       <c r="O208" s="119" t="s">
         <v>274</v>
@@ -19169,20 +19169,20 @@
       <c r="R208" s="178"/>
       <c r="S208" s="178"/>
       <c r="T208" s="119" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="U208" s="178"/>
       <c r="V208" s="30" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="W208" s="124"/>
       <c r="X208" s="120" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="Y208" s="119"/>
       <c r="Z208" s="119"/>
       <c r="AA208" s="119" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="AB208" s="178"/>
       <c r="AC208" s="120" t="s">
@@ -19195,16 +19195,16 @@
       <c r="AH208" s="119"/>
       <c r="AI208" s="119"/>
       <c r="AJ208" s="140" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="AK208" s="179"/>
       <c r="AL208" s="179"/>
       <c r="AM208" s="179"/>
       <c r="AN208" s="119" t="s">
+        <v>970</v>
+      </c>
+      <c r="AO208" s="124" t="s">
         <v>971</v>
-      </c>
-      <c r="AO208" s="124" t="s">
-        <v>972</v>
       </c>
       <c r="AP208" s="182"/>
       <c r="AQ208" s="179"/>
@@ -19212,15 +19212,15 @@
       <c r="AS208" s="178"/>
       <c r="AT208" s="120"/>
       <c r="AU208" s="120"/>
-      <c r="AV208" s="224"/>
+      <c r="AV208" s="239"/>
       <c r="AW208" s="185"/>
       <c r="AX208" s="143"/>
-      <c r="AY208" s="224"/>
+      <c r="AY208" s="239"/>
     </row>
     <row r="209" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="196"/>
+      <c r="A209" s="194"/>
       <c r="B209" s="191"/>
-      <c r="C209" s="235"/>
+      <c r="C209" s="233"/>
       <c r="D209" s="179"/>
       <c r="E209" s="179"/>
       <c r="F209" s="123"/>
@@ -19229,7 +19229,7 @@
       <c r="I209" s="123"/>
       <c r="J209" s="179"/>
       <c r="K209" s="122" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="L209" s="119"/>
       <c r="M209" s="122"/>
@@ -19267,13 +19267,13 @@
       <c r="AS209" s="179"/>
       <c r="AT209" s="120"/>
       <c r="AU209" s="120"/>
-      <c r="AV209" s="225"/>
+      <c r="AV209" s="240"/>
       <c r="AW209" s="186"/>
       <c r="AX209" s="143"/>
-      <c r="AY209" s="225"/>
+      <c r="AY209" s="240"/>
     </row>
     <row r="210" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="196"/>
+      <c r="A210" s="194"/>
       <c r="B210" s="191"/>
       <c r="C210" s="215"/>
       <c r="D210" s="179"/>
@@ -19287,7 +19287,7 @@
       <c r="L210" s="220"/>
       <c r="M210" s="180"/>
       <c r="N210" s="179"/>
-      <c r="O210" s="258"/>
+      <c r="O210" s="260"/>
       <c r="P210" s="179"/>
       <c r="Q210" s="123"/>
       <c r="R210" s="179"/>
@@ -19320,13 +19320,13 @@
       <c r="AS210" s="179"/>
       <c r="AT210" s="120"/>
       <c r="AU210" s="120"/>
-      <c r="AV210" s="225"/>
+      <c r="AV210" s="240"/>
       <c r="AW210" s="186"/>
       <c r="AX210" s="120"/>
-      <c r="AY210" s="225"/>
+      <c r="AY210" s="240"/>
     </row>
     <row r="211" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="196"/>
+      <c r="A211" s="194"/>
       <c r="B211" s="191"/>
       <c r="C211" s="215"/>
       <c r="D211" s="179"/>
@@ -19376,10 +19376,10 @@
       <c r="AV211" s="131"/>
       <c r="AW211" s="137"/>
       <c r="AX211" s="120"/>
-      <c r="AY211" s="225"/>
+      <c r="AY211" s="240"/>
     </row>
     <row r="212" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="196"/>
+      <c r="A212" s="194"/>
       <c r="B212" s="191"/>
       <c r="C212" s="215"/>
       <c r="D212" s="179"/>
@@ -19432,8 +19432,8 @@
       <c r="AY212" s="143"/>
     </row>
     <row r="213" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="196"/>
-      <c r="B213" s="192"/>
+      <c r="A213" s="194"/>
+      <c r="B213" s="212"/>
       <c r="C213" s="216"/>
       <c r="D213" s="184"/>
       <c r="E213" s="184"/>
@@ -19485,15 +19485,15 @@
       <c r="AY213" s="173"/>
     </row>
     <row r="214" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="196"/>
-      <c r="B214" s="190">
+      <c r="A214" s="194"/>
+      <c r="B214" s="211">
         <v>2</v>
       </c>
       <c r="C214" s="159" t="s">
+        <v>973</v>
+      </c>
+      <c r="D214" s="169" t="s">
         <v>974</v>
-      </c>
-      <c r="D214" s="169" t="s">
-        <v>975</v>
       </c>
       <c r="E214" s="169" t="s">
         <v>308</v>
@@ -19514,7 +19514,7 @@
         <v>59</v>
       </c>
       <c r="K214" s="119" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="L214" s="151" t="s">
         <v>310</v>
@@ -19523,25 +19523,25 @@
         <v>60</v>
       </c>
       <c r="N214" s="119" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="O214" s="119" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="P214" s="119" t="s">
         <v>362</v>
       </c>
       <c r="Q214" s="119" t="s">
+        <v>977</v>
+      </c>
+      <c r="R214" s="119" t="s">
         <v>978</v>
       </c>
-      <c r="R214" s="119" t="s">
+      <c r="S214" s="135" t="s">
         <v>979</v>
       </c>
-      <c r="S214" s="135" t="s">
-        <v>980</v>
-      </c>
       <c r="T214" s="120" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="U214" s="119" t="s">
         <v>75</v>
@@ -19550,7 +19550,7 @@
         <v>126</v>
       </c>
       <c r="W214" s="119" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="X214" s="120" t="s">
         <v>180</v>
@@ -19559,32 +19559,32 @@
         <v>412</v>
       </c>
       <c r="Z214" s="119" t="s">
+        <v>981</v>
+      </c>
+      <c r="AA214" s="119" t="s">
+        <v>611</v>
+      </c>
+      <c r="AB214" s="119" t="s">
         <v>982</v>
       </c>
-      <c r="AA214" s="119" t="s">
-        <v>612</v>
-      </c>
-      <c r="AB214" s="119" t="s">
+      <c r="AC214" s="133" t="s">
         <v>983</v>
       </c>
-      <c r="AC214" s="133" t="s">
+      <c r="AD214" s="119" t="s">
         <v>984</v>
-      </c>
-      <c r="AD214" s="119" t="s">
-        <v>985</v>
       </c>
       <c r="AE214" s="178"/>
       <c r="AF214" s="119" t="s">
+        <v>985</v>
+      </c>
+      <c r="AG214" s="119" t="s">
         <v>986</v>
       </c>
-      <c r="AG214" s="119" t="s">
+      <c r="AH214" s="119" t="s">
         <v>987</v>
       </c>
-      <c r="AH214" s="119" t="s">
-        <v>988</v>
-      </c>
       <c r="AI214" s="119" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AJ214" s="119" t="s">
         <v>86</v>
@@ -19593,25 +19593,25 @@
         <v>423</v>
       </c>
       <c r="AL214" s="119" t="s">
+        <v>988</v>
+      </c>
+      <c r="AM214" s="120" t="s">
         <v>989</v>
       </c>
-      <c r="AM214" s="120" t="s">
+      <c r="AN214" s="119" t="s">
         <v>990</v>
-      </c>
-      <c r="AN214" s="119" t="s">
-        <v>991</v>
       </c>
       <c r="AO214" s="119" t="s">
         <v>142</v>
       </c>
       <c r="AP214" s="119" t="s">
+        <v>991</v>
+      </c>
+      <c r="AQ214" s="119" t="s">
+        <v>818</v>
+      </c>
+      <c r="AR214" s="119" t="s">
         <v>992</v>
-      </c>
-      <c r="AQ214" s="119" t="s">
-        <v>819</v>
-      </c>
-      <c r="AR214" s="119" t="s">
-        <v>993</v>
       </c>
       <c r="AS214" s="120" t="s">
         <v>199</v>
@@ -19620,10 +19620,10 @@
         <v>383</v>
       </c>
       <c r="AU214" s="120" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AV214" s="120" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AW214" s="143" t="s">
         <v>150</v>
@@ -19636,13 +19636,13 @@
       </c>
     </row>
     <row r="215" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="196"/>
+      <c r="A215" s="194"/>
       <c r="B215" s="191"/>
       <c r="C215" s="159" t="s">
+        <v>994</v>
+      </c>
+      <c r="D215" s="169" t="s">
         <v>995</v>
-      </c>
-      <c r="D215" s="169" t="s">
-        <v>996</v>
       </c>
       <c r="E215" s="169"/>
       <c r="F215" s="119"/>
@@ -19651,65 +19651,65 @@
       <c r="I215" s="119"/>
       <c r="J215" s="120"/>
       <c r="K215" s="119" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="L215" s="151"/>
       <c r="M215" s="178"/>
       <c r="N215" s="119" t="s">
+        <v>997</v>
+      </c>
+      <c r="O215" s="119" t="s">
         <v>998</v>
-      </c>
-      <c r="O215" s="119" t="s">
-        <v>999</v>
       </c>
       <c r="P215" s="178"/>
       <c r="Q215" s="178"/>
       <c r="R215" s="119" t="s">
+        <v>999</v>
+      </c>
+      <c r="S215" s="135" t="s">
         <v>1000</v>
-      </c>
-      <c r="S215" s="135" t="s">
-        <v>1001</v>
       </c>
       <c r="T215" s="120"/>
       <c r="U215" s="178"/>
       <c r="V215" s="178"/>
       <c r="W215" s="119" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="X215" s="120"/>
       <c r="Y215" s="119"/>
       <c r="Z215" s="119" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="AA215" s="119" t="s">
         <v>279</v>
       </c>
       <c r="AB215" s="178"/>
       <c r="AC215" s="133" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="AD215" s="119" t="s">
         <v>210</v>
       </c>
       <c r="AE215" s="179"/>
       <c r="AF215" s="119" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AG215" s="119" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AH215" s="119"/>
       <c r="AI215" s="119"/>
       <c r="AJ215" s="119"/>
       <c r="AK215" s="178"/>
       <c r="AL215" s="119" t="s">
+        <v>1005</v>
+      </c>
+      <c r="AM215" s="120" t="s">
         <v>1006</v>
-      </c>
-      <c r="AM215" s="120" t="s">
-        <v>1007</v>
       </c>
       <c r="AN215" s="178"/>
       <c r="AO215" s="119" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AP215" s="178"/>
       <c r="AQ215" s="119" t="s">
@@ -19720,16 +19720,16 @@
       <c r="AT215" s="178"/>
       <c r="AU215" s="120"/>
       <c r="AV215" s="120" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AW215" s="143"/>
-      <c r="AX215" s="224"/>
+      <c r="AX215" s="239"/>
       <c r="AY215" s="143"/>
     </row>
     <row r="216" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="196"/>
+      <c r="A216" s="194"/>
       <c r="B216" s="191"/>
-      <c r="C216" s="226"/>
+      <c r="C216" s="224"/>
       <c r="D216" s="219"/>
       <c r="E216" s="169"/>
       <c r="F216" s="120"/>
@@ -19753,10 +19753,10 @@
       <c r="X216" s="120"/>
       <c r="Y216" s="120"/>
       <c r="Z216" s="119" t="s">
+        <v>1009</v>
+      </c>
+      <c r="AA216" s="119" t="s">
         <v>1010</v>
-      </c>
-      <c r="AA216" s="119" t="s">
-        <v>1011</v>
       </c>
       <c r="AB216" s="179"/>
       <c r="AC216" s="178"/>
@@ -19772,7 +19772,7 @@
       <c r="AM216" s="180"/>
       <c r="AN216" s="179"/>
       <c r="AO216" s="119" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="AP216" s="179"/>
       <c r="AQ216" s="119" t="s">
@@ -19784,11 +19784,11 @@
       <c r="AU216" s="120"/>
       <c r="AV216" s="120"/>
       <c r="AW216" s="143"/>
-      <c r="AX216" s="225"/>
+      <c r="AX216" s="240"/>
       <c r="AY216" s="143"/>
     </row>
     <row r="217" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="196"/>
+      <c r="A217" s="194"/>
       <c r="B217" s="191"/>
       <c r="C217" s="215"/>
       <c r="D217" s="179"/>
@@ -19835,13 +19835,13 @@
       <c r="AS217" s="120"/>
       <c r="AT217" s="179"/>
       <c r="AU217" s="120"/>
-      <c r="AV217" s="248"/>
+      <c r="AV217" s="249"/>
       <c r="AW217" s="143"/>
-      <c r="AX217" s="225"/>
+      <c r="AX217" s="240"/>
       <c r="AY217" s="143"/>
     </row>
     <row r="218" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="196"/>
+      <c r="A218" s="194"/>
       <c r="B218" s="191"/>
       <c r="C218" s="215"/>
       <c r="D218" s="179"/>
@@ -19888,13 +19888,13 @@
       <c r="AS218" s="120"/>
       <c r="AT218" s="179"/>
       <c r="AU218" s="120"/>
-      <c r="AV218" s="225"/>
+      <c r="AV218" s="240"/>
       <c r="AW218" s="120"/>
-      <c r="AX218" s="225"/>
+      <c r="AX218" s="240"/>
       <c r="AY218" s="120"/>
     </row>
     <row r="219" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="196"/>
+      <c r="A219" s="194"/>
       <c r="B219" s="191"/>
       <c r="C219" s="215"/>
       <c r="D219" s="179"/>
@@ -19941,13 +19941,13 @@
       <c r="AS219" s="120"/>
       <c r="AT219" s="120"/>
       <c r="AU219" s="120"/>
-      <c r="AV219" s="225"/>
+      <c r="AV219" s="240"/>
       <c r="AW219" s="120"/>
       <c r="AX219" s="120"/>
       <c r="AY219" s="120"/>
     </row>
     <row r="220" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="196"/>
+      <c r="A220" s="194"/>
       <c r="B220" s="191"/>
       <c r="C220" s="215"/>
       <c r="D220" s="179"/>
@@ -19994,14 +19994,14 @@
       <c r="AS220" s="120"/>
       <c r="AT220" s="120"/>
       <c r="AU220" s="120"/>
-      <c r="AV220" s="225"/>
+      <c r="AV220" s="240"/>
       <c r="AW220" s="120"/>
       <c r="AX220" s="120"/>
       <c r="AY220" s="120"/>
     </row>
     <row r="221" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="196"/>
-      <c r="B221" s="192"/>
+      <c r="A221" s="194"/>
+      <c r="B221" s="212"/>
       <c r="C221" s="216"/>
       <c r="D221" s="184"/>
       <c r="E221" s="156"/>
@@ -20053,33 +20053,33 @@
       <c r="AY221" s="132"/>
     </row>
     <row r="222" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="196"/>
+      <c r="A222" s="194"/>
       <c r="B222" s="213">
         <v>3</v>
       </c>
       <c r="C222" s="165" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D222" s="119" t="s">
         <v>1013</v>
       </c>
-      <c r="D222" s="119" t="s">
+      <c r="E222" s="119" t="s">
         <v>1014</v>
-      </c>
-      <c r="E222" s="119" t="s">
-        <v>1015</v>
       </c>
       <c r="F222" s="128" t="s">
         <v>117</v>
       </c>
       <c r="G222" s="168" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H222" s="168" t="s">
         <v>1016</v>
       </c>
-      <c r="H222" s="168" t="s">
+      <c r="I222" s="119" t="s">
         <v>1017</v>
       </c>
-      <c r="I222" s="119" t="s">
+      <c r="J222" s="169" t="s">
         <v>1018</v>
-      </c>
-      <c r="J222" s="169" t="s">
-        <v>1019</v>
       </c>
       <c r="K222" s="151" t="s">
         <v>310</v>
@@ -20094,61 +20094,61 @@
         <v>67</v>
       </c>
       <c r="O222" s="119" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="P222" s="119" t="s">
         <v>133</v>
       </c>
       <c r="Q222" s="119" t="s">
+        <v>1020</v>
+      </c>
+      <c r="R222" s="119" t="s">
         <v>1021</v>
       </c>
-      <c r="R222" s="119" t="s">
+      <c r="S222" s="119" t="s">
         <v>1022</v>
-      </c>
-      <c r="S222" s="119" t="s">
-        <v>1023</v>
       </c>
       <c r="T222" s="120" t="s">
         <v>318</v>
       </c>
       <c r="U222" s="119" t="s">
+        <v>1023</v>
+      </c>
+      <c r="V222" s="119" t="s">
         <v>1024</v>
-      </c>
-      <c r="V222" s="119" t="s">
-        <v>1025</v>
       </c>
       <c r="W222" s="119" t="s">
         <v>118</v>
       </c>
       <c r="X222" s="119" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Y222" s="119" t="s">
         <v>1026</v>
-      </c>
-      <c r="Y222" s="119" t="s">
-        <v>1027</v>
       </c>
       <c r="Z222" s="133" t="s">
         <v>77</v>
       </c>
       <c r="AA222" s="119" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AB222" s="119" t="s">
         <v>1028</v>
       </c>
-      <c r="AB222" s="119" t="s">
+      <c r="AC222" s="119" t="s">
         <v>1029</v>
       </c>
-      <c r="AC222" s="119" t="s">
+      <c r="AD222" s="119" t="s">
         <v>1030</v>
       </c>
-      <c r="AD222" s="119" t="s">
+      <c r="AE222" s="177" t="s">
+        <v>823</v>
+      </c>
+      <c r="AF222" s="120" t="s">
         <v>1031</v>
       </c>
-      <c r="AE222" s="177" t="s">
-        <v>824</v>
-      </c>
-      <c r="AF222" s="120" t="s">
-        <v>1032</v>
-      </c>
       <c r="AG222" s="119" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AH222" s="119" t="s">
         <v>329</v>
@@ -20163,25 +20163,25 @@
         <v>192</v>
       </c>
       <c r="AL222" s="120" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AM222" s="119" t="s">
         <v>1033</v>
       </c>
-      <c r="AM222" s="119" t="s">
+      <c r="AN222" s="119" t="s">
         <v>1034</v>
       </c>
-      <c r="AN222" s="119" t="s">
+      <c r="AO222" s="119" t="s">
         <v>1035</v>
       </c>
-      <c r="AO222" s="119" t="s">
+      <c r="AP222" s="120" t="s">
         <v>1036</v>
       </c>
-      <c r="AP222" s="120" t="s">
+      <c r="AQ222" s="119" t="s">
         <v>1037</v>
       </c>
-      <c r="AQ222" s="119" t="s">
-        <v>1038</v>
-      </c>
       <c r="AR222" s="120" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AS222" s="119" t="s">
         <v>93</v>
@@ -20193,7 +20193,7 @@
         <v>431</v>
       </c>
       <c r="AV222" s="138" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AW222" s="120" t="s">
         <v>97</v>
@@ -20206,26 +20206,26 @@
       </c>
     </row>
     <row r="223" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="196"/>
-      <c r="B223" s="196"/>
+      <c r="A223" s="194"/>
+      <c r="B223" s="194"/>
       <c r="C223" s="165" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D223" s="119" t="s">
         <v>1040</v>
       </c>
-      <c r="D223" s="119" t="s">
+      <c r="E223" s="119" t="s">
         <v>1041</v>
-      </c>
-      <c r="E223" s="119" t="s">
-        <v>1042</v>
       </c>
       <c r="F223" s="128"/>
       <c r="G223" s="168" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="H223" s="168" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I223" s="119" t="s">
         <v>1043</v>
-      </c>
-      <c r="I223" s="119" t="s">
-        <v>1044</v>
       </c>
       <c r="J223" s="169"/>
       <c r="K223" s="217"/>
@@ -20233,50 +20233,50 @@
       <c r="M223" s="123"/>
       <c r="N223" s="181"/>
       <c r="O223" s="119" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="P223" s="119" t="s">
         <v>274</v>
       </c>
       <c r="Q223" s="178"/>
       <c r="R223" s="119" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="S223" s="178"/>
       <c r="T223" s="120"/>
       <c r="U223" s="119" t="s">
+        <v>1046</v>
+      </c>
+      <c r="V223" s="119" t="s">
         <v>1047</v>
-      </c>
-      <c r="V223" s="119" t="s">
-        <v>1048</v>
       </c>
       <c r="W223" s="119"/>
       <c r="X223" s="119" t="s">
+        <v>1048</v>
+      </c>
+      <c r="Y223" s="119" t="s">
         <v>1049</v>
-      </c>
-      <c r="Y223" s="119" t="s">
-        <v>1050</v>
       </c>
       <c r="Z223" s="119"/>
       <c r="AA223" s="178"/>
       <c r="AB223" s="119" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AC223" s="119" t="s">
         <v>1051</v>
-      </c>
-      <c r="AC223" s="119" t="s">
-        <v>1052</v>
       </c>
       <c r="AD223" s="178"/>
       <c r="AE223" s="177" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AF223" s="120" t="s">
         <v>1053</v>
-      </c>
-      <c r="AF223" s="120" t="s">
-        <v>1054</v>
       </c>
       <c r="AG223" s="178"/>
       <c r="AH223" s="178"/>
       <c r="AI223" s="178"/>
       <c r="AJ223" s="119" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AK223" s="178"/>
       <c r="AL223" s="120"/>
@@ -20289,29 +20289,29 @@
       <c r="AS223" s="178"/>
       <c r="AT223" s="120"/>
       <c r="AU223" s="187"/>
-      <c r="AV223" s="233"/>
+      <c r="AV223" s="231"/>
       <c r="AW223" s="120"/>
       <c r="AX223" s="120"/>
       <c r="AY223" s="120"/>
     </row>
     <row r="224" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="196"/>
-      <c r="B224" s="196"/>
+      <c r="A224" s="194"/>
+      <c r="B224" s="194"/>
       <c r="C224" s="165" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D224" s="119" t="s">
         <v>1055</v>
       </c>
-      <c r="D224" s="119" t="s">
+      <c r="E224" s="119" t="s">
         <v>1056</v>
-      </c>
-      <c r="E224" s="119" t="s">
-        <v>1057</v>
       </c>
       <c r="F224" s="129"/>
       <c r="G224" s="168" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H224" s="168" t="s">
         <v>1058</v>
-      </c>
-      <c r="H224" s="168" t="s">
-        <v>1059</v>
       </c>
       <c r="I224" s="119"/>
       <c r="J224" s="169"/>
@@ -20326,17 +20326,17 @@
       <c r="S224" s="179"/>
       <c r="T224" s="120"/>
       <c r="U224" s="119" t="s">
+        <v>1059</v>
+      </c>
+      <c r="V224" s="119" t="s">
         <v>1060</v>
-      </c>
-      <c r="V224" s="119" t="s">
-        <v>1061</v>
       </c>
       <c r="W224" s="120"/>
       <c r="X224" s="119" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="Y224" s="119" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="Z224" s="120"/>
       <c r="AA224" s="179"/>
@@ -20344,7 +20344,7 @@
       <c r="AC224" s="178"/>
       <c r="AD224" s="179"/>
       <c r="AE224" s="177" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AF224" s="120"/>
       <c r="AG224" s="179"/>
@@ -20362,19 +20362,19 @@
       <c r="AS224" s="179"/>
       <c r="AT224" s="120"/>
       <c r="AU224" s="188"/>
-      <c r="AV224" s="211"/>
+      <c r="AV224" s="209"/>
       <c r="AW224" s="120"/>
       <c r="AX224" s="120"/>
       <c r="AY224" s="120"/>
     </row>
     <row r="225" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="196"/>
-      <c r="B225" s="196"/>
-      <c r="C225" s="247"/>
-      <c r="D225" s="198"/>
+      <c r="A225" s="194"/>
+      <c r="B225" s="194"/>
+      <c r="C225" s="244"/>
+      <c r="D225" s="189"/>
       <c r="E225" s="120"/>
       <c r="F225" s="129"/>
-      <c r="G225" s="201"/>
+      <c r="G225" s="198"/>
       <c r="H225" s="275"/>
       <c r="I225" s="120"/>
       <c r="J225" s="169"/>
@@ -20388,7 +20388,7 @@
       <c r="R225" s="179"/>
       <c r="S225" s="179"/>
       <c r="T225" s="120"/>
-      <c r="U225" s="198"/>
+      <c r="U225" s="189"/>
       <c r="V225" s="119"/>
       <c r="W225" s="120"/>
       <c r="X225" s="119"/>
@@ -20398,7 +20398,7 @@
       <c r="AB225" s="179"/>
       <c r="AC225" s="179"/>
       <c r="AD225" s="179"/>
-      <c r="AE225" s="228"/>
+      <c r="AE225" s="226"/>
       <c r="AF225" s="120"/>
       <c r="AG225" s="179"/>
       <c r="AH225" s="179"/>
@@ -20415,14 +20415,14 @@
       <c r="AS225" s="179"/>
       <c r="AT225" s="120"/>
       <c r="AU225" s="188"/>
-      <c r="AV225" s="211"/>
+      <c r="AV225" s="209"/>
       <c r="AW225" s="120"/>
       <c r="AX225" s="120"/>
       <c r="AY225" s="120"/>
     </row>
     <row r="226" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="196"/>
-      <c r="B226" s="196"/>
+      <c r="A226" s="194"/>
+      <c r="B226" s="194"/>
       <c r="C226" s="215"/>
       <c r="D226" s="179"/>
       <c r="E226" s="120"/>
@@ -20468,14 +20468,14 @@
       <c r="AS226" s="179"/>
       <c r="AT226" s="120"/>
       <c r="AU226" s="120"/>
-      <c r="AV226" s="211"/>
+      <c r="AV226" s="209"/>
       <c r="AW226" s="120"/>
       <c r="AX226" s="120"/>
       <c r="AY226" s="120"/>
     </row>
     <row r="227" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="196"/>
-      <c r="B227" s="196"/>
+      <c r="A227" s="194"/>
+      <c r="B227" s="194"/>
       <c r="C227" s="215"/>
       <c r="D227" s="179"/>
       <c r="E227" s="120"/>
@@ -20527,8 +20527,8 @@
       <c r="AY227" s="120"/>
     </row>
     <row r="228" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="196"/>
-      <c r="B228" s="196"/>
+      <c r="A228" s="194"/>
+      <c r="B228" s="194"/>
       <c r="C228" s="215"/>
       <c r="D228" s="179"/>
       <c r="E228" s="120"/>
@@ -20580,8 +20580,8 @@
       <c r="AY228" s="120"/>
     </row>
     <row r="229" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="196"/>
-      <c r="B229" s="197"/>
+      <c r="A229" s="194"/>
+      <c r="B229" s="195"/>
       <c r="C229" s="216"/>
       <c r="D229" s="184"/>
       <c r="E229" s="139"/>
@@ -20633,32 +20633,32 @@
       <c r="AY229" s="139"/>
     </row>
     <row r="230" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="196"/>
-      <c r="B230" s="190">
+      <c r="A230" s="194"/>
+      <c r="B230" s="211">
         <v>4</v>
       </c>
       <c r="C230" s="214"/>
       <c r="D230" s="119" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E230" s="119" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F230" s="122" t="s">
         <v>1064</v>
       </c>
-      <c r="F230" s="122" t="s">
+      <c r="G230" s="168" t="s">
         <v>1065</v>
-      </c>
-      <c r="G230" s="168" t="s">
-        <v>1066</v>
       </c>
       <c r="H230" s="119"/>
       <c r="I230" s="119" t="s">
         <v>118</v>
       </c>
       <c r="J230" s="119" t="s">
+        <v>1066</v>
+      </c>
+      <c r="K230" s="123" t="s">
         <v>1067</v>
-      </c>
-      <c r="K230" s="123" t="s">
-        <v>1068</v>
       </c>
       <c r="L230" s="119" t="s">
         <v>63</v>
@@ -20670,102 +20670,102 @@
         <v>61</v>
       </c>
       <c r="O230" s="133" t="s">
+        <v>1068</v>
+      </c>
+      <c r="P230" s="119" t="s">
         <v>1069</v>
       </c>
-      <c r="P230" s="119" t="s">
+      <c r="Q230" s="122" t="s">
         <v>1070</v>
       </c>
-      <c r="Q230" s="122" t="s">
+      <c r="R230" s="119" t="s">
         <v>1071</v>
       </c>
-      <c r="R230" s="119" t="s">
+      <c r="S230" s="119" t="s">
         <v>1072</v>
-      </c>
-      <c r="S230" s="119" t="s">
-        <v>1073</v>
       </c>
       <c r="T230" s="119" t="s">
         <v>75</v>
       </c>
       <c r="U230" s="120" t="s">
+        <v>1073</v>
+      </c>
+      <c r="V230" s="120" t="s">
         <v>1074</v>
-      </c>
-      <c r="V230" s="120" t="s">
-        <v>1075</v>
       </c>
       <c r="W230" s="119" t="s">
         <v>474</v>
       </c>
       <c r="X230" s="119" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="Y230" s="119" t="s">
         <v>389</v>
       </c>
       <c r="Z230" s="119" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AA230" s="119" t="s">
         <v>300</v>
       </c>
       <c r="AB230" s="119" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AC230" s="120" t="s">
         <v>1078</v>
-      </c>
-      <c r="AC230" s="120" t="s">
-        <v>1079</v>
       </c>
       <c r="AD230" s="119" t="s">
         <v>481</v>
       </c>
       <c r="AE230" s="119" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AF230" s="119" t="s">
         <v>1080</v>
       </c>
-      <c r="AF230" s="119" t="s">
+      <c r="AG230" s="120" t="s">
         <v>1081</v>
       </c>
-      <c r="AG230" s="120" t="s">
+      <c r="AH230" s="119" t="s">
         <v>1082</v>
       </c>
-      <c r="AH230" s="119" t="s">
-        <v>1083</v>
-      </c>
       <c r="AI230" s="119" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ230" s="119"/>
       <c r="AK230" s="119" t="s">
         <v>254</v>
       </c>
       <c r="AL230" s="119" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AM230" s="119" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AN230" s="119" t="s">
         <v>1084</v>
-      </c>
-      <c r="AN230" s="119" t="s">
-        <v>1085</v>
       </c>
       <c r="AO230" s="120"/>
       <c r="AP230" s="120" t="s">
         <v>133</v>
       </c>
       <c r="AQ230" s="120" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AR230" s="119" t="s">
+        <v>784</v>
+      </c>
+      <c r="AS230" s="120" t="s">
         <v>1086</v>
       </c>
-      <c r="AR230" s="119" t="s">
-        <v>785</v>
-      </c>
-      <c r="AS230" s="120" t="s">
+      <c r="AT230" s="120" t="s">
         <v>1087</v>
       </c>
-      <c r="AT230" s="120" t="s">
+      <c r="AU230" s="119" t="s">
         <v>1088</v>
       </c>
-      <c r="AU230" s="119" t="s">
-        <v>1089</v>
-      </c>
       <c r="AV230" s="138" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AW230" s="120" t="s">
         <v>97</v>
@@ -20778,100 +20778,100 @@
       </c>
     </row>
     <row r="231" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="196"/>
+      <c r="A231" s="194"/>
       <c r="B231" s="191"/>
       <c r="C231" s="215"/>
-      <c r="D231" s="198"/>
+      <c r="D231" s="189"/>
       <c r="E231" s="119" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F231" s="122" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G231" s="122"/>
       <c r="H231" s="120"/>
       <c r="I231" s="119"/>
       <c r="J231" s="119" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K231" s="123" t="s">
         <v>1091</v>
-      </c>
-      <c r="K231" s="123" t="s">
-        <v>1092</v>
       </c>
       <c r="L231" s="119"/>
       <c r="M231" s="178"/>
       <c r="N231" s="123"/>
       <c r="O231" s="178"/>
       <c r="P231" s="119" t="s">
+        <v>1092</v>
+      </c>
+      <c r="Q231" s="122" t="s">
         <v>1093</v>
-      </c>
-      <c r="Q231" s="122" t="s">
-        <v>1094</v>
       </c>
       <c r="R231" s="178"/>
       <c r="S231" s="178"/>
       <c r="T231" s="178"/>
       <c r="U231" s="120" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="V231" s="120"/>
       <c r="W231" s="119" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="X231" s="119"/>
       <c r="Y231" s="119"/>
       <c r="Z231" s="119"/>
       <c r="AA231" s="119" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AB231" s="119" t="s">
         <v>1096</v>
       </c>
-      <c r="AB231" s="119" t="s">
-        <v>1097</v>
-      </c>
       <c r="AC231" s="120" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="AD231" s="178"/>
       <c r="AE231" s="178"/>
       <c r="AF231" s="178"/>
       <c r="AG231" s="120" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AH231" s="119" t="s">
         <v>1098</v>
       </c>
-      <c r="AH231" s="119" t="s">
-        <v>1099</v>
-      </c>
       <c r="AI231" s="119" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="AJ231" s="120"/>
       <c r="AK231" s="119" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AL231" s="178"/>
       <c r="AM231" s="178"/>
       <c r="AN231" s="119" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AO231" s="120"/>
       <c r="AP231" s="120" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AQ231" s="120"/>
       <c r="AR231" s="119" t="s">
         <v>356</v>
       </c>
       <c r="AS231" s="120" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="AT231" s="120" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="AU231" s="187"/>
-      <c r="AV231" s="203"/>
+      <c r="AV231" s="200"/>
       <c r="AW231" s="120"/>
       <c r="AX231" s="178"/>
       <c r="AY231" s="120"/>
     </row>
     <row r="232" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="196"/>
+      <c r="A232" s="194"/>
       <c r="B232" s="191"/>
       <c r="C232" s="215"/>
       <c r="D232" s="179"/>
@@ -20908,7 +20908,7 @@
       <c r="AE232" s="179"/>
       <c r="AF232" s="179"/>
       <c r="AG232" s="120" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="AH232" s="178"/>
       <c r="AI232" s="120"/>
@@ -20921,16 +20921,16 @@
       <c r="AP232" s="120"/>
       <c r="AQ232" s="120"/>
       <c r="AR232" s="178"/>
-      <c r="AS232" s="248"/>
+      <c r="AS232" s="249"/>
       <c r="AT232" s="221"/>
       <c r="AU232" s="188"/>
-      <c r="AV232" s="204"/>
+      <c r="AV232" s="201"/>
       <c r="AW232" s="120"/>
       <c r="AX232" s="179"/>
       <c r="AY232" s="120"/>
     </row>
     <row r="233" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="196"/>
+      <c r="A233" s="194"/>
       <c r="B233" s="191"/>
       <c r="C233" s="215"/>
       <c r="D233" s="179"/>
@@ -20974,16 +20974,16 @@
       <c r="AP233" s="120"/>
       <c r="AQ233" s="120"/>
       <c r="AR233" s="179"/>
-      <c r="AS233" s="225"/>
-      <c r="AT233" s="211"/>
+      <c r="AS233" s="240"/>
+      <c r="AT233" s="209"/>
       <c r="AU233" s="188"/>
-      <c r="AV233" s="204"/>
+      <c r="AV233" s="201"/>
       <c r="AW233" s="120"/>
       <c r="AX233" s="179"/>
       <c r="AY233" s="120"/>
     </row>
     <row r="234" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="196"/>
+      <c r="A234" s="194"/>
       <c r="B234" s="191"/>
       <c r="C234" s="215"/>
       <c r="D234" s="179"/>
@@ -21011,11 +21011,11 @@
       <c r="Z234" s="120"/>
       <c r="AA234" s="120"/>
       <c r="AB234" s="14"/>
-      <c r="AC234" s="250"/>
+      <c r="AC234" s="254"/>
       <c r="AD234" s="179"/>
       <c r="AE234" s="179"/>
       <c r="AF234" s="123"/>
-      <c r="AG234" s="255"/>
+      <c r="AG234" s="257"/>
       <c r="AH234" s="179"/>
       <c r="AI234" s="120"/>
       <c r="AJ234" s="120"/>
@@ -21027,8 +21027,8 @@
       <c r="AP234" s="180"/>
       <c r="AQ234" s="131"/>
       <c r="AR234" s="179"/>
-      <c r="AS234" s="225"/>
-      <c r="AT234" s="211"/>
+      <c r="AS234" s="240"/>
+      <c r="AT234" s="209"/>
       <c r="AU234" s="120"/>
       <c r="AV234" s="120"/>
       <c r="AW234" s="120"/>
@@ -21036,7 +21036,7 @@
       <c r="AY234" s="120"/>
     </row>
     <row r="235" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="196"/>
+      <c r="A235" s="194"/>
       <c r="B235" s="191"/>
       <c r="C235" s="215"/>
       <c r="D235" s="179"/>
@@ -21080,8 +21080,8 @@
       <c r="AP235" s="179"/>
       <c r="AQ235" s="148"/>
       <c r="AR235" s="179"/>
-      <c r="AS235" s="225"/>
-      <c r="AT235" s="211"/>
+      <c r="AS235" s="240"/>
+      <c r="AT235" s="209"/>
       <c r="AU235" s="131"/>
       <c r="AV235" s="120"/>
       <c r="AW235" s="120"/>
@@ -21089,7 +21089,7 @@
       <c r="AY235" s="120"/>
     </row>
     <row r="236" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="196"/>
+      <c r="A236" s="194"/>
       <c r="B236" s="191"/>
       <c r="C236" s="215"/>
       <c r="D236" s="179"/>
@@ -21133,8 +21133,8 @@
       <c r="AP236" s="148"/>
       <c r="AQ236" s="120"/>
       <c r="AR236" s="179"/>
-      <c r="AS236" s="225"/>
-      <c r="AT236" s="211"/>
+      <c r="AS236" s="240"/>
+      <c r="AT236" s="209"/>
       <c r="AU236" s="120"/>
       <c r="AV236" s="120"/>
       <c r="AW236" s="120"/>
@@ -21142,8 +21142,8 @@
       <c r="AY236" s="120"/>
     </row>
     <row r="237" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="196"/>
-      <c r="B237" s="192"/>
+      <c r="A237" s="194"/>
+      <c r="B237" s="212"/>
       <c r="C237" s="216"/>
       <c r="D237" s="184"/>
       <c r="E237" s="139"/>
@@ -21195,15 +21195,15 @@
       <c r="AY237" s="139"/>
     </row>
     <row r="238" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="196"/>
-      <c r="B238" s="190">
+      <c r="A238" s="194"/>
+      <c r="B238" s="211">
         <v>5</v>
       </c>
       <c r="C238" s="223"/>
-      <c r="D238" s="198"/>
-      <c r="E238" s="198"/>
+      <c r="D238" s="189"/>
+      <c r="E238" s="189"/>
       <c r="F238" s="119"/>
-      <c r="G238" s="200"/>
+      <c r="G238" s="197"/>
       <c r="H238" s="119"/>
       <c r="I238" s="119"/>
       <c r="J238" s="178"/>
@@ -21211,7 +21211,7 @@
       <c r="L238" s="178"/>
       <c r="M238" s="120"/>
       <c r="N238" s="122" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="O238" s="178"/>
       <c r="P238" s="141"/>
@@ -21231,10 +21231,10 @@
       <c r="AB238" s="178"/>
       <c r="AC238" s="178"/>
       <c r="AD238" s="120" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AE238" s="120" t="s">
         <v>1104</v>
-      </c>
-      <c r="AE238" s="120" t="s">
-        <v>1105</v>
       </c>
       <c r="AF238" s="119"/>
       <c r="AG238" s="119"/>
@@ -21243,34 +21243,34 @@
       <c r="AJ238" s="119"/>
       <c r="AK238" s="178"/>
       <c r="AL238" s="119" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AM238" s="141" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AN238" s="119" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="AO238" s="178"/>
       <c r="AP238" s="119" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AQ238" s="119" t="s">
         <v>1107</v>
-      </c>
-      <c r="AQ238" s="119" t="s">
-        <v>1108</v>
       </c>
       <c r="AR238" s="178"/>
       <c r="AS238" s="137"/>
-      <c r="AT238" s="233"/>
-      <c r="AU238" s="224"/>
+      <c r="AT238" s="231"/>
+      <c r="AU238" s="239"/>
       <c r="AV238" s="138" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="AW238" s="134"/>
       <c r="AX238" s="178"/>
       <c r="AY238" s="178"/>
     </row>
     <row r="239" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="196"/>
+      <c r="A239" s="194"/>
       <c r="B239" s="191"/>
       <c r="C239" s="215"/>
       <c r="D239" s="179"/>
@@ -21300,10 +21300,10 @@
       <c r="AB239" s="179"/>
       <c r="AC239" s="179"/>
       <c r="AD239" s="120" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AE239" s="120" t="s">
         <v>1110</v>
-      </c>
-      <c r="AE239" s="120" t="s">
-        <v>1111</v>
       </c>
       <c r="AF239" s="119"/>
       <c r="AG239" s="119"/>
@@ -21314,22 +21314,22 @@
       <c r="AL239" s="119"/>
       <c r="AM239" s="141"/>
       <c r="AN239" s="119" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AO239" s="179"/>
       <c r="AP239" s="119"/>
       <c r="AQ239" s="119"/>
       <c r="AR239" s="179"/>
       <c r="AS239" s="137"/>
-      <c r="AT239" s="211"/>
-      <c r="AU239" s="225"/>
+      <c r="AT239" s="209"/>
+      <c r="AU239" s="240"/>
       <c r="AV239" s="138"/>
       <c r="AW239" s="134"/>
       <c r="AX239" s="179"/>
       <c r="AY239" s="179"/>
     </row>
     <row r="240" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="196"/>
+      <c r="A240" s="194"/>
       <c r="B240" s="191"/>
       <c r="C240" s="215"/>
       <c r="D240" s="179"/>
@@ -21374,15 +21374,15 @@
       <c r="AQ240" s="120"/>
       <c r="AR240" s="179"/>
       <c r="AS240" s="120"/>
-      <c r="AT240" s="211"/>
-      <c r="AU240" s="225"/>
+      <c r="AT240" s="209"/>
+      <c r="AU240" s="240"/>
       <c r="AV240" s="120"/>
       <c r="AW240" s="120"/>
       <c r="AX240" s="179"/>
       <c r="AY240" s="179"/>
     </row>
     <row r="241" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="196"/>
+      <c r="A241" s="194"/>
       <c r="B241" s="191"/>
       <c r="C241" s="215"/>
       <c r="D241" s="179"/>
@@ -21427,7 +21427,7 @@
       <c r="AQ241" s="131"/>
       <c r="AR241" s="179"/>
       <c r="AS241" s="120"/>
-      <c r="AT241" s="211"/>
+      <c r="AT241" s="209"/>
       <c r="AU241" s="137"/>
       <c r="AV241" s="120"/>
       <c r="AW241" s="120"/>
@@ -21435,7 +21435,7 @@
       <c r="AY241" s="55"/>
     </row>
     <row r="242" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="196"/>
+      <c r="A242" s="194"/>
       <c r="B242" s="191"/>
       <c r="C242" s="215"/>
       <c r="D242" s="179"/>
@@ -21488,8 +21488,8 @@
       <c r="AY242" s="146"/>
     </row>
     <row r="243" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="196"/>
-      <c r="B243" s="192"/>
+      <c r="A243" s="194"/>
+      <c r="B243" s="212"/>
       <c r="C243" s="216"/>
       <c r="D243" s="184"/>
       <c r="E243" s="184"/>
@@ -21541,13 +21541,13 @@
       <c r="AY243" s="173"/>
     </row>
     <row r="244" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="196"/>
-      <c r="B244" s="193">
+      <c r="A244" s="194"/>
+      <c r="B244" s="190">
         <v>6</v>
       </c>
-      <c r="C244" s="236"/>
+      <c r="C244" s="234"/>
       <c r="D244" s="119"/>
-      <c r="E244" s="259"/>
+      <c r="E244" s="261"/>
       <c r="F244" s="128"/>
       <c r="G244" s="128"/>
       <c r="H244" s="140"/>
@@ -21581,11 +21581,11 @@
       <c r="AJ244" s="119"/>
       <c r="AK244" s="119"/>
       <c r="AL244" s="119" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AM244" s="119"/>
       <c r="AN244" s="140"/>
-      <c r="AO244" s="259"/>
+      <c r="AO244" s="261"/>
       <c r="AP244" s="40"/>
       <c r="AQ244" s="95"/>
       <c r="AR244" s="119"/>
@@ -21598,7 +21598,7 @@
       <c r="AY244" s="96"/>
     </row>
     <row r="245" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="196"/>
+      <c r="A245" s="194"/>
       <c r="B245" s="191"/>
       <c r="C245" s="215"/>
       <c r="D245" s="120"/>
@@ -21651,7 +21651,7 @@
       <c r="AY245" s="98"/>
     </row>
     <row r="246" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="196"/>
+      <c r="A246" s="194"/>
       <c r="B246" s="191"/>
       <c r="C246" s="215"/>
       <c r="D246" s="120"/>
@@ -21704,7 +21704,7 @@
       <c r="AY246" s="96"/>
     </row>
     <row r="247" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="196"/>
+      <c r="A247" s="194"/>
       <c r="B247" s="191"/>
       <c r="C247" s="215"/>
       <c r="D247" s="120"/>
@@ -21757,11 +21757,11 @@
       <c r="AY247" s="96"/>
     </row>
     <row r="248" spans="1:51" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="206"/>
-      <c r="B248" s="194"/>
-      <c r="C248" s="237"/>
+      <c r="A248" s="204"/>
+      <c r="B248" s="192"/>
+      <c r="C248" s="235"/>
       <c r="D248" s="171"/>
-      <c r="E248" s="260"/>
+      <c r="E248" s="262"/>
       <c r="F248" s="130"/>
       <c r="G248" s="130"/>
       <c r="H248" s="101"/>
@@ -21797,7 +21797,7 @@
       <c r="AL248" s="131"/>
       <c r="AM248" s="171"/>
       <c r="AN248" s="63"/>
-      <c r="AO248" s="260"/>
+      <c r="AO248" s="262"/>
       <c r="AP248" s="42"/>
       <c r="AQ248" s="105"/>
       <c r="AR248" s="120"/>
@@ -21822,8 +21822,8 @@
       <c r="AY249" s="15"/>
     </row>
     <row r="250" spans="1:51" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="238" t="s">
-        <v>1114</v>
+      <c r="A250" s="236" t="s">
+        <v>1113</v>
       </c>
       <c r="B250" s="186"/>
       <c r="C250" s="186"/>
@@ -21855,8 +21855,8 @@
       <c r="M251" s="18"/>
     </row>
     <row r="252" spans="1:51" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="257" t="s">
-        <v>1115</v>
+      <c r="A252" s="259" t="s">
+        <v>1114</v>
       </c>
       <c r="B252" s="186"/>
       <c r="C252" s="186"/>
@@ -21922,8 +21922,6 @@
     <mergeCell ref="V209:V212"/>
     <mergeCell ref="O210:O212"/>
     <mergeCell ref="N191:N193"/>
-    <mergeCell ref="O7:O10"/>
-    <mergeCell ref="S134:S137"/>
     <mergeCell ref="B222:B229"/>
     <mergeCell ref="D141:D147"/>
     <mergeCell ref="C109:C115"/>
@@ -21946,10 +21944,6 @@
     <mergeCell ref="AM8:AM12"/>
     <mergeCell ref="D72:D79"/>
     <mergeCell ref="E191:E196"/>
-    <mergeCell ref="AE6:AE9"/>
-    <mergeCell ref="AL24:AL29"/>
-    <mergeCell ref="Q176:Q179"/>
-    <mergeCell ref="M97:M98"/>
     <mergeCell ref="AK238:AK240"/>
     <mergeCell ref="AY177:AY180"/>
     <mergeCell ref="AN110:AN114"/>
@@ -21967,6 +21961,9 @@
     <mergeCell ref="AA184:AA189"/>
     <mergeCell ref="T160:T163"/>
     <mergeCell ref="AD175:AD177"/>
+    <mergeCell ref="AN176:AN180"/>
+    <mergeCell ref="AQ86:AQ88"/>
+    <mergeCell ref="S134:S137"/>
     <mergeCell ref="A108:A157"/>
     <mergeCell ref="S32:S34"/>
     <mergeCell ref="S159:S161"/>
@@ -21986,9 +21983,11 @@
     <mergeCell ref="L97:L98"/>
     <mergeCell ref="B31:B38"/>
     <mergeCell ref="D83:D88"/>
-    <mergeCell ref="M17:M21"/>
-    <mergeCell ref="AN176:AN180"/>
-    <mergeCell ref="AQ86:AQ88"/>
+    <mergeCell ref="A158:A206"/>
+    <mergeCell ref="C119:C124"/>
+    <mergeCell ref="C72:C79"/>
+    <mergeCell ref="B71:B79"/>
+    <mergeCell ref="E34:E38"/>
     <mergeCell ref="E24:E30"/>
     <mergeCell ref="AQ63:AQ66"/>
     <mergeCell ref="AP85:AP87"/>
@@ -22010,6 +22009,9 @@
     <mergeCell ref="AN32:AN35"/>
     <mergeCell ref="AM25:AM29"/>
     <mergeCell ref="J175:J177"/>
+    <mergeCell ref="J72:J76"/>
+    <mergeCell ref="N90:N92"/>
+    <mergeCell ref="E184:E190"/>
     <mergeCell ref="L8:L12"/>
     <mergeCell ref="AL31:AL34"/>
     <mergeCell ref="AC33:AC37"/>
@@ -22049,6 +22051,8 @@
     <mergeCell ref="AA55:AA57"/>
     <mergeCell ref="AL127:AL131"/>
     <mergeCell ref="AW178:AW180"/>
+    <mergeCell ref="AV73:AV78"/>
+    <mergeCell ref="AB93:AB97"/>
     <mergeCell ref="AU9:AU12"/>
     <mergeCell ref="P142:P144"/>
     <mergeCell ref="H142:H147"/>
@@ -22097,7 +22101,23 @@
     <mergeCell ref="AX134:AX137"/>
     <mergeCell ref="AW141:AW143"/>
     <mergeCell ref="AY141:AY143"/>
-    <mergeCell ref="AO6:AO9"/>
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="AG208:AG209"/>
+    <mergeCell ref="P232:P236"/>
+    <mergeCell ref="AD90:AD92"/>
+    <mergeCell ref="AM55:AM58"/>
+    <mergeCell ref="AO55:AO58"/>
+    <mergeCell ref="AM126:AM129"/>
+    <mergeCell ref="AN209:AN211"/>
+    <mergeCell ref="O168:O172"/>
+    <mergeCell ref="AJ31:AJ34"/>
+    <mergeCell ref="AC176:AC180"/>
+    <mergeCell ref="AE6:AE9"/>
+    <mergeCell ref="AL24:AL29"/>
+    <mergeCell ref="Q176:Q179"/>
+    <mergeCell ref="M97:M98"/>
+    <mergeCell ref="M17:M21"/>
+    <mergeCell ref="O7:O10"/>
     <mergeCell ref="AP234:AP235"/>
     <mergeCell ref="AA223:AA226"/>
     <mergeCell ref="K159:K161"/>
@@ -22109,18 +22129,7 @@
     <mergeCell ref="AK232:AK236"/>
     <mergeCell ref="K90:K92"/>
     <mergeCell ref="M90:M92"/>
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="AG208:AG209"/>
-    <mergeCell ref="P232:P236"/>
-    <mergeCell ref="AD90:AD92"/>
-    <mergeCell ref="AM55:AM58"/>
-    <mergeCell ref="AO55:AO58"/>
-    <mergeCell ref="AM126:AM129"/>
-    <mergeCell ref="AN209:AN211"/>
-    <mergeCell ref="O168:O172"/>
-    <mergeCell ref="AJ31:AJ34"/>
     <mergeCell ref="K167:K170"/>
-    <mergeCell ref="AC176:AC180"/>
     <mergeCell ref="C197:C201"/>
     <mergeCell ref="E244:E248"/>
     <mergeCell ref="L168:L173"/>
@@ -22166,6 +22175,9 @@
     <mergeCell ref="AQ223:AQ225"/>
     <mergeCell ref="AI223:AI225"/>
     <mergeCell ref="AV217:AV220"/>
+    <mergeCell ref="AF226:AF228"/>
+    <mergeCell ref="AA72:AA75"/>
+    <mergeCell ref="AA168:AA172"/>
     <mergeCell ref="AT9:AT12"/>
     <mergeCell ref="AE56:AE60"/>
     <mergeCell ref="AX215:AX218"/>
@@ -22262,9 +22274,6 @@
     <mergeCell ref="AV191:AV194"/>
     <mergeCell ref="J232:J235"/>
     <mergeCell ref="B182:B190"/>
-    <mergeCell ref="AF226:AF228"/>
-    <mergeCell ref="AA72:AA75"/>
-    <mergeCell ref="AA168:AA172"/>
     <mergeCell ref="Q223:Q226"/>
     <mergeCell ref="AY136:AY139"/>
     <mergeCell ref="AC224:AC228"/>
@@ -22274,20 +22283,23 @@
     <mergeCell ref="AW182:AW186"/>
     <mergeCell ref="AU109:AU113"/>
     <mergeCell ref="AS134:AS137"/>
-    <mergeCell ref="AV73:AV78"/>
-    <mergeCell ref="AB93:AB97"/>
-    <mergeCell ref="J72:J76"/>
     <mergeCell ref="AH117:AH120"/>
     <mergeCell ref="AJ117:AJ120"/>
     <mergeCell ref="J126:J128"/>
-    <mergeCell ref="N90:N92"/>
     <mergeCell ref="AX117:AX120"/>
     <mergeCell ref="AY208:AY211"/>
-    <mergeCell ref="A158:A206"/>
     <mergeCell ref="AU136:AU139"/>
     <mergeCell ref="AI117:AI120"/>
     <mergeCell ref="AO210:AO212"/>
     <mergeCell ref="AW136:AW139"/>
+    <mergeCell ref="K187:K189"/>
+    <mergeCell ref="AY160:AY164"/>
+    <mergeCell ref="AX191:AX194"/>
+    <mergeCell ref="J160:J164"/>
+    <mergeCell ref="AB215:AB217"/>
+    <mergeCell ref="AT57:AT61"/>
+    <mergeCell ref="AX15:AX19"/>
+    <mergeCell ref="AC16:AC20"/>
     <mergeCell ref="AV231:AV233"/>
     <mergeCell ref="AI15:AI19"/>
     <mergeCell ref="Q56:Q59"/>
@@ -22299,38 +22311,39 @@
     <mergeCell ref="R175:R177"/>
     <mergeCell ref="AN232:AN236"/>
     <mergeCell ref="V81:V84"/>
-    <mergeCell ref="K187:K189"/>
     <mergeCell ref="P15:P19"/>
     <mergeCell ref="AB159:AB162"/>
     <mergeCell ref="AR141:AR143"/>
     <mergeCell ref="AU223:AU225"/>
     <mergeCell ref="AB109:AB112"/>
     <mergeCell ref="AP31:AP34"/>
-    <mergeCell ref="E184:E190"/>
-    <mergeCell ref="AY160:AY164"/>
     <mergeCell ref="AU72:AU75"/>
     <mergeCell ref="AJ89:AJ92"/>
-    <mergeCell ref="C119:C124"/>
     <mergeCell ref="AG15:AG18"/>
-    <mergeCell ref="C72:C79"/>
     <mergeCell ref="AB184:AB189"/>
-    <mergeCell ref="AM223:AM226"/>
-    <mergeCell ref="AX191:AX194"/>
-    <mergeCell ref="AG33:AG37"/>
-    <mergeCell ref="J160:J164"/>
-    <mergeCell ref="AC73:AC78"/>
-    <mergeCell ref="R15:R20"/>
-    <mergeCell ref="AM73:AM78"/>
-    <mergeCell ref="AI33:AI37"/>
-    <mergeCell ref="AA141:AA143"/>
     <mergeCell ref="AY97:AY99"/>
     <mergeCell ref="V91:V95"/>
     <mergeCell ref="AE134:AE136"/>
     <mergeCell ref="U208:U210"/>
     <mergeCell ref="AK109:AK112"/>
     <mergeCell ref="AI109:AI112"/>
-    <mergeCell ref="C225:C229"/>
-    <mergeCell ref="AC160:AC164"/>
+    <mergeCell ref="AB72:AB75"/>
+    <mergeCell ref="AP73:AP78"/>
+    <mergeCell ref="AV160:AV164"/>
+    <mergeCell ref="AY118:AY123"/>
+    <mergeCell ref="AQ91:AQ95"/>
+    <mergeCell ref="AC73:AC78"/>
+    <mergeCell ref="AP184:AP189"/>
+    <mergeCell ref="AI97:AI99"/>
+    <mergeCell ref="J142:J144"/>
+    <mergeCell ref="N97:N99"/>
+    <mergeCell ref="N135:N139"/>
+    <mergeCell ref="M126:M128"/>
+    <mergeCell ref="R15:R20"/>
+    <mergeCell ref="AM73:AM78"/>
+    <mergeCell ref="AI33:AI37"/>
+    <mergeCell ref="AA141:AA143"/>
+    <mergeCell ref="AG33:AG37"/>
     <mergeCell ref="AU89:AU93"/>
     <mergeCell ref="T167:T171"/>
     <mergeCell ref="AQ127:AQ131"/>
@@ -22338,16 +22351,12 @@
     <mergeCell ref="V175:V178"/>
     <mergeCell ref="B116:B124"/>
     <mergeCell ref="O141:O144"/>
-    <mergeCell ref="AB72:AB75"/>
     <mergeCell ref="Q141:Q144"/>
     <mergeCell ref="Q110:Q114"/>
     <mergeCell ref="AO126:AO129"/>
-    <mergeCell ref="AP73:AP78"/>
-    <mergeCell ref="B71:B79"/>
     <mergeCell ref="O111:O113"/>
     <mergeCell ref="P97:P98"/>
     <mergeCell ref="C126:C132"/>
-    <mergeCell ref="E34:E38"/>
     <mergeCell ref="H137:H140"/>
     <mergeCell ref="G34:G38"/>
     <mergeCell ref="B108:B115"/>
@@ -22364,7 +22373,15 @@
     <mergeCell ref="B49:B53"/>
     <mergeCell ref="B62:B70"/>
     <mergeCell ref="C33:C38"/>
-    <mergeCell ref="AV160:AV164"/>
+    <mergeCell ref="O82:O86"/>
+    <mergeCell ref="J117:J120"/>
+    <mergeCell ref="K97:K99"/>
+    <mergeCell ref="S117:S120"/>
+    <mergeCell ref="AL91:AL94"/>
+    <mergeCell ref="AL73:AL77"/>
+    <mergeCell ref="AN73:AN77"/>
+    <mergeCell ref="Q119:Q122"/>
+    <mergeCell ref="AO97:AO99"/>
     <mergeCell ref="AA235:AA237"/>
     <mergeCell ref="AO217:AO220"/>
     <mergeCell ref="AH33:AH37"/>
@@ -22389,8 +22406,6 @@
     <mergeCell ref="AC134:AC136"/>
     <mergeCell ref="AX97:AX99"/>
     <mergeCell ref="K35:K38"/>
-    <mergeCell ref="M215:M217"/>
-    <mergeCell ref="O82:O86"/>
     <mergeCell ref="AY238:AY240"/>
     <mergeCell ref="K238:K240"/>
     <mergeCell ref="AA238:AA239"/>
@@ -22412,24 +22427,9 @@
     <mergeCell ref="AY182:AY186"/>
     <mergeCell ref="AX238:AX240"/>
     <mergeCell ref="K223:K225"/>
-    <mergeCell ref="J117:J120"/>
-    <mergeCell ref="K97:K99"/>
     <mergeCell ref="AO142:AO144"/>
     <mergeCell ref="AG216:AG218"/>
     <mergeCell ref="AP137:AP140"/>
-    <mergeCell ref="S117:S120"/>
-    <mergeCell ref="AE207:AE213"/>
-    <mergeCell ref="AL91:AL94"/>
-    <mergeCell ref="AL73:AL77"/>
-    <mergeCell ref="AN73:AN77"/>
-    <mergeCell ref="Q119:Q122"/>
-    <mergeCell ref="AO97:AO99"/>
-    <mergeCell ref="AP184:AP189"/>
-    <mergeCell ref="AI97:AI99"/>
-    <mergeCell ref="J142:J144"/>
-    <mergeCell ref="N97:N99"/>
-    <mergeCell ref="N135:N139"/>
-    <mergeCell ref="M126:M128"/>
     <mergeCell ref="A250:M250"/>
     <mergeCell ref="E15:E22"/>
     <mergeCell ref="R72:R75"/>
@@ -22478,7 +22478,6 @@
     <mergeCell ref="O126:O128"/>
     <mergeCell ref="AB175:AB177"/>
     <mergeCell ref="AL108:AL111"/>
-    <mergeCell ref="AB215:AB217"/>
     <mergeCell ref="AT238:AT241"/>
     <mergeCell ref="AL135:AL138"/>
     <mergeCell ref="V158:V162"/>
@@ -22502,12 +22501,7 @@
     <mergeCell ref="AD34:AD36"/>
     <mergeCell ref="AO223:AO228"/>
     <mergeCell ref="AR33:AR37"/>
-    <mergeCell ref="AY118:AY123"/>
     <mergeCell ref="AT33:AT37"/>
-    <mergeCell ref="H33:H38"/>
-    <mergeCell ref="P191:P192"/>
-    <mergeCell ref="E208:E213"/>
-    <mergeCell ref="AH55:AH57"/>
     <mergeCell ref="AE225:AE228"/>
     <mergeCell ref="B148:B152"/>
     <mergeCell ref="AM216:AM220"/>
@@ -22521,15 +22515,17 @@
     <mergeCell ref="R224:R227"/>
     <mergeCell ref="K119:K123"/>
     <mergeCell ref="AJ63:AJ66"/>
-    <mergeCell ref="AQ91:AQ95"/>
     <mergeCell ref="B158:B165"/>
-    <mergeCell ref="AT57:AT61"/>
     <mergeCell ref="L74:L78"/>
     <mergeCell ref="R161:R164"/>
-    <mergeCell ref="AX15:AX19"/>
     <mergeCell ref="M55:M57"/>
     <mergeCell ref="B191:B196"/>
     <mergeCell ref="B80:B88"/>
+    <mergeCell ref="C225:C229"/>
+    <mergeCell ref="AC160:AC164"/>
+    <mergeCell ref="M215:M217"/>
+    <mergeCell ref="AE207:AE213"/>
+    <mergeCell ref="AM223:AM226"/>
     <mergeCell ref="B23:B30"/>
     <mergeCell ref="B153:B157"/>
     <mergeCell ref="AE168:AE172"/>
@@ -22549,7 +22545,11 @@
     <mergeCell ref="AA159:AA162"/>
     <mergeCell ref="E175:E181"/>
     <mergeCell ref="AH91:AH95"/>
-    <mergeCell ref="AC16:AC20"/>
+    <mergeCell ref="B174:B181"/>
+    <mergeCell ref="H33:H38"/>
+    <mergeCell ref="P191:P192"/>
+    <mergeCell ref="E208:E213"/>
+    <mergeCell ref="AH55:AH57"/>
     <mergeCell ref="AX231:AX233"/>
     <mergeCell ref="AE117:AE120"/>
     <mergeCell ref="AS223:AS226"/>
@@ -22598,7 +22598,6 @@
     <mergeCell ref="B89:B96"/>
     <mergeCell ref="B141:B147"/>
     <mergeCell ref="A54:A107"/>
-    <mergeCell ref="B174:B181"/>
     <mergeCell ref="B244:B248"/>
     <mergeCell ref="AN117:AN122"/>
     <mergeCell ref="AJ224:AJ228"/>
@@ -22646,6 +22645,7 @@
     <mergeCell ref="AK8:AK12"/>
     <mergeCell ref="AF15:AF18"/>
     <mergeCell ref="AJ7:AJ10"/>
+    <mergeCell ref="AO6:AO9"/>
     <mergeCell ref="AV7:AV9"/>
     <mergeCell ref="AU18:AU21"/>
     <mergeCell ref="AG7:AG9"/>
